--- a/pelvic-block-iqc-pareto/Pelvic_Block_IQC_Pareto_RootCause.xlsx
+++ b/pelvic-block-iqc-pareto/Pelvic_Block_IQC_Pareto_RootCause.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -101,6 +101,12 @@
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -242,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -298,6 +304,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -333,58 +340,58 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,7 +470,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -471,14 +477,26 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F3864"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>Defect Pareto — Rejected Pelvic Blocks (SH: Martins, 2026-07-08)</a:t>
+              <a:rPr sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F3864"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Defect Pareto — Rejected Pelvic Blocks   (SH: Martins, 2026-07-08)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -493,13 +511,183 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2E5B8A"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E5B8A"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E5B8A"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E5B8A"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E5B8A"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="AFC7E3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="AFC7E3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="6"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="AFC7E3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="AFC7E3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="8"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="AFC7E3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="9"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="AFC7E3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="0"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="950" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="404040"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="950" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="404040"/>
+                  </a:solidFill>
+                  <a:latin typeface="Calibri"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <dLblPos val="outEnd"/>
+            <showVal val="1"/>
+          </dLbls>
           <cat>
             <numRef>
-              <f>'Pareto'!$C$6:$C$15</f>
+              <f>'Pareto'!$M$6:$M$15</f>
             </numRef>
           </cat>
           <val>
@@ -508,7 +696,7 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="40"/>
+        <gapWidth val="55"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -523,13 +711,80 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="5"/>
+            <size val="6"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <numFmt formatCode="0%"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="850" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="C0504D"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="850" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="C0504D"/>
+                  </a:solidFill>
+                  <a:latin typeface="Calibri"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <dLblPos val="t"/>
+            <showVal val="1"/>
+          </dLbls>
+          <val>
+            <numRef>
+              <f>'Pareto'!$F$6:$F$15</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Pareto'!N5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="A6A6A6"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
             <spPr>
               <a:ln>
                 <a:prstDash val="solid"/>
@@ -538,7 +793,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Pareto'!$F$6:$F$15</f>
+              <f>'Pareto'!$N$6:$N$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -551,24 +806,40 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Defect mode</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="BFBFBF"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr rot="-2700000"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="850" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="595959"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="850" b="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -576,9 +847,20 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E6E6E6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -594,8 +876,31 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="595959"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
         <crosses val="autoZero"/>
       </valAx>
@@ -606,8 +911,8 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -626,12 +931,35 @@
         <numFmt formatCode="0%" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="595959"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
         <crosses val="max"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -648,7 +976,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="4320000"/>
+    <ext cx="9360000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -665,12 +993,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>0</col>
       <colOff>0</colOff>
       <row>27</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6819900" cy="3114675"/>
+    <ext cx="5667375" cy="2905125"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -3734,7 +4062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3797,17 +4125,23 @@
           <t>Cumulative %</t>
         </is>
       </c>
+      <c r="M5" s="19" t="n"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>80% target</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="A6" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>Membrane damage in critical area</t>
         </is>
@@ -3816,25 +4150,33 @@
         <f>SUM('Inspection Log'!Q5:Q430)</f>
         <v/>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="23">
         <f>D6/SUM('Inspection Log'!L5:U430)</f>
         <v/>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="23">
         <f>E6</f>
         <v/>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>D6 · Membrane dmg</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Ureters not embedded</t>
         </is>
@@ -3843,25 +4185,33 @@
         <f>SUM('Inspection Log'!L5:L430)</f>
         <v/>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="23">
         <f>D7/SUM('Inspection Log'!L5:U430)</f>
         <v/>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="23">
         <f>F6+E7</f>
         <v/>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>D1 · Ureters n/e</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="n">
+      <c r="A8" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>Suspensory ligaments damaged</t>
         </is>
@@ -3870,25 +4220,33 @@
         <f>SUM('Inspection Log'!O5:O430)</f>
         <v/>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="23">
         <f>D8/SUM('Inspection Log'!L5:U430)</f>
         <v/>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="23">
         <f>F7+E8</f>
         <v/>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>D4 · Susp. ligament</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>Urethra cut</t>
         </is>
@@ -3897,25 +4255,33 @@
         <f>SUM('Inspection Log'!P5:P430)</f>
         <v/>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="23">
         <f>D9/SUM('Inspection Log'!L5:U430)</f>
         <v/>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="23">
         <f>F8+E9</f>
         <v/>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>D5 · Urethra cut</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="n">
+      <c r="A10" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>Ureter missing</t>
         </is>
@@ -3924,25 +4290,33 @@
         <f>SUM('Inspection Log'!N5:N430)</f>
         <v/>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="23">
         <f>D10/SUM('Inspection Log'!L5:U430)</f>
         <v/>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="23">
         <f>F9+E10</f>
         <v/>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>D3 · Ureter missing</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>D8</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>Bowel cut / opened / separated</t>
         </is>
@@ -3951,25 +4325,33 @@
         <f>SUM('Inspection Log'!S5:S430)</f>
         <v/>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="23">
         <f>D11/SUM('Inspection Log'!L5:U430)</f>
         <v/>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="23">
         <f>F10+E11</f>
         <v/>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>D8 · Bowel cut</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="n">
+      <c r="A12" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>Ureter cut / severed</t>
         </is>
@@ -3978,25 +4360,33 @@
         <f>SUM('Inspection Log'!M5:M430)</f>
         <v/>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="23">
         <f>D12/SUM('Inspection Log'!L5:U430)</f>
         <v/>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="23">
         <f>F11+E12</f>
         <v/>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>D2 · Ureter cut</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>Bladder deformed / deformed attachment</t>
         </is>
@@ -4005,25 +4395,33 @@
         <f>SUM('Inspection Log'!R5:R430)</f>
         <v/>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="23">
         <f>D13/SUM('Inspection Log'!L5:U430)</f>
         <v/>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="23">
         <f>F12+E13</f>
         <v/>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>D7 · Bladder def.</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="n">
+      <c r="A14" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>D9</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Blood clots</t>
         </is>
@@ -4032,25 +4430,33 @@
         <f>SUM('Inspection Log'!T5:T430)</f>
         <v/>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="23">
         <f>D14/SUM('Inspection Log'!L5:U430)</f>
         <v/>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="23">
         <f>F13+E14</f>
         <v/>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>D9 · Blood clots</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>D10</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>Broad ligament hole / tear</t>
         </is>
@@ -4059,32 +4465,40 @@
         <f>SUM('Inspection Log'!U5:U430)</f>
         <v/>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="23">
         <f>D15/SUM('Inspection Log'!L5:U430)</f>
         <v/>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="23">
         <f>F14+E15</f>
         <v/>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>D10 · Broad ligament</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="n"/>
-      <c r="B16" s="24" t="n"/>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="A16" s="25" t="n"/>
+      <c r="B16" s="25" t="n"/>
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="27">
         <f>SUM(D6:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>D16/SUM('Inspection Log'!L5:U430)</f>
         <v/>
       </c>
-      <c r="F16" s="24" t="n"/>
+      <c r="F16" s="25" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
@@ -4121,37 +4535,37 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Evisceration</t>
         </is>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <f>SUM('Inspection Log'!L5:L430)+SUM('Inspection Log'!M5:M430)+SUM('Inspection Log'!O5:O430)+SUM('Inspection Log'!Q5:Q430)+SUM('Inspection Log'!S5:S430)+SUM('Inspection Log'!U5:U430)</f>
         <v/>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <f>C21/SUM('Inspection Log'!L5:U430)</f>
         <v/>
       </c>
-      <c r="E21" s="29" t="inlineStr">
+      <c r="E21" s="30" t="inlineStr">
         <is>
           <t>D1, D2, D4, D6, D8, D10</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Carcass splitting</t>
         </is>
@@ -4160,23 +4574,23 @@
         <f>SUM('Inspection Log'!P5:P430)</f>
         <v/>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="23">
         <f>C22/SUM('Inspection Log'!L5:U430)</f>
         <v/>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>Bung dropping</t>
         </is>
@@ -4185,23 +4599,23 @@
         <f>SUM('Inspection Log'!N5:N430)</f>
         <v/>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="23">
         <f>C23/SUM('Inspection Log'!L5:U430)</f>
         <v/>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="24" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>Live / physiology</t>
         </is>
@@ -4210,23 +4624,23 @@
         <f>SUM('Inspection Log'!R5:R430)</f>
         <v/>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="23">
         <f>C24/SUM('Inspection Log'!L5:U430)</f>
         <v/>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>Sticking / Bleeding</t>
         </is>
@@ -4235,11 +4649,11 @@
         <f>SUM('Inspection Log'!T5:T430)</f>
         <v/>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="23">
         <f>C25/SUM('Inspection Log'!L5:U430)</f>
         <v/>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="24" t="inlineStr">
         <is>
           <t>D9</t>
         </is>
@@ -4362,53 +4776,53 @@
           <t>D6</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Membrane damage in critical area</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>Membrane torn/holed in critical area</t>
         </is>
       </c>
-      <c r="D5" s="33" t="inlineStr">
+      <c r="D5" s="34" t="inlineStr">
         <is>
           <t>Knife path too deep / tensile tear during gut pull</t>
         </is>
       </c>
-      <c r="E5" s="33" t="inlineStr">
+      <c r="E5" s="34" t="inlineStr">
         <is>
           <t>Evisceration technique not standardized for pelvic zone</t>
         </is>
       </c>
-      <c r="F5" s="33" t="inlineStr">
+      <c r="F5" s="34" t="inlineStr">
         <is>
           <t>No defined knife depth/path SOP + line speed pressure</t>
         </is>
       </c>
-      <c r="G5" s="34" t="inlineStr">
+      <c r="G5" s="35" t="inlineStr">
         <is>
           <t>(confirm w/ supplier) training + line-speed control gap</t>
         </is>
       </c>
-      <c r="H5" s="35" t="inlineStr">
+      <c r="H5" s="36" t="inlineStr">
         <is>
           <t>Retrain knife depth &amp; path in pelvic zone; blunt-dissect; slow line through pelvic cut</t>
         </is>
       </c>
-      <c r="I5" s="36" t="inlineStr">
+      <c r="I5" s="37" t="inlineStr">
         <is>
           <t>SH Martins - Evisceration lead</t>
         </is>
       </c>
-      <c r="J5" s="36" t="inlineStr"/>
-      <c r="K5" s="37" t="inlineStr">
+      <c r="J5" s="37" t="inlineStr"/>
+      <c r="K5" s="38" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L5" s="38" t="inlineStr"/>
+      <c r="L5" s="39" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
@@ -4416,53 +4830,53 @@
           <t>D1</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Ureters not embedded</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>Ureters not embedded in tissue</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>Fascia/perirenal fat stripped away from ureter</t>
         </is>
       </c>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>Excessive pull force / over-trim during gut set removal</t>
         </is>
       </c>
-      <c r="F6" s="33" t="inlineStr">
+      <c r="F6" s="34" t="inlineStr">
         <is>
           <t>Pull technique &amp; trim spec not controlled</t>
         </is>
       </c>
-      <c r="G6" s="34" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t>(confirm) handling standard missing</t>
         </is>
       </c>
-      <c r="H6" s="35" t="inlineStr">
+      <c r="H6" s="36" t="inlineStr">
         <is>
           <t>Standardize pull-force &amp; angle; limit fat stripping; gentler pit drop</t>
         </is>
       </c>
-      <c r="I6" s="36" t="inlineStr">
+      <c r="I6" s="37" t="inlineStr">
         <is>
           <t>SH Martins - Evisceration lead</t>
         </is>
       </c>
-      <c r="J6" s="36" t="inlineStr"/>
-      <c r="K6" s="37" t="inlineStr">
+      <c r="J6" s="37" t="inlineStr"/>
+      <c r="K6" s="38" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L6" s="38" t="inlineStr"/>
+      <c r="L6" s="39" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
@@ -4470,53 +4884,53 @@
           <t>D4</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Suspensory ligaments damaged</t>
         </is>
       </c>
-      <c r="C7" s="33" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>Suspensory ligaments torn/frayed</t>
         </is>
       </c>
-      <c r="D7" s="33" t="inlineStr">
+      <c r="D7" s="34" t="inlineStr">
         <is>
           <t>Block pulled/handled by the ligaments</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="E7" s="34" t="inlineStr">
         <is>
           <t>Rough handling + high traction on removal</t>
         </is>
       </c>
-      <c r="F7" s="33" t="inlineStr">
+      <c r="F7" s="34" t="inlineStr">
         <is>
           <t>No 'support-surface' handling rule</t>
         </is>
       </c>
-      <c r="G7" s="34" t="inlineStr">
+      <c r="G7" s="35" t="inlineStr">
         <is>
           <t>(confirm) handling standard missing</t>
         </is>
       </c>
-      <c r="H7" s="35" t="inlineStr">
+      <c r="H7" s="36" t="inlineStr">
         <is>
           <t>Handle block by support surface, not ligaments; control pull force</t>
         </is>
       </c>
-      <c r="I7" s="36" t="inlineStr">
+      <c r="I7" s="37" t="inlineStr">
         <is>
           <t>SH Martins - Evisceration lead</t>
         </is>
       </c>
-      <c r="J7" s="36" t="inlineStr"/>
-      <c r="K7" s="37" t="inlineStr">
+      <c r="J7" s="37" t="inlineStr"/>
+      <c r="K7" s="38" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L7" s="38" t="inlineStr"/>
+      <c r="L7" s="39" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
@@ -4524,53 +4938,53 @@
           <t>D5</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Urethra cut</t>
         </is>
       </c>
-      <c r="C8" s="33" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>Urethra cut</t>
         </is>
       </c>
-      <c r="D8" s="33" t="inlineStr">
+      <c r="D8" s="34" t="inlineStr">
         <is>
           <t>Sharp transection through pelvic zone</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>Splitting saw off-center / bung-drop cut catches urethra</t>
         </is>
       </c>
-      <c r="F8" s="33" t="inlineStr">
+      <c r="F8" s="34" t="inlineStr">
         <is>
           <t>Saw alignment &amp; pelvic-split centering not verified</t>
         </is>
       </c>
-      <c r="G8" s="34" t="inlineStr">
+      <c r="G8" s="35" t="inlineStr">
         <is>
           <t>(confirm) saw calibration + technique gap</t>
         </is>
       </c>
-      <c r="H8" s="35" t="inlineStr">
+      <c r="H8" s="36" t="inlineStr">
         <is>
           <t>Center split on symphysis; calibrate/align saw; slow through pelvic zone</t>
         </is>
       </c>
-      <c r="I8" s="36" t="inlineStr">
+      <c r="I8" s="37" t="inlineStr">
         <is>
           <t>SH Martins - Splitting lead</t>
         </is>
       </c>
-      <c r="J8" s="36" t="inlineStr"/>
-      <c r="K8" s="37" t="inlineStr">
+      <c r="J8" s="37" t="inlineStr"/>
+      <c r="K8" s="38" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L8" s="38" t="inlineStr"/>
+      <c r="L8" s="39" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
@@ -4578,81 +4992,81 @@
           <t>D8</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Bowel cut / opened / separated</t>
         </is>
       </c>
-      <c r="C9" s="33" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>Bowel cut open / separated (FOOD SAFETY)</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr">
+      <c r="D9" s="34" t="inlineStr">
         <is>
           <t>Knife slip or aggressive bung separation opens bowel</t>
         </is>
       </c>
-      <c r="E9" s="33" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t>Bung not adequately bagged/tied before cut</t>
         </is>
       </c>
-      <c r="F9" s="33" t="inlineStr">
+      <c r="F9" s="34" t="inlineStr">
         <is>
           <t>Bung-dropping CCP not robust</t>
         </is>
       </c>
-      <c r="G9" s="34" t="inlineStr">
+      <c r="G9" s="35" t="inlineStr">
         <is>
           <t>(confirm) contamination-control gap at bung station</t>
         </is>
       </c>
-      <c r="H9" s="35" t="inlineStr">
+      <c r="H9" s="36" t="inlineStr">
         <is>
           <t>Reinforce bung bag/tie-off; retrain knife path; treat as contamination CCP</t>
         </is>
       </c>
-      <c r="I9" s="36" t="inlineStr">
+      <c r="I9" s="37" t="inlineStr">
         <is>
           <t>SH Martins - Bung/Evisc. lead</t>
         </is>
       </c>
-      <c r="J9" s="36" t="inlineStr"/>
-      <c r="K9" s="37" t="inlineStr">
+      <c r="J9" s="37" t="inlineStr"/>
+      <c r="K9" s="38" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L9" s="38" t="inlineStr"/>
+      <c r="L9" s="39" t="inlineStr"/>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="39" t="n"/>
-      <c r="B10" s="39" t="n"/>
-      <c r="C10" s="39" t="n"/>
-      <c r="D10" s="39" t="n"/>
-      <c r="E10" s="39" t="n"/>
-      <c r="F10" s="39" t="n"/>
-      <c r="G10" s="40" t="n"/>
-      <c r="H10" s="41" t="n"/>
-      <c r="I10" s="39" t="n"/>
-      <c r="J10" s="39" t="n"/>
-      <c r="K10" s="39" t="n"/>
-      <c r="L10" s="42" t="n"/>
+      <c r="A10" s="40" t="n"/>
+      <c r="B10" s="40" t="n"/>
+      <c r="C10" s="40" t="n"/>
+      <c r="D10" s="40" t="n"/>
+      <c r="E10" s="40" t="n"/>
+      <c r="F10" s="40" t="n"/>
+      <c r="G10" s="41" t="n"/>
+      <c r="H10" s="42" t="n"/>
+      <c r="I10" s="40" t="n"/>
+      <c r="J10" s="40" t="n"/>
+      <c r="K10" s="40" t="n"/>
+      <c r="L10" s="43" t="n"/>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="39" t="n"/>
-      <c r="B11" s="39" t="n"/>
-      <c r="C11" s="39" t="n"/>
-      <c r="D11" s="39" t="n"/>
-      <c r="E11" s="39" t="n"/>
-      <c r="F11" s="39" t="n"/>
-      <c r="G11" s="40" t="n"/>
-      <c r="H11" s="41" t="n"/>
-      <c r="I11" s="39" t="n"/>
-      <c r="J11" s="39" t="n"/>
-      <c r="K11" s="39" t="n"/>
-      <c r="L11" s="42" t="n"/>
+      <c r="A11" s="40" t="n"/>
+      <c r="B11" s="40" t="n"/>
+      <c r="C11" s="40" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
+      <c r="G11" s="41" t="n"/>
+      <c r="H11" s="42" t="n"/>
+      <c r="I11" s="40" t="n"/>
+      <c r="J11" s="40" t="n"/>
+      <c r="K11" s="40" t="n"/>
+      <c r="L11" s="43" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4700,119 +5114,119 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>KEY METRICS</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t>Blocks Inspected</t>
         </is>
       </c>
-      <c r="B5" s="45">
+      <c r="B5" s="46">
         <f>COUNTA('Inspection Log'!A5:A430)-COUNTBLANK('Inspection Log'!A5:A430)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="B6" s="45">
+      <c r="B6" s="46">
         <f>COUNTIF('Inspection Log'!J5:J430,"Pass")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
+      <c r="A7" s="45" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="B7" s="45">
+      <c r="B7" s="46">
         <f>COUNTIF('Inspection Log'!J5:J430,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="44" t="inlineStr">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t>First Pass Yield</t>
         </is>
       </c>
-      <c r="B8" s="46">
+      <c r="B8" s="47">
         <f>IFERROR(COUNTIF('Inspection Log'!J5:J430,"Pass")/(COUNTA('Inspection Log'!A5:A430)-COUNTBLANK('Inspection Log'!A5:A430)),0)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="44" t="inlineStr">
+      <c r="A9" s="45" t="inlineStr">
         <is>
           <t>Total Defect Occurrences</t>
         </is>
       </c>
-      <c r="B9" s="45">
+      <c r="B9" s="46">
         <f>SUM('Inspection Log'!L5:U430)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="44" t="inlineStr">
+      <c r="A10" s="45" t="inlineStr">
         <is>
           <t>Defects per Failed Block</t>
         </is>
       </c>
-      <c r="B10" s="47">
+      <c r="B10" s="48">
         <f>IFERROR(SUM('Inspection Log'!L5:U430)/COUNTIF('Inspection Log'!J5:J430,"Fail"),0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="44" t="inlineStr">
         <is>
           <t>TOP DEFECT (this batch)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="inlineStr">
+      <c r="A13" s="49" t="inlineStr">
         <is>
           <t>Membrane damage in critical area</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="49" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>Dominant supplier station</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="50" t="inlineStr">
+      <c r="A15" s="51" t="inlineStr">
         <is>
           <t>S3 Evisceration  -&gt;  primary target for corrective action</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="51" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Critical / food-safety defect occurrences</t>
         </is>
       </c>
-      <c r="B17" s="52">
+      <c r="B17" s="53">
         <f>SUM('Inspection Log'!Q5:Q430)+SUM('Inspection Log'!S5:S430)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="53" t="inlineStr">
+      <c r="A18" s="54" t="inlineStr">
         <is>
           <t xml:space="preserve">  (Critical codes: D6, D8 — membrane damage &amp; bowel breach)</t>
         </is>

--- a/pelvic-block-iqc-pareto/Pelvic_Block_IQC_Pareto_RootCause.xlsx
+++ b/pelvic-block-iqc-pareto/Pelvic_Block_IQC_Pareto_RootCause.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,9 +92,20 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00375623"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -107,11 +118,6 @@
       <i val="1"/>
       <color rgb="00808080"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -173,6 +179,12 @@
       <color rgb="00808080"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00833C00"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -213,12 +225,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -248,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -286,8 +298,14 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -295,20 +313,20 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -328,7 +346,7 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -340,58 +358,57 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="1" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="20" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="20" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="20" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -491,7 +508,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Defect Pareto — Rejected Pelvic Blocks   (SH: Martins, 2026-07-08)</a:t>
+              <a:t>Defect Pareto — Rejected Pelvic Blocks   (SH: Martins, 2 batches)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -658,6 +675,20 @@
               </a:ln>
             </spPr>
           </dPt>
+          <dPt>
+            <idx val="10"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="AFC7E3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <dLbls>
             <numFmt formatCode="0"/>
             <txPr>
@@ -687,12 +718,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Pareto'!$M$6:$M$15</f>
+              <f>'Pareto'!$M$6:$M$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Pareto'!$D$6:$D$15</f>
+              <f>'Pareto'!$D$6:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -762,7 +793,7 @@
           </dLbls>
           <val>
             <numRef>
-              <f>'Pareto'!$F$6:$F$15</f>
+              <f>'Pareto'!$F$6:$F$16</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -793,7 +824,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Pareto'!$N$6:$N$15</f>
+              <f>'Pareto'!$N$6:$N$16</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -995,7 +1026,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5667375" cy="2905125"/>
@@ -1348,14 +1379,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>This workbook ingests IQC inspection results for rejected pelvic blocks, sorts the defects with a Pareto (which few defects cause most of the loss), and</t>
+          <t>Ingest IQC results for rejected pelvic blocks, sort defects with a Pareto (the few defects causing most loss), and map every defect back to the</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>maps every defect back to the point in the SUPPLIER's process where it is created — so corrective action can be taken BEFORE the tissue block reaches us.</t>
+          <t>point in the SUPPLIER's process where it is created — so corrective action can be taken BEFORE the tissue block reaches us.</t>
         </is>
       </c>
     </row>
@@ -1379,114 +1410,114 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                                                                                                                          |</t>
+          <t xml:space="preserve">                                                                                    OUR side -&gt;  Harvest techs receive block from pit  -&gt;  spec-out / accept  -&gt;  IQC inspection (this data)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                                                                                              OUR side -&gt;  Harvest techs receive block from pit  -&gt;  spec-out / accept decision  -&gt;  IQC inspection (this data)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>HOW THE SHEETS FIT TOGETHER</t>
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>THE SHEETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Inspection Log   Master data — ONE ROW PER BLOCK. Each free-text scrap reason is normalized into 1/0 flags against the defect taxonomy. Append future batches here.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. Inspection Log   Master data — ONE ROW PER BLOCK. Each free-text scrap reason is normalized into 1/0 flags against the defect taxonomy. Append future batches here.</t>
+          <t xml:space="preserve">  2. Defect Taxonomy  Controlled vocabulary (D1–D11) + root-cause map: each defect -&gt; process step, supplier station, 6M cause, mechanism, corrective action.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Defect Taxonomy  The controlled vocabulary (D1–D10) + the root-cause map: each defect -&gt; process step, supplier station, 6M cause, mechanism, corrective action.</t>
+          <t xml:space="preserve">  3. Pareto           Auto-calculating defect Pareto (bar + cumulative line) and a rollup by SUPPLIER STATION — the key view for the supplier conversation.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Pareto           Auto-calculating defect Pareto (bar + cumulative line) and a rollup by SUPPLIER STATION — the single most useful view for the supplier conversation.</t>
+          <t xml:space="preserve">  4. Root Cause 5-Why  Structured RCA template, seeded for the vital-few defects, with a Lessons-Learned column to fill in over time.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Root Cause 5-Why  A structured RCA template, pre-seeded for the vital-few defects, with a Lessons-Learned column for you to fill in over time.</t>
+          <t xml:space="preserve">  5. Dashboard        Combined KPIs + a per-batch breakdown so you can watch the trend batch over batch.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5. Dashboard        Batch KPI summary (yield, top defect, food-safety flags).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>HOW TO ADD THE NEXT INSPECTION (keep the framework alive)</t>
+      <c r="A19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>HOW TO ADD THE NEXT INSPECTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  a. In 'Inspection Log', add one row per inspected block (metadata + Result = Pass/Fail + verbatim reason).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  a. Go to 'Inspection Log'. Add one row per inspected block (copy the metadata columns, set Result = Pass/Fail, paste the verbatim reason).</t>
+          <t xml:space="preserve">  b. Put a 1 in each defect column (D1–D11) that applies. Use the dropdown. If a NEW defect type appears, add it to 'Defect Taxonomy' first, then add its column.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  b. Put a 1 in each defect column (D1–D10) that applies to that block; leave the rest blank/0. Use the dropdown list; if a NEW defect appears, add it to 'Defect Taxonomy' first.</t>
+          <t xml:space="preserve">  c. Pareto + Dashboard recalc automatically. Re-sort the Pareto table high-&gt;low if the ranking changes (counts are live; row order is not).</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  c. The Pareto and Dashboard recalculate automatically. (Re-sort the Pareto table high-&gt;low if the ranking changes — counts update live, row order does not.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>READING THE PARETO</t>
+      <c r="A24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>WHAT THE DATA SAYS SO FAR  (2 batches, SH: Martins — kills 2026-05-27 &amp; 2026-07-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  57 blocks inspected · 9 pass · 48 fail · combined First Pass Yield 15.8% · 78 defect occurrences</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  The 'vital few' are the leftmost bars whose cumulative line reaches ~80%. Fix those first. For THIS batch they are membrane damage, ureters-not-embedded,</t>
+          <t xml:space="preserve">  Vital few (~78%): membrane damage (critical area), ureters not embedded, urethra breach, suspensory-ligament damage.  ~78% of ALL defects originate at ONE station: Evisceration.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  suspensory-ligament damage and urethra cuts — and ~77% of all defects trace to ONE supplier station: Evisceration.</t>
+          <t xml:space="preserve">  OPEN ITEM: 5 blocks (kill 2026-05-27) with an 8" hole in the bladder suspensory ligament are recorded as PASS pending ME/DE determination — flip to Fail + tag D4 if confirmed.</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1534,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Critical = function-destroying or food-safety (e.g. bowel breach = contamination).   Major = block rejected.   Minor = cosmetic / recoverable.</t>
+          <t xml:space="preserve">  Critical = function-destroying or food-safety (e.g. bowel/colon/rectum breach = contamination).   Major = block rejected.   Minor = cosmetic / recoverable.</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1551,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  IQC Tally Sheet — SH: Martins — Kill/Harvest 2026-07-08 — 26 inspected, 1 pass, 25 fail (First Pass Yield 3.8%).  Original file kept as source_IQC_Martins_failed_blocks_2026-07-08.xlsx</t>
+          <t xml:space="preserve">  IQC Tally Sheets — SH: Martins. Originals kept as source_*.xlsx in this folder.</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:X61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1581,9 +1612,9 @@
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="6" customWidth="1" min="14" max="14"/>
@@ -1594,7 +1625,9 @@
     <col width="6" customWidth="1" min="19" max="19"/>
     <col width="6" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="34" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1607,7 +1640,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Append future inspections below. Put 1 in each defect column that applies. Counts on Pareto/Dashboard update automatically.</t>
+          <t>Append future inspections below. Put 1 in each defect column that applies. Pareto/Dashboard update automatically.</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1752,17 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
+          <t>D11</t>
+        </is>
+      </c>
+      <c r="W4" s="6" t="inlineStr">
+        <is>
           <t># Defects</t>
+        </is>
+      </c>
+      <c r="X4" s="6" t="inlineStr">
+        <is>
+          <t>Notes / Disposition</t>
         </is>
       </c>
     </row>
@@ -1731,19 +1774,15 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr"/>
       <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -1751,14 +1790,10 @@
       </c>
       <c r="F5" s="7" t="inlineStr"/>
       <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
@@ -1768,7 +1803,7 @@
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>Large hole near right broad ligament and membrane causing seperation of bowel and ureters.</t>
+          <t>hole in the distal end of the colon</t>
         </is>
       </c>
       <c r="L5" s="10" t="n"/>
@@ -1776,21 +1811,19 @@
       <c r="N5" s="10" t="n"/>
       <c r="O5" s="10" t="n"/>
       <c r="P5" s="10" t="n"/>
-      <c r="Q5" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q5" s="10" t="n"/>
       <c r="R5" s="10" t="n"/>
       <c r="S5" s="11" t="n">
         <v>1</v>
       </c>
       <c r="T5" s="10" t="n"/>
-      <c r="U5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="12">
-        <f>SUM(L5:U5)</f>
-        <v/>
-      </c>
+      <c r="U5" s="10" t="n"/>
+      <c r="V5" s="10" t="n"/>
+      <c r="W5" s="12">
+        <f>SUM(L5:V5)</f>
+        <v/>
+      </c>
+      <c r="X5" s="13" t="inlineStr"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -1800,19 +1833,15 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -1820,14 +1849,10 @@
       </c>
       <c r="F6" s="7" t="inlineStr"/>
       <c r="G6" s="7" t="inlineStr"/>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H6" s="7" t="inlineStr"/>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -1837,7 +1862,7 @@
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>2 inch damage on membrane seperating bowel in critical area</t>
+          <t>hole in the distal end of the colon</t>
         </is>
       </c>
       <c r="L6" s="10" t="n"/>
@@ -1845,19 +1870,19 @@
       <c r="N6" s="10" t="n"/>
       <c r="O6" s="10" t="n"/>
       <c r="P6" s="10" t="n"/>
-      <c r="Q6" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q6" s="10" t="n"/>
       <c r="R6" s="10" t="n"/>
       <c r="S6" s="11" t="n">
         <v>1</v>
       </c>
       <c r="T6" s="10" t="n"/>
       <c r="U6" s="10" t="n"/>
-      <c r="V6" s="12">
-        <f>SUM(L6:U6)</f>
-        <v/>
-      </c>
+      <c r="V6" s="10" t="n"/>
+      <c r="W6" s="12">
+        <f>SUM(L6:V6)</f>
+        <v/>
+      </c>
+      <c r="X6" s="13" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -1867,19 +1892,15 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr"/>
       <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -1887,14 +1908,10 @@
       </c>
       <c r="F7" s="7" t="inlineStr"/>
       <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -1904,25 +1921,27 @@
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>urethra is cut</t>
+          <t>hole in the distal end of the colon</t>
         </is>
       </c>
       <c r="L7" s="10" t="n"/>
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="10" t="n"/>
       <c r="O7" s="10" t="n"/>
-      <c r="P7" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="P7" s="10" t="n"/>
       <c r="Q7" s="10" t="n"/>
       <c r="R7" s="10" t="n"/>
-      <c r="S7" s="10" t="n"/>
+      <c r="S7" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="T7" s="10" t="n"/>
       <c r="U7" s="10" t="n"/>
-      <c r="V7" s="12">
-        <f>SUM(L7:U7)</f>
-        <v/>
-      </c>
+      <c r="V7" s="10" t="n"/>
+      <c r="W7" s="12">
+        <f>SUM(L7:V7)</f>
+        <v/>
+      </c>
+      <c r="X7" s="13" t="inlineStr"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -1932,19 +1951,15 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -1952,14 +1967,10 @@
       </c>
       <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H8" s="7" t="inlineStr"/>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -1969,25 +1980,29 @@
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>bladder deformed 12 inch deformed attachment</t>
+          <t>hole in the distal end of the urethra and bladder neck separation</t>
         </is>
       </c>
       <c r="L8" s="10" t="n"/>
       <c r="M8" s="10" t="n"/>
       <c r="N8" s="10" t="n"/>
       <c r="O8" s="10" t="n"/>
-      <c r="P8" s="10" t="n"/>
+      <c r="P8" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q8" s="10" t="n"/>
-      <c r="R8" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="R8" s="10" t="n"/>
       <c r="S8" s="10" t="n"/>
       <c r="T8" s="10" t="n"/>
       <c r="U8" s="10" t="n"/>
-      <c r="V8" s="12">
-        <f>SUM(L8:U8)</f>
-        <v/>
-      </c>
+      <c r="V8" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" s="12">
+        <f>SUM(L8:V8)</f>
+        <v/>
+      </c>
+      <c r="X8" s="13" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -1997,19 +2012,15 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
       <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -2017,43 +2028,41 @@
       </c>
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H9" s="7" t="inlineStr"/>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>suspensory ligaments damaged, ureters not embedded</t>
-        </is>
-      </c>
-      <c r="L9" s="11" t="n">
-        <v>1</v>
-      </c>
+          <t>8" hole in the bladder suspencery ligamant. ureter still intact???</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="n"/>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="10" t="n"/>
-      <c r="O9" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="O9" s="10" t="n"/>
       <c r="P9" s="10" t="n"/>
       <c r="Q9" s="10" t="n"/>
       <c r="R9" s="10" t="n"/>
       <c r="S9" s="10" t="n"/>
       <c r="T9" s="10" t="n"/>
       <c r="U9" s="10" t="n"/>
-      <c r="V9" s="12">
-        <f>SUM(L9:U9)</f>
-        <v/>
+      <c r="V9" s="10" t="n"/>
+      <c r="W9" s="12">
+        <f>SUM(L9:V9)</f>
+        <v/>
+      </c>
+      <c r="X9" s="15" t="inlineStr">
+        <is>
+          <t>QUESTIONABLE - pending ME/DE determination (per sheet note). If reclassified Fail -&gt; D4 (suspensory ligament).</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
@@ -2064,19 +2073,15 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -2084,45 +2089,41 @@
       </c>
       <c r="F10" s="7" t="inlineStr"/>
       <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>ureters not embedded, suspensory ligaments damaged, cut urethra</t>
-        </is>
-      </c>
-      <c r="L10" s="11" t="n">
-        <v>1</v>
-      </c>
+          <t>8" hole in the bladder suspencery ligamant. ureter still intact???</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="n"/>
       <c r="M10" s="10" t="n"/>
       <c r="N10" s="10" t="n"/>
-      <c r="O10" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="10" t="n"/>
       <c r="Q10" s="10" t="n"/>
       <c r="R10" s="10" t="n"/>
       <c r="S10" s="10" t="n"/>
       <c r="T10" s="10" t="n"/>
       <c r="U10" s="10" t="n"/>
-      <c r="V10" s="12">
-        <f>SUM(L10:U10)</f>
-        <v/>
+      <c r="V10" s="10" t="n"/>
+      <c r="W10" s="12">
+        <f>SUM(L10:V10)</f>
+        <v/>
+      </c>
+      <c r="X10" s="15" t="inlineStr">
+        <is>
+          <t>QUESTIONABLE - pending ME/DE determination (per sheet note). If reclassified Fail -&gt; D4 (suspensory ligament).</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
@@ -2133,19 +2134,15 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
       <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -2153,47 +2150,41 @@
       </c>
       <c r="F11" s="7" t="inlineStr"/>
       <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H11" s="7" t="inlineStr"/>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>ureters not embedded and cut, suspensory ligaments damaged, cut urethra</t>
-        </is>
-      </c>
-      <c r="L11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="11" t="n">
-        <v>1</v>
-      </c>
+          <t>8" hole in the bladder suspencery ligamant. ureter still intact???</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="n"/>
+      <c r="M11" s="10" t="n"/>
       <c r="N11" s="10" t="n"/>
-      <c r="O11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="O11" s="10" t="n"/>
+      <c r="P11" s="10" t="n"/>
       <c r="Q11" s="10" t="n"/>
       <c r="R11" s="10" t="n"/>
       <c r="S11" s="10" t="n"/>
       <c r="T11" s="10" t="n"/>
       <c r="U11" s="10" t="n"/>
-      <c r="V11" s="12">
-        <f>SUM(L11:U11)</f>
-        <v/>
+      <c r="V11" s="10" t="n"/>
+      <c r="W11" s="12">
+        <f>SUM(L11:V11)</f>
+        <v/>
+      </c>
+      <c r="X11" s="15" t="inlineStr">
+        <is>
+          <t>QUESTIONABLE - pending ME/DE determination (per sheet note). If reclassified Fail -&gt; D4 (suspensory ligament).</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
@@ -2204,19 +2195,15 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
       <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -2224,47 +2211,41 @@
       </c>
       <c r="F12" s="7" t="inlineStr"/>
       <c r="G12" s="7" t="inlineStr"/>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H12" s="7" t="inlineStr"/>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>ureters not embedded, suspensory ligaments damaged, cut urethra, membrane damaged in critical area</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="n">
-        <v>1</v>
-      </c>
+          <t>8" hole in the bladder suspencery ligamant. ureter still intact???</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="n"/>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="10" t="n"/>
-      <c r="O12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="10" t="n"/>
       <c r="R12" s="10" t="n"/>
       <c r="S12" s="10" t="n"/>
       <c r="T12" s="10" t="n"/>
       <c r="U12" s="10" t="n"/>
-      <c r="V12" s="12">
-        <f>SUM(L12:U12)</f>
-        <v/>
+      <c r="V12" s="10" t="n"/>
+      <c r="W12" s="12">
+        <f>SUM(L12:V12)</f>
+        <v/>
+      </c>
+      <c r="X12" s="15" t="inlineStr">
+        <is>
+          <t>QUESTIONABLE - pending ME/DE determination (per sheet note). If reclassified Fail -&gt; D4 (suspensory ligament).</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
@@ -2275,19 +2256,15 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -2295,46 +2272,44 @@
       </c>
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>suspensory ligaments damaged, ureters not embedded</t>
-        </is>
-      </c>
-      <c r="L13" s="11" t="n">
-        <v>1</v>
-      </c>
+          <t>8" hole in the bladder suspencery ligamant. ureter still intact???</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="n"/>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="10" t="n"/>
-      <c r="O13" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="O13" s="10" t="n"/>
       <c r="P13" s="10" t="n"/>
       <c r="Q13" s="10" t="n"/>
       <c r="R13" s="10" t="n"/>
       <c r="S13" s="10" t="n"/>
       <c r="T13" s="10" t="n"/>
       <c r="U13" s="10" t="n"/>
-      <c r="V13" s="12">
-        <f>SUM(L13:U13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+      <c r="V13" s="10" t="n"/>
+      <c r="W13" s="12">
+        <f>SUM(L13:V13)</f>
+        <v/>
+      </c>
+      <c r="X13" s="15" t="inlineStr">
+        <is>
+          <t>QUESTIONABLE - pending ME/DE determination (per sheet note). If reclassified Fail -&gt; D4 (suspensory ligament).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>B010</t>
@@ -2342,19 +2317,15 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
       <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -2362,50 +2333,40 @@
       </c>
       <c r="F14" s="7" t="inlineStr"/>
       <c r="G14" s="7" t="inlineStr"/>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H14" s="7" t="inlineStr"/>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>ureters not embedded, suspensory ligaments damaged, cut urethra, membrane damaged in critical area</t>
-        </is>
-      </c>
-      <c r="L14" s="11" t="n">
-        <v>1</v>
-      </c>
+          <t>no damage found</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="n"/>
       <c r="M14" s="10" t="n"/>
       <c r="N14" s="10" t="n"/>
-      <c r="O14" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="10" t="n"/>
       <c r="R14" s="10" t="n"/>
       <c r="S14" s="10" t="n"/>
       <c r="T14" s="10" t="n"/>
       <c r="U14" s="10" t="n"/>
-      <c r="V14" s="12">
-        <f>SUM(L14:U14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
+      <c r="V14" s="10" t="n"/>
+      <c r="W14" s="12">
+        <f>SUM(L14:V14)</f>
+        <v/>
+      </c>
+      <c r="X14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>B011</t>
@@ -2413,19 +2374,15 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
       <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -2433,31 +2390,25 @@
       </c>
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>left ureter is missing</t>
+          <t>no damage found</t>
         </is>
       </c>
       <c r="L15" s="10" t="n"/>
       <c r="M15" s="10" t="n"/>
-      <c r="N15" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="N15" s="10" t="n"/>
       <c r="O15" s="10" t="n"/>
       <c r="P15" s="10" t="n"/>
       <c r="Q15" s="10" t="n"/>
@@ -2465,10 +2416,12 @@
       <c r="S15" s="10" t="n"/>
       <c r="T15" s="10" t="n"/>
       <c r="U15" s="10" t="n"/>
-      <c r="V15" s="12">
-        <f>SUM(L15:U15)</f>
-        <v/>
-      </c>
+      <c r="V15" s="10" t="n"/>
+      <c r="W15" s="12">
+        <f>SUM(L15:V15)</f>
+        <v/>
+      </c>
+      <c r="X15" s="13" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
@@ -2478,19 +2431,15 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr"/>
       <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -2498,14 +2447,10 @@
       </c>
       <c r="F16" s="7" t="inlineStr"/>
       <c r="G16" s="7" t="inlineStr"/>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H16" s="7" t="inlineStr"/>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -2515,29 +2460,27 @@
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>ureters not embedded, suspensory ligaments damaged, membrane damaged in critical area</t>
-        </is>
-      </c>
-      <c r="L16" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="10" t="n"/>
+          <t>ureter cut off</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="n"/>
+      <c r="M16" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="N16" s="10" t="n"/>
-      <c r="O16" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="O16" s="10" t="n"/>
       <c r="P16" s="10" t="n"/>
-      <c r="Q16" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q16" s="10" t="n"/>
       <c r="R16" s="10" t="n"/>
       <c r="S16" s="10" t="n"/>
       <c r="T16" s="10" t="n"/>
       <c r="U16" s="10" t="n"/>
-      <c r="V16" s="12">
-        <f>SUM(L16:U16)</f>
-        <v/>
-      </c>
+      <c r="V16" s="10" t="n"/>
+      <c r="W16" s="12">
+        <f>SUM(L16:V16)</f>
+        <v/>
+      </c>
+      <c r="X16" s="13" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
@@ -2547,19 +2490,15 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
       <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -2567,14 +2506,10 @@
       </c>
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H17" s="7" t="inlineStr"/>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -2584,17 +2519,13 @@
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>ureters not embedded, suspensory ligaments damaged, membrane damaged in critical area</t>
-        </is>
-      </c>
-      <c r="L17" s="11" t="n">
-        <v>1</v>
-      </c>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="n"/>
       <c r="M17" s="10" t="n"/>
       <c r="N17" s="10" t="n"/>
-      <c r="O17" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="O17" s="10" t="n"/>
       <c r="P17" s="10" t="n"/>
       <c r="Q17" s="11" t="n">
         <v>1</v>
@@ -2603,10 +2534,12 @@
       <c r="S17" s="10" t="n"/>
       <c r="T17" s="10" t="n"/>
       <c r="U17" s="10" t="n"/>
-      <c r="V17" s="12">
-        <f>SUM(L17:U17)</f>
-        <v/>
-      </c>
+      <c r="V17" s="10" t="n"/>
+      <c r="W17" s="12">
+        <f>SUM(L17:V17)</f>
+        <v/>
+      </c>
+      <c r="X17" s="13" t="inlineStr"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
@@ -2616,19 +2549,15 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -2636,14 +2565,10 @@
       </c>
       <c r="F18" s="7" t="inlineStr"/>
       <c r="G18" s="7" t="inlineStr"/>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H18" s="7" t="inlineStr"/>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -2653,27 +2578,27 @@
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>left ureter missing, blood clots</t>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
         </is>
       </c>
       <c r="L18" s="10" t="n"/>
       <c r="M18" s="10" t="n"/>
-      <c r="N18" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="N18" s="10" t="n"/>
       <c r="O18" s="10" t="n"/>
       <c r="P18" s="10" t="n"/>
-      <c r="Q18" s="10" t="n"/>
+      <c r="Q18" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="R18" s="10" t="n"/>
       <c r="S18" s="10" t="n"/>
-      <c r="T18" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="T18" s="10" t="n"/>
       <c r="U18" s="10" t="n"/>
-      <c r="V18" s="12">
-        <f>SUM(L18:U18)</f>
-        <v/>
-      </c>
+      <c r="V18" s="10" t="n"/>
+      <c r="W18" s="12">
+        <f>SUM(L18:V18)</f>
+        <v/>
+      </c>
+      <c r="X18" s="13" t="inlineStr"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -2683,19 +2608,15 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
       <c r="E19" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -2703,14 +2624,10 @@
       </c>
       <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H19" s="7" t="inlineStr"/>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -2720,14 +2637,12 @@
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>right ureter missing, membrane damage in critical area</t>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
         </is>
       </c>
       <c r="L19" s="10" t="n"/>
       <c r="M19" s="10" t="n"/>
-      <c r="N19" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="N19" s="10" t="n"/>
       <c r="O19" s="10" t="n"/>
       <c r="P19" s="10" t="n"/>
       <c r="Q19" s="11" t="n">
@@ -2737,10 +2652,12 @@
       <c r="S19" s="10" t="n"/>
       <c r="T19" s="10" t="n"/>
       <c r="U19" s="10" t="n"/>
-      <c r="V19" s="12">
-        <f>SUM(L19:U19)</f>
-        <v/>
-      </c>
+      <c r="V19" s="10" t="n"/>
+      <c r="W19" s="12">
+        <f>SUM(L19:V19)</f>
+        <v/>
+      </c>
+      <c r="X19" s="13" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
@@ -2750,19 +2667,15 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr"/>
       <c r="E20" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -2770,14 +2683,10 @@
       </c>
       <c r="F20" s="7" t="inlineStr"/>
       <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H20" s="7" t="inlineStr"/>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
@@ -2787,12 +2696,10 @@
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>membrane damage in critical area, ureters not embedded</t>
-        </is>
-      </c>
-      <c r="L20" s="11" t="n">
-        <v>1</v>
-      </c>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="n"/>
       <c r="M20" s="10" t="n"/>
       <c r="N20" s="10" t="n"/>
       <c r="O20" s="10" t="n"/>
@@ -2804,10 +2711,12 @@
       <c r="S20" s="10" t="n"/>
       <c r="T20" s="10" t="n"/>
       <c r="U20" s="10" t="n"/>
-      <c r="V20" s="12">
-        <f>SUM(L20:U20)</f>
-        <v/>
-      </c>
+      <c r="V20" s="10" t="n"/>
+      <c r="W20" s="12">
+        <f>SUM(L20:V20)</f>
+        <v/>
+      </c>
+      <c r="X20" s="13" t="inlineStr"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
@@ -2817,19 +2726,15 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
       <c r="E21" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -2837,14 +2742,10 @@
       </c>
       <c r="F21" s="7" t="inlineStr"/>
       <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H21" s="7" t="inlineStr"/>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -2854,12 +2755,10 @@
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>membrane damage in critical area, ureters not embedded</t>
-        </is>
-      </c>
-      <c r="L21" s="11" t="n">
-        <v>1</v>
-      </c>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="n"/>
       <c r="M21" s="10" t="n"/>
       <c r="N21" s="10" t="n"/>
       <c r="O21" s="10" t="n"/>
@@ -2871,10 +2770,12 @@
       <c r="S21" s="10" t="n"/>
       <c r="T21" s="10" t="n"/>
       <c r="U21" s="10" t="n"/>
-      <c r="V21" s="12">
-        <f>SUM(L21:U21)</f>
-        <v/>
-      </c>
+      <c r="V21" s="10" t="n"/>
+      <c r="W21" s="12">
+        <f>SUM(L21:V21)</f>
+        <v/>
+      </c>
+      <c r="X21" s="13" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
@@ -2884,19 +2785,15 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr"/>
       <c r="E22" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -2904,14 +2801,10 @@
       </c>
       <c r="F22" s="7" t="inlineStr"/>
       <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -2921,15 +2814,11 @@
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>ureter cut, membrane damage in critital area, right ureter not embedded</t>
-        </is>
-      </c>
-      <c r="L22" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" s="11" t="n">
-        <v>1</v>
-      </c>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="n"/>
+      <c r="M22" s="10" t="n"/>
       <c r="N22" s="10" t="n"/>
       <c r="O22" s="10" t="n"/>
       <c r="P22" s="10" t="n"/>
@@ -2940,10 +2829,12 @@
       <c r="S22" s="10" t="n"/>
       <c r="T22" s="10" t="n"/>
       <c r="U22" s="10" t="n"/>
-      <c r="V22" s="12">
-        <f>SUM(L22:U22)</f>
-        <v/>
-      </c>
+      <c r="V22" s="10" t="n"/>
+      <c r="W22" s="12">
+        <f>SUM(L22:V22)</f>
+        <v/>
+      </c>
+      <c r="X22" s="13" t="inlineStr"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
@@ -2953,19 +2844,15 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
       <c r="E23" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -2973,14 +2860,10 @@
       </c>
       <c r="F23" s="7" t="inlineStr"/>
       <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
@@ -2990,16 +2873,14 @@
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>urethra cut, membrnae damage in critial area</t>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
         </is>
       </c>
       <c r="L23" s="10" t="n"/>
       <c r="M23" s="10" t="n"/>
       <c r="N23" s="10" t="n"/>
       <c r="O23" s="10" t="n"/>
-      <c r="P23" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="P23" s="10" t="n"/>
       <c r="Q23" s="11" t="n">
         <v>1</v>
       </c>
@@ -3007,10 +2888,12 @@
       <c r="S23" s="10" t="n"/>
       <c r="T23" s="10" t="n"/>
       <c r="U23" s="10" t="n"/>
-      <c r="V23" s="12">
-        <f>SUM(L23:U23)</f>
-        <v/>
-      </c>
+      <c r="V23" s="10" t="n"/>
+      <c r="W23" s="12">
+        <f>SUM(L23:V23)</f>
+        <v/>
+      </c>
+      <c r="X23" s="13" t="inlineStr"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
@@ -3020,19 +2903,15 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr"/>
       <c r="E24" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -3040,14 +2919,10 @@
       </c>
       <c r="F24" s="7" t="inlineStr"/>
       <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H24" s="7" t="inlineStr"/>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
@@ -3057,7 +2932,7 @@
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>bowel is cut open</t>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
         </is>
       </c>
       <c r="L24" s="10" t="n"/>
@@ -3065,17 +2940,19 @@
       <c r="N24" s="10" t="n"/>
       <c r="O24" s="10" t="n"/>
       <c r="P24" s="10" t="n"/>
-      <c r="Q24" s="10" t="n"/>
+      <c r="Q24" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="R24" s="10" t="n"/>
-      <c r="S24" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="S24" s="10" t="n"/>
       <c r="T24" s="10" t="n"/>
       <c r="U24" s="10" t="n"/>
-      <c r="V24" s="12">
-        <f>SUM(L24:U24)</f>
-        <v/>
-      </c>
+      <c r="V24" s="10" t="n"/>
+      <c r="W24" s="12">
+        <f>SUM(L24:V24)</f>
+        <v/>
+      </c>
+      <c r="X24" s="13" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
@@ -3085,19 +2962,15 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr"/>
       <c r="E25" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -3105,14 +2978,10 @@
       </c>
       <c r="F25" s="7" t="inlineStr"/>
       <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
@@ -3122,16 +2991,14 @@
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>urethra is cut, membrane damage in critical area</t>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
         </is>
       </c>
       <c r="L25" s="10" t="n"/>
       <c r="M25" s="10" t="n"/>
       <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
-      <c r="P25" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="P25" s="10" t="n"/>
       <c r="Q25" s="11" t="n">
         <v>1</v>
       </c>
@@ -3139,10 +3006,12 @@
       <c r="S25" s="10" t="n"/>
       <c r="T25" s="10" t="n"/>
       <c r="U25" s="10" t="n"/>
-      <c r="V25" s="12">
-        <f>SUM(L25:U25)</f>
-        <v/>
-      </c>
+      <c r="V25" s="10" t="n"/>
+      <c r="W25" s="12">
+        <f>SUM(L25:V25)</f>
+        <v/>
+      </c>
+      <c r="X25" s="13" t="inlineStr"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
@@ -3152,19 +3021,15 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr"/>
       <c r="E26" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -3172,14 +3037,10 @@
       </c>
       <c r="F26" s="7" t="inlineStr"/>
       <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H26" s="7" t="inlineStr"/>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -3189,7 +3050,7 @@
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>membrane damage in critical area</t>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
         </is>
       </c>
       <c r="L26" s="10" t="n"/>
@@ -3204,10 +3065,12 @@
       <c r="S26" s="10" t="n"/>
       <c r="T26" s="10" t="n"/>
       <c r="U26" s="10" t="n"/>
-      <c r="V26" s="12">
-        <f>SUM(L26:U26)</f>
-        <v/>
-      </c>
+      <c r="V26" s="10" t="n"/>
+      <c r="W26" s="12">
+        <f>SUM(L26:V26)</f>
+        <v/>
+      </c>
+      <c r="X26" s="13" t="inlineStr"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
@@ -3217,19 +3080,15 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -3237,14 +3096,10 @@
       </c>
       <c r="F27" s="7" t="inlineStr"/>
       <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H27" s="7" t="inlineStr"/>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -3254,7 +3109,7 @@
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>membrane damage in critical area</t>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
         </is>
       </c>
       <c r="L27" s="10" t="n"/>
@@ -3269,10 +3124,12 @@
       <c r="S27" s="10" t="n"/>
       <c r="T27" s="10" t="n"/>
       <c r="U27" s="10" t="n"/>
-      <c r="V27" s="12">
-        <f>SUM(L27:U27)</f>
-        <v/>
-      </c>
+      <c r="V27" s="10" t="n"/>
+      <c r="W27" s="12">
+        <f>SUM(L27:V27)</f>
+        <v/>
+      </c>
+      <c r="X27" s="13" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
@@ -3282,19 +3139,15 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -3302,14 +3155,10 @@
       </c>
       <c r="F28" s="7" t="inlineStr"/>
       <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H28" s="7" t="inlineStr"/>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -3319,7 +3168,7 @@
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>membrane damage in critical area</t>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
         </is>
       </c>
       <c r="L28" s="10" t="n"/>
@@ -3334,10 +3183,12 @@
       <c r="S28" s="10" t="n"/>
       <c r="T28" s="10" t="n"/>
       <c r="U28" s="10" t="n"/>
-      <c r="V28" s="12">
-        <f>SUM(L28:U28)</f>
-        <v/>
-      </c>
+      <c r="V28" s="10" t="n"/>
+      <c r="W28" s="12">
+        <f>SUM(L28:V28)</f>
+        <v/>
+      </c>
+      <c r="X28" s="13" t="inlineStr"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
@@ -3347,19 +3198,15 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr"/>
       <c r="E29" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -3367,14 +3214,10 @@
       </c>
       <c r="F29" s="7" t="inlineStr"/>
       <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H29" s="7" t="inlineStr"/>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
+          <t>Pelvic block</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -3384,7 +3227,7 @@
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>membrane damage in critical area</t>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
         </is>
       </c>
       <c r="L29" s="10" t="n"/>
@@ -3399,12 +3242,14 @@
       <c r="S29" s="10" t="n"/>
       <c r="T29" s="10" t="n"/>
       <c r="U29" s="10" t="n"/>
-      <c r="V29" s="12">
-        <f>SUM(L29:U29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
+      <c r="V29" s="10" t="n"/>
+      <c r="W29" s="12">
+        <f>SUM(L29:V29)</f>
+        <v/>
+      </c>
+      <c r="X29" s="13" t="inlineStr"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
           <t>B026</t>
@@ -3412,19 +3257,15 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr"/>
       <c r="E30" s="7" t="inlineStr">
         <is>
           <t>Martins</t>
@@ -3432,47 +3273,2142 @@
       </c>
       <c r="F30" s="7" t="inlineStr"/>
       <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>12:30 PM - 12:45 PM</t>
-        </is>
-      </c>
+      <c r="H30" s="7" t="inlineStr"/>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>Tiss, porcine, fem, Pelvic block</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K30" s="9" t="inlineStr"/>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
       <c r="L30" s="10" t="n"/>
       <c r="M30" s="10" t="n"/>
       <c r="N30" s="10" t="n"/>
       <c r="O30" s="10" t="n"/>
       <c r="P30" s="10" t="n"/>
-      <c r="Q30" s="10" t="n"/>
+      <c r="Q30" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="R30" s="10" t="n"/>
       <c r="S30" s="10" t="n"/>
       <c r="T30" s="10" t="n"/>
       <c r="U30" s="10" t="n"/>
-      <c r="V30" s="12">
-        <f>SUM(L30:U30)</f>
-        <v/>
-      </c>
+      <c r="V30" s="10" t="n"/>
+      <c r="W30" s="12">
+        <f>SUM(L30:V30)</f>
+        <v/>
+      </c>
+      <c r="X30" s="13" t="inlineStr"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>B027</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr"/>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>rectum seperation</t>
+        </is>
+      </c>
+      <c r="L31" s="10" t="n"/>
+      <c r="M31" s="10" t="n"/>
+      <c r="N31" s="10" t="n"/>
+      <c r="O31" s="10" t="n"/>
+      <c r="P31" s="10" t="n"/>
+      <c r="Q31" s="10" t="n"/>
+      <c r="R31" s="10" t="n"/>
+      <c r="S31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" s="10" t="n"/>
+      <c r="U31" s="10" t="n"/>
+      <c r="V31" s="10" t="n"/>
+      <c r="W31" s="12">
+        <f>SUM(L31:V31)</f>
+        <v/>
+      </c>
+      <c r="X31" s="13" t="inlineStr"/>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>B028</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr"/>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>laceration in urethra</t>
+        </is>
+      </c>
+      <c r="L32" s="10" t="n"/>
+      <c r="M32" s="10" t="n"/>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="10" t="n"/>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="10" t="n"/>
+      <c r="T32" s="10" t="n"/>
+      <c r="U32" s="10" t="n"/>
+      <c r="V32" s="10" t="n"/>
+      <c r="W32" s="12">
+        <f>SUM(L32:V32)</f>
+        <v/>
+      </c>
+      <c r="X32" s="13" t="inlineStr"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>B029</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr"/>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>laceration in urethra</t>
+        </is>
+      </c>
+      <c r="L33" s="10" t="n"/>
+      <c r="M33" s="10" t="n"/>
+      <c r="N33" s="10" t="n"/>
+      <c r="O33" s="10" t="n"/>
+      <c r="P33" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="10" t="n"/>
+      <c r="R33" s="10" t="n"/>
+      <c r="S33" s="10" t="n"/>
+      <c r="T33" s="10" t="n"/>
+      <c r="U33" s="10" t="n"/>
+      <c r="V33" s="10" t="n"/>
+      <c r="W33" s="12">
+        <f>SUM(L33:V33)</f>
+        <v/>
+      </c>
+      <c r="X33" s="13" t="inlineStr"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>B030</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr"/>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>hole in the distal end of the urethra and hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
+      <c r="L34" s="10" t="n"/>
+      <c r="M34" s="10" t="n"/>
+      <c r="N34" s="10" t="n"/>
+      <c r="O34" s="10" t="n"/>
+      <c r="P34" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" s="10" t="n"/>
+      <c r="S34" s="10" t="n"/>
+      <c r="T34" s="10" t="n"/>
+      <c r="U34" s="10" t="n"/>
+      <c r="V34" s="10" t="n"/>
+      <c r="W34" s="12">
+        <f>SUM(L34:V34)</f>
+        <v/>
+      </c>
+      <c r="X34" s="13" t="inlineStr"/>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>B031</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr"/>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>hole in the distal end of the colon passed the template</t>
+        </is>
+      </c>
+      <c r="L35" s="10" t="n"/>
+      <c r="M35" s="10" t="n"/>
+      <c r="N35" s="10" t="n"/>
+      <c r="O35" s="10" t="n"/>
+      <c r="P35" s="10" t="n"/>
+      <c r="Q35" s="10" t="n"/>
+      <c r="R35" s="10" t="n"/>
+      <c r="S35" s="10" t="n"/>
+      <c r="T35" s="10" t="n"/>
+      <c r="U35" s="10" t="n"/>
+      <c r="V35" s="10" t="n"/>
+      <c r="W35" s="12">
+        <f>SUM(L35:V35)</f>
+        <v/>
+      </c>
+      <c r="X35" s="15" t="inlineStr">
+        <is>
+          <t>Colon hole small enough to pass template.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>B032</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>Large hole near right broad ligament and membrane causing seperation of bowel and ureters.</t>
+        </is>
+      </c>
+      <c r="L36" s="10" t="n"/>
+      <c r="M36" s="10" t="n"/>
+      <c r="N36" s="10" t="n"/>
+      <c r="O36" s="10" t="n"/>
+      <c r="P36" s="10" t="n"/>
+      <c r="Q36" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" s="10" t="n"/>
+      <c r="S36" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" s="10" t="n"/>
+      <c r="U36" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" s="10" t="n"/>
+      <c r="W36" s="12">
+        <f>SUM(L36:V36)</f>
+        <v/>
+      </c>
+      <c r="X36" s="13" t="inlineStr"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>B033</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>2 inch damage on membrane seperating bowel in critical area</t>
+        </is>
+      </c>
+      <c r="L37" s="10" t="n"/>
+      <c r="M37" s="10" t="n"/>
+      <c r="N37" s="10" t="n"/>
+      <c r="O37" s="10" t="n"/>
+      <c r="P37" s="10" t="n"/>
+      <c r="Q37" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" s="10" t="n"/>
+      <c r="S37" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" s="10" t="n"/>
+      <c r="U37" s="10" t="n"/>
+      <c r="V37" s="10" t="n"/>
+      <c r="W37" s="12">
+        <f>SUM(L37:V37)</f>
+        <v/>
+      </c>
+      <c r="X37" s="13" t="inlineStr"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>B034</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr"/>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>urethra is cut</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="n"/>
+      <c r="M38" s="10" t="n"/>
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="10" t="n"/>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="10" t="n"/>
+      <c r="T38" s="10" t="n"/>
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="10" t="n"/>
+      <c r="W38" s="12">
+        <f>SUM(L38:V38)</f>
+        <v/>
+      </c>
+      <c r="X38" s="13" t="inlineStr"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>B035</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr"/>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>bladder deformed 12 inch deformed attachment</t>
+        </is>
+      </c>
+      <c r="L39" s="10" t="n"/>
+      <c r="M39" s="10" t="n"/>
+      <c r="N39" s="10" t="n"/>
+      <c r="O39" s="10" t="n"/>
+      <c r="P39" s="10" t="n"/>
+      <c r="Q39" s="10" t="n"/>
+      <c r="R39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" s="10" t="n"/>
+      <c r="T39" s="10" t="n"/>
+      <c r="U39" s="10" t="n"/>
+      <c r="V39" s="10" t="n"/>
+      <c r="W39" s="12">
+        <f>SUM(L39:V39)</f>
+        <v/>
+      </c>
+      <c r="X39" s="13" t="inlineStr"/>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>B036</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr"/>
+      <c r="G40" s="7" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K40" s="9" t="inlineStr">
+        <is>
+          <t>suspensory ligaments damaged, ureters not embedded</t>
+        </is>
+      </c>
+      <c r="L40" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" s="10" t="n"/>
+      <c r="N40" s="10" t="n"/>
+      <c r="O40" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P40" s="10" t="n"/>
+      <c r="Q40" s="10" t="n"/>
+      <c r="R40" s="10" t="n"/>
+      <c r="S40" s="10" t="n"/>
+      <c r="T40" s="10" t="n"/>
+      <c r="U40" s="10" t="n"/>
+      <c r="V40" s="10" t="n"/>
+      <c r="W40" s="12">
+        <f>SUM(L40:V40)</f>
+        <v/>
+      </c>
+      <c r="X40" s="13" t="inlineStr"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>B037</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>ureters not embedded, suspensory ligaments damaged, cut urethra</t>
+        </is>
+      </c>
+      <c r="L41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="10" t="n"/>
+      <c r="N41" s="10" t="n"/>
+      <c r="O41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="10" t="n"/>
+      <c r="R41" s="10" t="n"/>
+      <c r="S41" s="10" t="n"/>
+      <c r="T41" s="10" t="n"/>
+      <c r="U41" s="10" t="n"/>
+      <c r="V41" s="10" t="n"/>
+      <c r="W41" s="12">
+        <f>SUM(L41:V41)</f>
+        <v/>
+      </c>
+      <c r="X41" s="13" t="inlineStr"/>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>B038</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="7" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K42" s="9" t="inlineStr">
+        <is>
+          <t>ureters not embedded and cut, suspensory ligaments damaged, cut urethra</t>
+        </is>
+      </c>
+      <c r="L42" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" s="10" t="n"/>
+      <c r="O42" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="10" t="n"/>
+      <c r="R42" s="10" t="n"/>
+      <c r="S42" s="10" t="n"/>
+      <c r="T42" s="10" t="n"/>
+      <c r="U42" s="10" t="n"/>
+      <c r="V42" s="10" t="n"/>
+      <c r="W42" s="12">
+        <f>SUM(L42:V42)</f>
+        <v/>
+      </c>
+      <c r="X42" s="13" t="inlineStr"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>B039</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr"/>
+      <c r="G43" s="7" t="inlineStr"/>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>ureters not embedded, suspensory ligaments damaged, cut urethra, membrane damaged in critical area</t>
+        </is>
+      </c>
+      <c r="L43" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" s="10" t="n"/>
+      <c r="N43" s="10" t="n"/>
+      <c r="O43" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" s="10" t="n"/>
+      <c r="S43" s="10" t="n"/>
+      <c r="T43" s="10" t="n"/>
+      <c r="U43" s="10" t="n"/>
+      <c r="V43" s="10" t="n"/>
+      <c r="W43" s="12">
+        <f>SUM(L43:V43)</f>
+        <v/>
+      </c>
+      <c r="X43" s="13" t="inlineStr"/>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>B040</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr"/>
+      <c r="G44" s="7" t="inlineStr"/>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K44" s="9" t="inlineStr">
+        <is>
+          <t>suspensory ligaments damaged, ureters not embedded</t>
+        </is>
+      </c>
+      <c r="L44" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" s="10" t="n"/>
+      <c r="N44" s="10" t="n"/>
+      <c r="O44" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" s="10" t="n"/>
+      <c r="Q44" s="10" t="n"/>
+      <c r="R44" s="10" t="n"/>
+      <c r="S44" s="10" t="n"/>
+      <c r="T44" s="10" t="n"/>
+      <c r="U44" s="10" t="n"/>
+      <c r="V44" s="10" t="n"/>
+      <c r="W44" s="12">
+        <f>SUM(L44:V44)</f>
+        <v/>
+      </c>
+      <c r="X44" s="13" t="inlineStr"/>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>B041</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr"/>
+      <c r="G45" s="7" t="inlineStr"/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>ureters not embedded, suspensory ligaments damaged, cut urethra, membrane damaged in critical area</t>
+        </is>
+      </c>
+      <c r="L45" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" s="10" t="n"/>
+      <c r="N45" s="10" t="n"/>
+      <c r="O45" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" s="10" t="n"/>
+      <c r="S45" s="10" t="n"/>
+      <c r="T45" s="10" t="n"/>
+      <c r="U45" s="10" t="n"/>
+      <c r="V45" s="10" t="n"/>
+      <c r="W45" s="12">
+        <f>SUM(L45:V45)</f>
+        <v/>
+      </c>
+      <c r="X45" s="13" t="inlineStr"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>B042</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr"/>
+      <c r="G46" s="7" t="inlineStr"/>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K46" s="9" t="inlineStr">
+        <is>
+          <t>left ureter is missing</t>
+        </is>
+      </c>
+      <c r="L46" s="10" t="n"/>
+      <c r="M46" s="10" t="n"/>
+      <c r="N46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="10" t="n"/>
+      <c r="P46" s="10" t="n"/>
+      <c r="Q46" s="10" t="n"/>
+      <c r="R46" s="10" t="n"/>
+      <c r="S46" s="10" t="n"/>
+      <c r="T46" s="10" t="n"/>
+      <c r="U46" s="10" t="n"/>
+      <c r="V46" s="10" t="n"/>
+      <c r="W46" s="12">
+        <f>SUM(L46:V46)</f>
+        <v/>
+      </c>
+      <c r="X46" s="13" t="inlineStr"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>B043</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr"/>
+      <c r="G47" s="7" t="inlineStr"/>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K47" s="9" t="inlineStr">
+        <is>
+          <t>ureters not embedded, suspensory ligaments damaged, membrane damaged in critical area</t>
+        </is>
+      </c>
+      <c r="L47" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" s="10" t="n"/>
+      <c r="N47" s="10" t="n"/>
+      <c r="O47" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" s="10" t="n"/>
+      <c r="Q47" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" s="10" t="n"/>
+      <c r="S47" s="10" t="n"/>
+      <c r="T47" s="10" t="n"/>
+      <c r="U47" s="10" t="n"/>
+      <c r="V47" s="10" t="n"/>
+      <c r="W47" s="12">
+        <f>SUM(L47:V47)</f>
+        <v/>
+      </c>
+      <c r="X47" s="13" t="inlineStr"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>B044</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr"/>
+      <c r="G48" s="7" t="inlineStr"/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K48" s="9" t="inlineStr">
+        <is>
+          <t>ureters not embedded, suspensory ligaments damaged, membrane damaged in critical area</t>
+        </is>
+      </c>
+      <c r="L48" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" s="10" t="n"/>
+      <c r="N48" s="10" t="n"/>
+      <c r="O48" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" s="10" t="n"/>
+      <c r="Q48" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" s="10" t="n"/>
+      <c r="S48" s="10" t="n"/>
+      <c r="T48" s="10" t="n"/>
+      <c r="U48" s="10" t="n"/>
+      <c r="V48" s="10" t="n"/>
+      <c r="W48" s="12">
+        <f>SUM(L48:V48)</f>
+        <v/>
+      </c>
+      <c r="X48" s="13" t="inlineStr"/>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>B045</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr"/>
+      <c r="G49" s="7" t="inlineStr"/>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>left ureter missing, blood clots</t>
+        </is>
+      </c>
+      <c r="L49" s="10" t="n"/>
+      <c r="M49" s="10" t="n"/>
+      <c r="N49" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" s="10" t="n"/>
+      <c r="P49" s="10" t="n"/>
+      <c r="Q49" s="10" t="n"/>
+      <c r="R49" s="10" t="n"/>
+      <c r="S49" s="10" t="n"/>
+      <c r="T49" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" s="10" t="n"/>
+      <c r="V49" s="10" t="n"/>
+      <c r="W49" s="12">
+        <f>SUM(L49:V49)</f>
+        <v/>
+      </c>
+      <c r="X49" s="13" t="inlineStr"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>B046</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr"/>
+      <c r="G50" s="7" t="inlineStr"/>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K50" s="9" t="inlineStr">
+        <is>
+          <t>right ureter missing, membrane damage in critical area</t>
+        </is>
+      </c>
+      <c r="L50" s="10" t="n"/>
+      <c r="M50" s="10" t="n"/>
+      <c r="N50" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" s="10" t="n"/>
+      <c r="P50" s="10" t="n"/>
+      <c r="Q50" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" s="10" t="n"/>
+      <c r="S50" s="10" t="n"/>
+      <c r="T50" s="10" t="n"/>
+      <c r="U50" s="10" t="n"/>
+      <c r="V50" s="10" t="n"/>
+      <c r="W50" s="12">
+        <f>SUM(L50:V50)</f>
+        <v/>
+      </c>
+      <c r="X50" s="13" t="inlineStr"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>B047</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr"/>
+      <c r="G51" s="7" t="inlineStr"/>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>membrane damage in critical area, ureters not embedded</t>
+        </is>
+      </c>
+      <c r="L51" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" s="10" t="n"/>
+      <c r="N51" s="10" t="n"/>
+      <c r="O51" s="10" t="n"/>
+      <c r="P51" s="10" t="n"/>
+      <c r="Q51" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="10" t="n"/>
+      <c r="T51" s="10" t="n"/>
+      <c r="U51" s="10" t="n"/>
+      <c r="V51" s="10" t="n"/>
+      <c r="W51" s="12">
+        <f>SUM(L51:V51)</f>
+        <v/>
+      </c>
+      <c r="X51" s="13" t="inlineStr"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>B048</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr"/>
+      <c r="G52" s="7" t="inlineStr"/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J52" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K52" s="9" t="inlineStr">
+        <is>
+          <t>membrane damage in critical area, ureters not embedded</t>
+        </is>
+      </c>
+      <c r="L52" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" s="10" t="n"/>
+      <c r="N52" s="10" t="n"/>
+      <c r="O52" s="10" t="n"/>
+      <c r="P52" s="10" t="n"/>
+      <c r="Q52" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="10" t="n"/>
+      <c r="T52" s="10" t="n"/>
+      <c r="U52" s="10" t="n"/>
+      <c r="V52" s="10" t="n"/>
+      <c r="W52" s="12">
+        <f>SUM(L52:V52)</f>
+        <v/>
+      </c>
+      <c r="X52" s="13" t="inlineStr"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>B049</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr"/>
+      <c r="G53" s="7" t="inlineStr"/>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J53" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>ureter cut, membrane damage in critital area, right ureter not embedded</t>
+        </is>
+      </c>
+      <c r="L53" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" s="10" t="n"/>
+      <c r="O53" s="10" t="n"/>
+      <c r="P53" s="10" t="n"/>
+      <c r="Q53" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R53" s="10" t="n"/>
+      <c r="S53" s="10" t="n"/>
+      <c r="T53" s="10" t="n"/>
+      <c r="U53" s="10" t="n"/>
+      <c r="V53" s="10" t="n"/>
+      <c r="W53" s="12">
+        <f>SUM(L53:V53)</f>
+        <v/>
+      </c>
+      <c r="X53" s="13" t="inlineStr"/>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>B050</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr"/>
+      <c r="G54" s="7" t="inlineStr"/>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>urethra cut, membrnae damage in critial area</t>
+        </is>
+      </c>
+      <c r="L54" s="10" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="10" t="n"/>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
+      <c r="W54" s="12">
+        <f>SUM(L54:V54)</f>
+        <v/>
+      </c>
+      <c r="X54" s="13" t="inlineStr"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>B051</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr"/>
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>bowel is cut open</t>
+        </is>
+      </c>
+      <c r="L55" s="10" t="n"/>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="10" t="n"/>
+      <c r="O55" s="10" t="n"/>
+      <c r="P55" s="10" t="n"/>
+      <c r="Q55" s="10" t="n"/>
+      <c r="R55" s="10" t="n"/>
+      <c r="S55" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" s="10" t="n"/>
+      <c r="U55" s="10" t="n"/>
+      <c r="V55" s="10" t="n"/>
+      <c r="W55" s="12">
+        <f>SUM(L55:V55)</f>
+        <v/>
+      </c>
+      <c r="X55" s="13" t="inlineStr"/>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>B052</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr"/>
+      <c r="G56" s="7" t="inlineStr"/>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K56" s="9" t="inlineStr">
+        <is>
+          <t>urethra is cut, membrane damage in critical area</t>
+        </is>
+      </c>
+      <c r="L56" s="10" t="n"/>
+      <c r="M56" s="10" t="n"/>
+      <c r="N56" s="10" t="n"/>
+      <c r="O56" s="10" t="n"/>
+      <c r="P56" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" s="10" t="n"/>
+      <c r="S56" s="10" t="n"/>
+      <c r="T56" s="10" t="n"/>
+      <c r="U56" s="10" t="n"/>
+      <c r="V56" s="10" t="n"/>
+      <c r="W56" s="12">
+        <f>SUM(L56:V56)</f>
+        <v/>
+      </c>
+      <c r="X56" s="13" t="inlineStr"/>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>B053</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr"/>
+      <c r="G57" s="7" t="inlineStr"/>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K57" s="9" t="inlineStr">
+        <is>
+          <t>membrane damage in critical area</t>
+        </is>
+      </c>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="12">
+        <f>SUM(L57:V57)</f>
+        <v/>
+      </c>
+      <c r="X57" s="13" t="inlineStr"/>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>B054</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr"/>
+      <c r="G58" s="7" t="inlineStr"/>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K58" s="9" t="inlineStr">
+        <is>
+          <t>membrane damage in critical area</t>
+        </is>
+      </c>
+      <c r="L58" s="10" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="10" t="n"/>
+      <c r="Q58" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="10" t="n"/>
+      <c r="T58" s="10" t="n"/>
+      <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
+      <c r="W58" s="12">
+        <f>SUM(L58:V58)</f>
+        <v/>
+      </c>
+      <c r="X58" s="13" t="inlineStr"/>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>B055</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr"/>
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J59" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>membrane damage in critical area</t>
+        </is>
+      </c>
+      <c r="L59" s="10" t="n"/>
+      <c r="M59" s="10" t="n"/>
+      <c r="N59" s="10" t="n"/>
+      <c r="O59" s="10" t="n"/>
+      <c r="P59" s="10" t="n"/>
+      <c r="Q59" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="10" t="n"/>
+      <c r="T59" s="10" t="n"/>
+      <c r="U59" s="10" t="n"/>
+      <c r="V59" s="10" t="n"/>
+      <c r="W59" s="12">
+        <f>SUM(L59:V59)</f>
+        <v/>
+      </c>
+      <c r="X59" s="13" t="inlineStr"/>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>B056</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>membrane damage in critical area</t>
+        </is>
+      </c>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="10" t="n"/>
+      <c r="Q60" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="12">
+        <f>SUM(L60:V60)</f>
+        <v/>
+      </c>
+      <c r="X60" s="13" t="inlineStr"/>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>B057</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr"/>
+      <c r="G61" s="7" t="inlineStr"/>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>12:30 PM - 12:45 PM</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J61" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="inlineStr"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="10" t="n"/>
+      <c r="Q61" s="10" t="n"/>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
+      <c r="U61" s="10" t="n"/>
+      <c r="V61" s="10" t="n"/>
+      <c r="W61" s="12">
+        <f>SUM(L61:V61)</f>
+        <v/>
+      </c>
+      <c r="X61" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:V2"/>
-    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="A1:X1"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="J5:J405" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail"</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:U405" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:V405" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3486,12 +5422,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -3511,7 +5447,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The controlled vocabulary. Every scrap reason must map to a code here. This is where a defect is traced back to the supplier's process.</t>
+          <t>The controlled vocabulary. Every scrap reason maps to a code here — the point where a defect is traced back to the supplier's process.</t>
         </is>
       </c>
     </row>
@@ -3568,7 +5504,7 @@
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
@@ -3583,7 +5519,7 @@
           <t>Ureter(s) dislodged/stripped from the surrounding pelvic fat &amp; fascia; no longer seated in tissue.</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -3613,10 +5549,10 @@
           <t>Standardize gut-pull technique &amp; pull-force; reduce stripping of perirenal fat; gentler drop to pit.</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr"/>
+      <c r="J5" s="18" t="inlineStr"/>
     </row>
     <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
@@ -3628,10 +5564,10 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Ureter partially or fully transected (sharp cut edge).</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
+          <t>Ureter partially or fully transected / cut off (sharp cut edge).</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -3661,10 +5597,10 @@
           <t>Retrain knife path around pelvic organs; verify saw alignment through symphysis.</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr"/>
+      <c r="J6" s="18" t="inlineStr"/>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
@@ -3679,7 +5615,7 @@
           <t>One ureter (left or right) absent from the block.</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -3709,10 +5645,10 @@
           <t>Tighten bung-dropping cut boundary; audit pit collection for detached tissue.</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr"/>
+      <c r="J7" s="18" t="inlineStr"/>
     </row>
     <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
@@ -3724,10 +5660,10 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Suspensory ligament(s) of the pelvic block torn/frayed.</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
+          <t>Suspensory ligament(s) torn/frayed or holed (incl. bladder suspensory ligament).</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -3757,25 +5693,25 @@
           <t>Control pull-force &amp; angle on gut set removal; handle block by support surface, not by ligaments.</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr"/>
+      <c r="J8" s="18" t="inlineStr"/>
     </row>
     <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Urethra cut</t>
+          <t>Urethra breach (cut / laceration / hole)</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Urethra transected (sharp cut).</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
+          <t>Urethra transected, lacerated or perforated (incl. hole in distal urethra).</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -3797,7 +5733,7 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>Splitting saw off-center through pelvis, or bung-drop cut catches urethra.</t>
+          <t>Splitting saw off-center through pelvis, or bung-drop cut catches/perforates urethra.</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -3805,10 +5741,10 @@
           <t>Center pelvic split on symphysis; calibrate/align splitting saw; slow through pelvic zone.</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr"/>
+      <c r="J9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
@@ -3820,7 +5756,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Hole/tear in the membrane separating bowel from the pelvic organs, in the critical (functional) zone.</t>
+          <t>Hole/tear in the mesentery membrane separating bowel from pelvic organs, in the critical zone (&gt;1.5").</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -3853,10 +5789,10 @@
           <t>Retrain evisceration knife depth &amp; path; slow line in pelvic zone; blunt-dissect where possible.</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr"/>
+      <c r="J10" s="18" t="inlineStr"/>
     </row>
     <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
@@ -3871,7 +5807,7 @@
           <t>Bladder misshapen or attachment distorted.</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -3901,22 +5837,22 @@
           <t>Manage lairage/feed-water timing to reduce bladder fill; avoid compressing block.</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr"/>
+      <c r="J11" s="18" t="inlineStr"/>
     </row>
     <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>D8</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Bowel cut / opened / separated</t>
+          <t>Bowel / colon / rectum breach</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Bowel integrity breached (cut open or separated from block).  FOOD-SAFETY / contamination risk.</t>
+          <t>Bowel integrity breached - cut, hole, or separation of colon/rectum. FOOD-SAFETY / contamination risk.</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -3941,7 +5877,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>Knife slip or aggressive bung separation opens/severs bowel.</t>
+          <t>Knife slip or aggressive bung separation opens/severs colon or rectum.</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -3949,10 +5885,10 @@
           <t>Reinforce bung-bagging/tie-off; retrain knife path; treat as contamination CCP at supplier.</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr"/>
+      <c r="J12" s="18" t="inlineStr"/>
     </row>
     <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>D9</t>
         </is>
@@ -3967,7 +5903,7 @@
           <t>Retained blood clots in the tissue block.</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -3997,10 +5933,10 @@
           <t>Verify stick placement &amp; bleed-out time; check stun-to-stick interval.</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr"/>
+      <c r="J13" s="18" t="inlineStr"/>
     </row>
     <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>D10</t>
         </is>
@@ -4015,7 +5951,7 @@
           <t>Large hole/tear in the broad ligament.</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -4045,7 +5981,55 @@
           <t>Control pull-force; retrain knife path near broad ligament.</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr"/>
+      <c r="J14" s="18" t="inlineStr"/>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>D11</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Bladder neck separation</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Bladder detached/separated at the neck (bladder-urethra junction at the pelvic floor).</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Carcass splitting saw / pelvic outlet cut</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>S4 Carcass splitting</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Machine / Method</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>Saw path or traction at the pelvic floor separates the bladder neck from the urethra.</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Center pelvic split; protect bladder neck at the pelvic outlet; control traction.</t>
+        </is>
+      </c>
+      <c r="J15" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4062,14 +6046,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4083,14 +6067,14 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Counts pull live from the Inspection Log. Fix the 'vital few' (cumulative line to ~80%) first. Re-sort high-&gt;low if ranking changes.</t>
+          <t>Counts pull live from the Inspection Log (all batches). Fix the 'vital few' (cumulative line to ~80%) first. Re-sort high-&gt;low if ranking changes.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>A.  DEFECT PARETO  (by occurrence across all inspected blocks)</t>
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>A.  DEFECT PARETO  (by occurrence across all inspected blocks, all batches)</t>
         </is>
       </c>
     </row>
@@ -4125,7 +6109,7 @@
           <t>Cumulative %</t>
         </is>
       </c>
-      <c r="M5" s="19" t="n"/>
+      <c r="M5" s="21" t="n"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>80% target</t>
@@ -4133,28 +6117,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="A6" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>Membrane damage in critical area</t>
         </is>
       </c>
       <c r="D6" s="12">
-        <f>SUM('Inspection Log'!Q5:Q430)</f>
-        <v/>
-      </c>
-      <c r="E6" s="23">
-        <f>D6/SUM('Inspection Log'!L5:U430)</f>
-        <v/>
-      </c>
-      <c r="F6" s="23">
+        <f>SUM('Inspection Log'!Q5:Q461)</f>
+        <v/>
+      </c>
+      <c r="E6" s="25">
+        <f>D6/SUM('Inspection Log'!L5:V461)</f>
+        <v/>
+      </c>
+      <c r="F6" s="25">
         <f>E6</f>
         <v/>
       </c>
@@ -4168,28 +6152,28 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="n">
+      <c r="A7" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>Ureters not embedded</t>
         </is>
       </c>
       <c r="D7" s="12">
-        <f>SUM('Inspection Log'!L5:L430)</f>
-        <v/>
-      </c>
-      <c r="E7" s="23">
-        <f>D7/SUM('Inspection Log'!L5:U430)</f>
-        <v/>
-      </c>
-      <c r="F7" s="23">
+        <f>SUM('Inspection Log'!L5:L461)</f>
+        <v/>
+      </c>
+      <c r="E7" s="25">
+        <f>D7/SUM('Inspection Log'!L5:V461)</f>
+        <v/>
+      </c>
+      <c r="F7" s="25">
         <f>F6+E7</f>
         <v/>
       </c>
@@ -4203,34 +6187,34 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>D4</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>Suspensory ligaments damaged</t>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>Urethra breach (cut / laceration / hole)</t>
         </is>
       </c>
       <c r="D8" s="12">
-        <f>SUM('Inspection Log'!O5:O430)</f>
-        <v/>
-      </c>
-      <c r="E8" s="23">
-        <f>D8/SUM('Inspection Log'!L5:U430)</f>
-        <v/>
-      </c>
-      <c r="F8" s="23">
+        <f>SUM('Inspection Log'!P5:P461)</f>
+        <v/>
+      </c>
+      <c r="E8" s="25">
+        <f>D8/SUM('Inspection Log'!L5:V461)</f>
+        <v/>
+      </c>
+      <c r="F8" s="25">
         <f>F7+E8</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>D4 · Susp. ligament</t>
+          <t>D5 · Urethra breach</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -4238,34 +6222,34 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="n">
+      <c r="A9" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>D5</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>Urethra cut</t>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>Suspensory ligaments damaged</t>
         </is>
       </c>
       <c r="D9" s="12">
-        <f>SUM('Inspection Log'!P5:P430)</f>
-        <v/>
-      </c>
-      <c r="E9" s="23">
-        <f>D9/SUM('Inspection Log'!L5:U430)</f>
-        <v/>
-      </c>
-      <c r="F9" s="23">
+        <f>SUM('Inspection Log'!O5:O461)</f>
+        <v/>
+      </c>
+      <c r="E9" s="25">
+        <f>D9/SUM('Inspection Log'!L5:V461)</f>
+        <v/>
+      </c>
+      <c r="F9" s="25">
         <f>F8+E9</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>D5 · Urethra cut</t>
+          <t>D4 · Susp. ligament</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -4273,34 +6257,34 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>Ureter missing</t>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Bowel / colon / rectum breach</t>
         </is>
       </c>
       <c r="D10" s="12">
-        <f>SUM('Inspection Log'!N5:N430)</f>
-        <v/>
-      </c>
-      <c r="E10" s="23">
-        <f>D10/SUM('Inspection Log'!L5:U430)</f>
-        <v/>
-      </c>
-      <c r="F10" s="23">
+        <f>SUM('Inspection Log'!S5:S461)</f>
+        <v/>
+      </c>
+      <c r="E10" s="25">
+        <f>D10/SUM('Inspection Log'!L5:V461)</f>
+        <v/>
+      </c>
+      <c r="F10" s="25">
         <f>F9+E10</f>
         <v/>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>D3 · Ureter missing</t>
+          <t>D8 · Bowel/colon</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -4308,34 +6292,34 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="n">
+      <c r="A11" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>D8</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>Bowel cut / opened / separated</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Ureter cut / severed</t>
         </is>
       </c>
       <c r="D11" s="12">
-        <f>SUM('Inspection Log'!S5:S430)</f>
-        <v/>
-      </c>
-      <c r="E11" s="23">
-        <f>D11/SUM('Inspection Log'!L5:U430)</f>
-        <v/>
-      </c>
-      <c r="F11" s="23">
+        <f>SUM('Inspection Log'!M5:M461)</f>
+        <v/>
+      </c>
+      <c r="E11" s="25">
+        <f>D11/SUM('Inspection Log'!L5:V461)</f>
+        <v/>
+      </c>
+      <c r="F11" s="25">
         <f>F10+E11</f>
         <v/>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>D8 · Bowel cut</t>
+          <t>D2 · Ureter cut</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -4343,34 +6327,34 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>Ureter cut / severed</t>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Ureter missing</t>
         </is>
       </c>
       <c r="D12" s="12">
-        <f>SUM('Inspection Log'!M5:M430)</f>
-        <v/>
-      </c>
-      <c r="E12" s="23">
-        <f>D12/SUM('Inspection Log'!L5:U430)</f>
-        <v/>
-      </c>
-      <c r="F12" s="23">
+        <f>SUM('Inspection Log'!N5:N461)</f>
+        <v/>
+      </c>
+      <c r="E12" s="25">
+        <f>D12/SUM('Inspection Log'!L5:V461)</f>
+        <v/>
+      </c>
+      <c r="F12" s="25">
         <f>F11+E12</f>
         <v/>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>D2 · Ureter cut</t>
+          <t>D3 · Ureter missing</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -4378,28 +6362,28 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="n">
+      <c r="A13" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>Bladder deformed / deformed attachment</t>
         </is>
       </c>
       <c r="D13" s="12">
-        <f>SUM('Inspection Log'!R5:R430)</f>
-        <v/>
-      </c>
-      <c r="E13" s="23">
-        <f>D13/SUM('Inspection Log'!L5:U430)</f>
-        <v/>
-      </c>
-      <c r="F13" s="23">
+        <f>SUM('Inspection Log'!R5:R461)</f>
+        <v/>
+      </c>
+      <c r="E13" s="25">
+        <f>D13/SUM('Inspection Log'!L5:V461)</f>
+        <v/>
+      </c>
+      <c r="F13" s="25">
         <f>F12+E13</f>
         <v/>
       </c>
@@ -4413,28 +6397,28 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>D9</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>Blood clots</t>
         </is>
       </c>
       <c r="D14" s="12">
-        <f>SUM('Inspection Log'!T5:T430)</f>
-        <v/>
-      </c>
-      <c r="E14" s="23">
-        <f>D14/SUM('Inspection Log'!L5:U430)</f>
-        <v/>
-      </c>
-      <c r="F14" s="23">
+        <f>SUM('Inspection Log'!T5:T461)</f>
+        <v/>
+      </c>
+      <c r="E14" s="25">
+        <f>D14/SUM('Inspection Log'!L5:V461)</f>
+        <v/>
+      </c>
+      <c r="F14" s="25">
         <f>F13+E14</f>
         <v/>
       </c>
@@ -4448,28 +6432,28 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="n">
+      <c r="A15" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>D10</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>Broad ligament hole / tear</t>
         </is>
       </c>
       <c r="D15" s="12">
-        <f>SUM('Inspection Log'!U5:U430)</f>
-        <v/>
-      </c>
-      <c r="E15" s="23">
-        <f>D15/SUM('Inspection Log'!L5:U430)</f>
-        <v/>
-      </c>
-      <c r="F15" s="23">
+        <f>SUM('Inspection Log'!U5:U461)</f>
+        <v/>
+      </c>
+      <c r="E15" s="25">
+        <f>D15/SUM('Inspection Log'!L5:V461)</f>
+        <v/>
+      </c>
+      <c r="F15" s="25">
         <f>F14+E15</f>
         <v/>
       </c>
@@ -4483,177 +6467,212 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="n"/>
-      <c r="B16" s="25" t="n"/>
+      <c r="A16" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>D11</t>
+        </is>
+      </c>
       <c r="C16" s="26" t="inlineStr">
         <is>
+          <t>Bladder neck separation</t>
+        </is>
+      </c>
+      <c r="D16" s="12">
+        <f>SUM('Inspection Log'!V5:V461)</f>
+        <v/>
+      </c>
+      <c r="E16" s="25">
+        <f>D16/SUM('Inspection Log'!L5:V461)</f>
+        <v/>
+      </c>
+      <c r="F16" s="25">
+        <f>F15+E16</f>
+        <v/>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>D11 · Bladder neck sep.</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="n"/>
+      <c r="B17" s="27" t="n"/>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D16" s="27">
-        <f>SUM(D6:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="28">
-        <f>D16/SUM('Inspection Log'!L5:U430)</f>
-        <v/>
-      </c>
-      <c r="F16" s="25" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="D17" s="29">
+        <f>SUM(D6:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="30">
+        <f>D17/SUM('Inspection Log'!L5:V461)</f>
+        <v/>
+      </c>
+      <c r="F17" s="27" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>B.  ROLLUP BY SUPPLIER STATION  (which station to fix first)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Station</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Station Name</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Defect Count</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>% of Total</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Defect Codes</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="B21" s="30" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>Evisceration</t>
         </is>
       </c>
-      <c r="C21" s="31">
-        <f>SUM('Inspection Log'!L5:L430)+SUM('Inspection Log'!M5:M430)+SUM('Inspection Log'!O5:O430)+SUM('Inspection Log'!Q5:Q430)+SUM('Inspection Log'!S5:S430)+SUM('Inspection Log'!U5:U430)</f>
-        <v/>
-      </c>
-      <c r="D21" s="32">
-        <f>C21/SUM('Inspection Log'!L5:U430)</f>
-        <v/>
-      </c>
-      <c r="E21" s="30" t="inlineStr">
+      <c r="C22" s="33">
+        <f>SUM('Inspection Log'!L5:L461)+SUM('Inspection Log'!M5:M461)+SUM('Inspection Log'!O5:O461)+SUM('Inspection Log'!Q5:Q461)+SUM('Inspection Log'!S5:S461)+SUM('Inspection Log'!U5:U461)</f>
+        <v/>
+      </c>
+      <c r="D22" s="34">
+        <f>C22/SUM('Inspection Log'!L5:V461)</f>
+        <v/>
+      </c>
+      <c r="E22" s="32" t="inlineStr">
         <is>
           <t>D1, D2, D4, D6, D8, D10</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="21" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>Carcass splitting</t>
         </is>
       </c>
-      <c r="C22" s="12">
-        <f>SUM('Inspection Log'!P5:P430)</f>
-        <v/>
-      </c>
-      <c r="D22" s="23">
-        <f>C22/SUM('Inspection Log'!L5:U430)</f>
-        <v/>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
-        <is>
-          <t>D5</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="C23" s="12">
+        <f>SUM('Inspection Log'!P5:P461)+SUM('Inspection Log'!V5:V461)</f>
+        <v/>
+      </c>
+      <c r="D23" s="25">
+        <f>C23/SUM('Inspection Log'!L5:V461)</f>
+        <v/>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>D5, D11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Bung dropping</t>
         </is>
       </c>
-      <c r="C23" s="12">
-        <f>SUM('Inspection Log'!N5:N430)</f>
-        <v/>
-      </c>
-      <c r="D23" s="23">
-        <f>C23/SUM('Inspection Log'!L5:U430)</f>
-        <v/>
-      </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="C24" s="12">
+        <f>SUM('Inspection Log'!N5:N461)</f>
+        <v/>
+      </c>
+      <c r="D24" s="25">
+        <f>C24/SUM('Inspection Log'!L5:V461)</f>
+        <v/>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Live / physiology</t>
         </is>
       </c>
-      <c r="C24" s="12">
-        <f>SUM('Inspection Log'!R5:R430)</f>
-        <v/>
-      </c>
-      <c r="D24" s="23">
-        <f>C24/SUM('Inspection Log'!L5:U430)</f>
-        <v/>
-      </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="C25" s="12">
+        <f>SUM('Inspection Log'!R5:R461)</f>
+        <v/>
+      </c>
+      <c r="D25" s="25">
+        <f>C25/SUM('Inspection Log'!L5:V461)</f>
+        <v/>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Sticking / Bleeding</t>
         </is>
       </c>
-      <c r="C25" s="12">
-        <f>SUM('Inspection Log'!T5:T430)</f>
-        <v/>
-      </c>
-      <c r="D25" s="23">
-        <f>C25/SUM('Inspection Log'!L5:U430)</f>
-        <v/>
-      </c>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="C26" s="12">
+        <f>SUM('Inspection Log'!T5:T461)</f>
+        <v/>
+      </c>
+      <c r="D26" s="25">
+        <f>C26/SUM('Inspection Log'!L5:V461)</f>
+        <v/>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
         <is>
           <t>D9</t>
         </is>
@@ -4661,7 +6680,7 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
@@ -4677,11 +6696,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -4704,7 +6723,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Seeded with a starting hypothesis chain for the vital-few defects. Drive each chain to a true root cause with the supplier, then log the countermeasure &amp; lesson.</t>
+          <t>Seeded with a starting hypothesis chain for the vital-few defects. Drive each to a true root cause with the supplier, then log the countermeasure &amp; lesson.</t>
         </is>
       </c>
     </row>
@@ -4771,302 +6790,316 @@
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>Membrane damage in critical area</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
-        <is>
-          <t>Membrane torn/holed in critical area</t>
-        </is>
-      </c>
-      <c r="D5" s="34" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Membrane torn/holed in critical area (&gt;1.5")</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Knife path too deep / tensile tear during gut pull</t>
         </is>
       </c>
-      <c r="E5" s="34" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Evisceration technique not standardized for pelvic zone</t>
         </is>
       </c>
-      <c r="F5" s="34" t="inlineStr">
-        <is>
-          <t>No defined knife depth/path SOP + line speed pressure</t>
-        </is>
-      </c>
-      <c r="G5" s="35" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>No defined knife depth/path SOP + line-speed pressure</t>
+        </is>
+      </c>
+      <c r="G5" s="36" t="inlineStr">
         <is>
           <t>(confirm w/ supplier) training + line-speed control gap</t>
         </is>
       </c>
-      <c r="H5" s="36" t="inlineStr">
+      <c r="H5" s="37" t="inlineStr">
         <is>
           <t>Retrain knife depth &amp; path in pelvic zone; blunt-dissect; slow line through pelvic cut</t>
         </is>
       </c>
-      <c r="I5" s="37" t="inlineStr">
+      <c r="I5" s="38" t="inlineStr">
         <is>
           <t>SH Martins - Evisceration lead</t>
         </is>
       </c>
-      <c r="J5" s="37" t="inlineStr"/>
-      <c r="K5" s="38" t="inlineStr">
+      <c r="J5" s="38" t="inlineStr"/>
+      <c r="K5" s="39" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L5" s="39" t="inlineStr"/>
+      <c r="L5" s="40" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Ureters not embedded</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Ureters not embedded in tissue</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Fascia/perirenal fat stripped away from ureter</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Excessive pull force / over-trim during gut set removal</t>
         </is>
       </c>
-      <c r="F6" s="34" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>Pull technique &amp; trim spec not controlled</t>
         </is>
       </c>
-      <c r="G6" s="35" t="inlineStr">
+      <c r="G6" s="36" t="inlineStr">
         <is>
           <t>(confirm) handling standard missing</t>
         </is>
       </c>
-      <c r="H6" s="36" t="inlineStr">
+      <c r="H6" s="37" t="inlineStr">
         <is>
           <t>Standardize pull-force &amp; angle; limit fat stripping; gentler pit drop</t>
         </is>
       </c>
-      <c r="I6" s="37" t="inlineStr">
+      <c r="I6" s="38" t="inlineStr">
         <is>
           <t>SH Martins - Evisceration lead</t>
         </is>
       </c>
-      <c r="J6" s="37" t="inlineStr"/>
-      <c r="K6" s="38" t="inlineStr">
+      <c r="J6" s="38" t="inlineStr"/>
+      <c r="K6" s="39" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L6" s="39" t="inlineStr"/>
+      <c r="L6" s="40" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Urethra breach (cut / laceration / hole)</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Urethra cut / laceration / hole</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Sharp transection or perforation through pelvic zone</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Splitting saw off-center / bung-drop cut catches urethra</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Saw alignment &amp; pelvic-split centering not verified</t>
+        </is>
+      </c>
+      <c r="G7" s="36" t="inlineStr">
+        <is>
+          <t>(confirm) saw calibration + technique gap</t>
+        </is>
+      </c>
+      <c r="H7" s="37" t="inlineStr">
+        <is>
+          <t>Center split on symphysis; calibrate/align saw; slow through pelvic zone</t>
+        </is>
+      </c>
+      <c r="I7" s="38" t="inlineStr">
+        <is>
+          <t>SH Martins - Splitting lead</t>
+        </is>
+      </c>
+      <c r="J7" s="38" t="inlineStr"/>
+      <c r="K7" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L7" s="40" t="inlineStr"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Suspensory ligaments damaged</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
-        <is>
-          <t>Suspensory ligaments torn/frayed</t>
-        </is>
-      </c>
-      <c r="D7" s="34" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Suspensory ligaments torn/frayed/holed</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Block pulled/handled by the ligaments</t>
         </is>
       </c>
-      <c r="E7" s="34" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Rough handling + high traction on removal</t>
         </is>
       </c>
-      <c r="F7" s="34" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>No 'support-surface' handling rule</t>
         </is>
       </c>
-      <c r="G7" s="35" t="inlineStr">
+      <c r="G8" s="36" t="inlineStr">
         <is>
           <t>(confirm) handling standard missing</t>
         </is>
       </c>
-      <c r="H7" s="36" t="inlineStr">
+      <c r="H8" s="37" t="inlineStr">
         <is>
           <t>Handle block by support surface, not ligaments; control pull force</t>
         </is>
       </c>
-      <c r="I7" s="37" t="inlineStr">
+      <c r="I8" s="38" t="inlineStr">
         <is>
           <t>SH Martins - Evisceration lead</t>
         </is>
       </c>
-      <c r="J7" s="37" t="inlineStr"/>
-      <c r="K7" s="38" t="inlineStr">
+      <c r="J8" s="38" t="inlineStr"/>
+      <c r="K8" s="39" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L7" s="39" t="inlineStr"/>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>D5</t>
-        </is>
-      </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>Urethra cut</t>
-        </is>
-      </c>
-      <c r="C8" s="34" t="inlineStr">
-        <is>
-          <t>Urethra cut</t>
-        </is>
-      </c>
-      <c r="D8" s="34" t="inlineStr">
-        <is>
-          <t>Sharp transection through pelvic zone</t>
-        </is>
-      </c>
-      <c r="E8" s="34" t="inlineStr">
-        <is>
-          <t>Splitting saw off-center / bung-drop cut catches urethra</t>
-        </is>
-      </c>
-      <c r="F8" s="34" t="inlineStr">
-        <is>
-          <t>Saw alignment &amp; pelvic-split centering not verified</t>
-        </is>
-      </c>
-      <c r="G8" s="35" t="inlineStr">
-        <is>
-          <t>(confirm) saw calibration + technique gap</t>
-        </is>
-      </c>
-      <c r="H8" s="36" t="inlineStr">
-        <is>
-          <t>Center split on symphysis; calibrate/align saw; slow through pelvic zone</t>
-        </is>
-      </c>
-      <c r="I8" s="37" t="inlineStr">
-        <is>
-          <t>SH Martins - Splitting lead</t>
-        </is>
-      </c>
-      <c r="J8" s="37" t="inlineStr"/>
-      <c r="K8" s="38" t="inlineStr">
+      <c r="L8" s="40" t="inlineStr"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Bowel / colon / rectum breach</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Bowel/colon/rectum breached (FOOD SAFETY)</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Knife slip or aggressive bung separation opens colon/rectum</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Bung not adequately bagged/tied before cut</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Bung-dropping CCP not robust</t>
+        </is>
+      </c>
+      <c r="G9" s="36" t="inlineStr">
+        <is>
+          <t>(confirm) contamination-control gap at bung station</t>
+        </is>
+      </c>
+      <c r="H9" s="37" t="inlineStr">
+        <is>
+          <t>Reinforce bung bag/tie-off; retrain knife path; treat as contamination CCP</t>
+        </is>
+      </c>
+      <c r="I9" s="38" t="inlineStr">
+        <is>
+          <t>SH Martins - Bung/Evisc. lead</t>
+        </is>
+      </c>
+      <c r="J9" s="38" t="inlineStr"/>
+      <c r="K9" s="39" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L8" s="39" t="inlineStr"/>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>D8</t>
-        </is>
-      </c>
-      <c r="B9" s="33" t="inlineStr">
-        <is>
-          <t>Bowel cut / opened / separated</t>
-        </is>
-      </c>
-      <c r="C9" s="34" t="inlineStr">
-        <is>
-          <t>Bowel cut open / separated (FOOD SAFETY)</t>
-        </is>
-      </c>
-      <c r="D9" s="34" t="inlineStr">
-        <is>
-          <t>Knife slip or aggressive bung separation opens bowel</t>
-        </is>
-      </c>
-      <c r="E9" s="34" t="inlineStr">
-        <is>
-          <t>Bung not adequately bagged/tied before cut</t>
-        </is>
-      </c>
-      <c r="F9" s="34" t="inlineStr">
-        <is>
-          <t>Bung-dropping CCP not robust</t>
-        </is>
-      </c>
-      <c r="G9" s="35" t="inlineStr">
-        <is>
-          <t>(confirm) contamination-control gap at bung station</t>
-        </is>
-      </c>
-      <c r="H9" s="36" t="inlineStr">
-        <is>
-          <t>Reinforce bung bag/tie-off; retrain knife path; treat as contamination CCP</t>
-        </is>
-      </c>
-      <c r="I9" s="37" t="inlineStr">
-        <is>
-          <t>SH Martins - Bung/Evisc. lead</t>
-        </is>
-      </c>
-      <c r="J9" s="37" t="inlineStr"/>
-      <c r="K9" s="38" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="L9" s="39" t="inlineStr"/>
+      <c r="L9" s="40" t="inlineStr"/>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="40" t="n"/>
-      <c r="B10" s="40" t="n"/>
-      <c r="C10" s="40" t="n"/>
-      <c r="D10" s="40" t="n"/>
-      <c r="E10" s="40" t="n"/>
-      <c r="F10" s="40" t="n"/>
-      <c r="G10" s="41" t="n"/>
-      <c r="H10" s="42" t="n"/>
-      <c r="I10" s="40" t="n"/>
-      <c r="J10" s="40" t="n"/>
-      <c r="K10" s="40" t="n"/>
-      <c r="L10" s="43" t="n"/>
+      <c r="A10" s="41" t="n"/>
+      <c r="B10" s="41" t="n"/>
+      <c r="C10" s="41" t="n"/>
+      <c r="D10" s="41" t="n"/>
+      <c r="E10" s="41" t="n"/>
+      <c r="F10" s="41" t="n"/>
+      <c r="G10" s="42" t="n"/>
+      <c r="H10" s="43" t="n"/>
+      <c r="I10" s="41" t="n"/>
+      <c r="J10" s="41" t="n"/>
+      <c r="K10" s="41" t="n"/>
+      <c r="L10" s="44" t="n"/>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="40" t="n"/>
-      <c r="B11" s="40" t="n"/>
-      <c r="C11" s="40" t="n"/>
-      <c r="D11" s="40" t="n"/>
-      <c r="E11" s="40" t="n"/>
-      <c r="F11" s="40" t="n"/>
-      <c r="G11" s="41" t="n"/>
-      <c r="H11" s="42" t="n"/>
-      <c r="I11" s="40" t="n"/>
-      <c r="J11" s="40" t="n"/>
-      <c r="K11" s="40" t="n"/>
-      <c r="L11" s="43" t="n"/>
+      <c r="A11" s="41" t="n"/>
+      <c r="B11" s="41" t="n"/>
+      <c r="C11" s="41" t="n"/>
+      <c r="D11" s="41" t="n"/>
+      <c r="E11" s="41" t="n"/>
+      <c r="F11" s="41" t="n"/>
+      <c r="G11" s="42" t="n"/>
+      <c r="H11" s="43" t="n"/>
+      <c r="I11" s="41" t="n"/>
+      <c r="J11" s="41" t="n"/>
+      <c r="K11" s="41" t="n"/>
+      <c r="L11" s="44" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="41" t="n"/>
+      <c r="B12" s="41" t="n"/>
+      <c r="C12" s="41" t="n"/>
+      <c r="D12" s="41" t="n"/>
+      <c r="E12" s="41" t="n"/>
+      <c r="F12" s="41" t="n"/>
+      <c r="G12" s="42" t="n"/>
+      <c r="H12" s="43" t="n"/>
+      <c r="I12" s="41" t="n"/>
+      <c r="J12" s="41" t="n"/>
+      <c r="K12" s="41" t="n"/>
+      <c r="L12" s="44" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5088,156 +7121,267 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — BATCH SUMMARY</t>
+          <t>DASHBOARD — SUMMARY</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SH: Martins  |  Kill/Harvest 2026-07-08  |  Batch 12:30–12:45 PM</t>
+          <t>SH: Martins  |  2 batches ingested (kills 2026-05-27 &amp; 2026-07-08)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
-        <is>
-          <t>KEY METRICS</t>
+      <c r="A4" s="45" t="inlineStr">
+        <is>
+          <t>KEY METRICS (all batches)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>Blocks Inspected</t>
         </is>
       </c>
-      <c r="B5" s="46">
-        <f>COUNTA('Inspection Log'!A5:A430)-COUNTBLANK('Inspection Log'!A5:A430)</f>
+      <c r="B5" s="47">
+        <f>COUNTIF('Inspection Log'!J5:J461,"Pass")+COUNTIF('Inspection Log'!J5:J461,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="45" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="B6" s="46">
-        <f>COUNTIF('Inspection Log'!J5:J430,"Pass")</f>
+      <c r="B6" s="47">
+        <f>COUNTIF('Inspection Log'!J5:J461,"Pass")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="45" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="B7" s="46">
-        <f>COUNTIF('Inspection Log'!J5:J430,"Fail")</f>
+      <c r="B7" s="47">
+        <f>COUNTIF('Inspection Log'!J5:J461,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>First Pass Yield</t>
         </is>
       </c>
-      <c r="B8" s="47">
-        <f>IFERROR(COUNTIF('Inspection Log'!J5:J430,"Pass")/(COUNTA('Inspection Log'!A5:A430)-COUNTBLANK('Inspection Log'!A5:A430)),0)</f>
+      <c r="B8" s="48">
+        <f>IFERROR(COUNTIF('Inspection Log'!J5:J461,"Pass")/(COUNTIF('Inspection Log'!J5:J461,"Pass")+COUNTIF('Inspection Log'!J5:J461,"Fail")),0)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="45" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>Total Defect Occurrences</t>
         </is>
       </c>
-      <c r="B9" s="46">
-        <f>SUM('Inspection Log'!L5:U430)</f>
+      <c r="B9" s="47">
+        <f>SUM('Inspection Log'!L5:V461)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="45" t="inlineStr">
+      <c r="A10" s="46" t="inlineStr">
         <is>
           <t>Defects per Failed Block</t>
         </is>
       </c>
-      <c r="B10" s="48">
-        <f>IFERROR(SUM('Inspection Log'!L5:U430)/COUNTIF('Inspection Log'!J5:J430,"Fail"),0)</f>
+      <c r="B10" s="49">
+        <f>IFERROR(SUM('Inspection Log'!L5:V461)/COUNTIF('Inspection Log'!J5:J461,"Fail"),0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="44" t="inlineStr">
-        <is>
-          <t>TOP DEFECT (this batch)</t>
+      <c r="A12" s="45" t="inlineStr">
+        <is>
+          <t>PER-BATCH BREAKDOWN (watch the trend)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="49" t="inlineStr">
-        <is>
-          <t>Membrane damage in critical area</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Kill Date</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Inspected</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>First Pass Yield</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Top Defect (this batch)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="50" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B14" s="22">
+        <f>COUNTIF('Inspection Log'!C5:C461,"2026-05-27")</f>
+        <v/>
+      </c>
+      <c r="C14" s="22">
+        <f>COUNTIFS('Inspection Log'!C5:C461,"2026-05-27",'Inspection Log'!J5:J461,"Pass")</f>
+        <v/>
+      </c>
+      <c r="D14" s="22">
+        <f>COUNTIFS('Inspection Log'!C5:C461,"2026-05-27",'Inspection Log'!J5:J461,"Fail")</f>
+        <v/>
+      </c>
+      <c r="E14" s="25">
+        <f>IFERROR(C14/B14,0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>D6 Membrane damage in critical area (15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B15" s="22">
+        <f>COUNTIF('Inspection Log'!C5:C461,"2026-07-08")</f>
+        <v/>
+      </c>
+      <c r="C15" s="22">
+        <f>COUNTIFS('Inspection Log'!C5:C461,"2026-07-08",'Inspection Log'!J5:J461,"Pass")</f>
+        <v/>
+      </c>
+      <c r="D15" s="22">
+        <f>COUNTIFS('Inspection Log'!C5:C461,"2026-07-08",'Inspection Log'!J5:J461,"Fail")</f>
+        <v/>
+      </c>
+      <c r="E15" s="34">
+        <f>IFERROR(C15/B15,0)</f>
+        <v/>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>D6 Membrane damage in critical area (16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="45" t="inlineStr">
+        <is>
+          <t>Top defect (all batches)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="50" t="inlineStr">
+        <is>
+          <t>D6 Membrane damage in critical area</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="51" t="inlineStr">
         <is>
           <t>Dominant supplier station</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="51" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="52" t="inlineStr">
         <is>
           <t>S3 Evisceration  -&gt;  primary target for corrective action</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="52" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="53" t="inlineStr">
         <is>
           <t>Critical / food-safety defect occurrences</t>
         </is>
       </c>
-      <c r="B17" s="53">
-        <f>SUM('Inspection Log'!Q5:Q430)+SUM('Inspection Log'!S5:S430)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (Critical codes: D6, D8 — membrane damage &amp; bowel breach)</t>
+      <c r="B22" s="54">
+        <f>SUM('Inspection Log'!Q5:Q461)+SUM('Inspection Log'!S5:S461)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (Critical codes: D6, D8 — membrane damage &amp; bowel/colon/rectum breach)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="56" t="inlineStr">
+        <is>
+          <t>OPEN ITEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="57" t="inlineStr">
+        <is>
+          <t>5 blocks (kill 2026-05-27), 8" hole in bladder suspensory ligament, recorded as PASS pending ME/DE determination. If confirmed Fail -&gt; tag D4.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A15:D15"/>
+  <mergeCells count="5">
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pelvic-block-iqc-pareto/Pelvic_Block_IQC_Pareto_RootCause.xlsx
+++ b/pelvic-block-iqc-pareto/Pelvic_Block_IQC_Pareto_RootCause.xlsx
@@ -508,7 +508,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Defect Pareto — Rejected Pelvic Blocks   (SH: Martins, 2 batches)</a:t>
+              <a:t>Defect Pareto — Rejected Pelvic Blocks   (SH: Martins · 3 kill dates)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -595,7 +595,7 @@
             <idx val="4"/>
             <spPr>
               <a:solidFill>
-                <a:srgbClr val="AFC7E3"/>
+                <a:srgbClr val="2E5B8A"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
@@ -689,6 +689,34 @@
               </a:ln>
             </spPr>
           </dPt>
+          <dPt>
+            <idx val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="AFC7E3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="12"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="AFC7E3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <dLbls>
             <numFmt formatCode="0"/>
             <txPr>
@@ -718,12 +746,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Pareto'!$M$6:$M$16</f>
+              <f>'Pareto'!$M$6:$M$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Pareto'!$D$6:$D$16</f>
+              <f>'Pareto'!$D$6:$D$18</f>
             </numRef>
           </val>
         </ser>
@@ -793,7 +821,7 @@
           </dLbls>
           <val>
             <numRef>
-              <f>'Pareto'!$F$6:$F$16</f>
+              <f>'Pareto'!$F$6:$F$18</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -824,7 +852,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Pareto'!$N$6:$N$16</f>
+              <f>'Pareto'!$N$6:$N$18</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1026,10 +1054,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5667375" cy="2905125"/>
+    <ext cx="5724525" cy="2905125"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1496,28 +1524,28 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>WHAT THE DATA SAYS SO FAR  (2 batches, SH: Martins — kills 2026-05-27 &amp; 2026-07-08)</t>
+          <t>WHAT THE DATA SAYS SO FAR  (4 inspection sheets across 3 kill dates: 2026-05-27, 2026-07-08, 2026-07-28 — SH: Martins)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  57 blocks inspected · 9 pass · 48 fail · combined First Pass Yield 15.8% · 78 defect occurrences</t>
+          <t xml:space="preserve">  99 blocks inspected · 10 pass · 89 fail · combined First Pass Yield 10.1% · 122 defect occurrences</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Vital few (~78%): membrane damage (critical area), ureters not embedded, urethra breach, suspensory-ligament damage.  ~78% of ALL defects originate at ONE station: Evisceration.</t>
+          <t xml:space="preserve">  Vital few (~80%): membrane damage (critical area), ureters not embedded, urethra breach, bowel/colon/rectum breach, suspensory-ligament damage.  ~84% of ALL defects originate at ONE station: Evisceration.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  OPEN ITEM: 5 blocks (kill 2026-05-27) with an 8" hole in the bladder suspensory ligament are recorded as PASS pending ME/DE determination — flip to Fail + tag D4 if confirmed.</t>
+          <t xml:space="preserve">  OPEN ITEMS: (1) 5 blocks (kill 2026-05-27), 8" hole in bladder suspensory ligament — recorded PASS pending ME/DE (flip to Fail + tag D4 if confirmed).  (2) Rasmin 07-28 sheet handwritten total said '22 fails' but per-row entries sum to 29 (used).</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X61"/>
+  <dimension ref="A1:Z103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1626,8 +1654,10 @@
     <col width="6" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="9" customWidth="1" min="23" max="23"/>
-    <col width="34" customWidth="1" min="24" max="24"/>
+    <col width="6" customWidth="1" min="23" max="23"/>
+    <col width="6" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="34" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1757,10 +1787,20 @@
       </c>
       <c r="W4" s="6" t="inlineStr">
         <is>
+          <t>D12</t>
+        </is>
+      </c>
+      <c r="X4" s="6" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="Y4" s="6" t="inlineStr">
+        <is>
           <t># Defects</t>
         </is>
       </c>
-      <c r="X4" s="6" t="inlineStr">
+      <c r="Z4" s="6" t="inlineStr">
         <is>
           <t>Notes / Disposition</t>
         </is>
@@ -1819,11 +1859,13 @@
       <c r="T5" s="10" t="n"/>
       <c r="U5" s="10" t="n"/>
       <c r="V5" s="10" t="n"/>
-      <c r="W5" s="12">
-        <f>SUM(L5:V5)</f>
-        <v/>
-      </c>
-      <c r="X5" s="13" t="inlineStr"/>
+      <c r="W5" s="10" t="n"/>
+      <c r="X5" s="10" t="n"/>
+      <c r="Y5" s="12">
+        <f>SUM(L5:X5)</f>
+        <v/>
+      </c>
+      <c r="Z5" s="13" t="inlineStr"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -1878,11 +1920,13 @@
       <c r="T6" s="10" t="n"/>
       <c r="U6" s="10" t="n"/>
       <c r="V6" s="10" t="n"/>
-      <c r="W6" s="12">
-        <f>SUM(L6:V6)</f>
-        <v/>
-      </c>
-      <c r="X6" s="13" t="inlineStr"/>
+      <c r="W6" s="10" t="n"/>
+      <c r="X6" s="10" t="n"/>
+      <c r="Y6" s="12">
+        <f>SUM(L6:X6)</f>
+        <v/>
+      </c>
+      <c r="Z6" s="13" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -1937,11 +1981,13 @@
       <c r="T7" s="10" t="n"/>
       <c r="U7" s="10" t="n"/>
       <c r="V7" s="10" t="n"/>
-      <c r="W7" s="12">
-        <f>SUM(L7:V7)</f>
-        <v/>
-      </c>
-      <c r="X7" s="13" t="inlineStr"/>
+      <c r="W7" s="10" t="n"/>
+      <c r="X7" s="10" t="n"/>
+      <c r="Y7" s="12">
+        <f>SUM(L7:X7)</f>
+        <v/>
+      </c>
+      <c r="Z7" s="13" t="inlineStr"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -1998,11 +2044,13 @@
       <c r="V8" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="W8" s="12">
-        <f>SUM(L8:V8)</f>
-        <v/>
-      </c>
-      <c r="X8" s="13" t="inlineStr"/>
+      <c r="W8" s="10" t="n"/>
+      <c r="X8" s="10" t="n"/>
+      <c r="Y8" s="12">
+        <f>SUM(L8:X8)</f>
+        <v/>
+      </c>
+      <c r="Z8" s="13" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -2055,11 +2103,13 @@
       <c r="T9" s="10" t="n"/>
       <c r="U9" s="10" t="n"/>
       <c r="V9" s="10" t="n"/>
-      <c r="W9" s="12">
-        <f>SUM(L9:V9)</f>
-        <v/>
-      </c>
-      <c r="X9" s="15" t="inlineStr">
+      <c r="W9" s="10" t="n"/>
+      <c r="X9" s="10" t="n"/>
+      <c r="Y9" s="12">
+        <f>SUM(L9:X9)</f>
+        <v/>
+      </c>
+      <c r="Z9" s="15" t="inlineStr">
         <is>
           <t>QUESTIONABLE - pending ME/DE determination (per sheet note). If reclassified Fail -&gt; D4 (suspensory ligament).</t>
         </is>
@@ -2116,11 +2166,13 @@
       <c r="T10" s="10" t="n"/>
       <c r="U10" s="10" t="n"/>
       <c r="V10" s="10" t="n"/>
-      <c r="W10" s="12">
-        <f>SUM(L10:V10)</f>
-        <v/>
-      </c>
-      <c r="X10" s="15" t="inlineStr">
+      <c r="W10" s="10" t="n"/>
+      <c r="X10" s="10" t="n"/>
+      <c r="Y10" s="12">
+        <f>SUM(L10:X10)</f>
+        <v/>
+      </c>
+      <c r="Z10" s="15" t="inlineStr">
         <is>
           <t>QUESTIONABLE - pending ME/DE determination (per sheet note). If reclassified Fail -&gt; D4 (suspensory ligament).</t>
         </is>
@@ -2177,11 +2229,13 @@
       <c r="T11" s="10" t="n"/>
       <c r="U11" s="10" t="n"/>
       <c r="V11" s="10" t="n"/>
-      <c r="W11" s="12">
-        <f>SUM(L11:V11)</f>
-        <v/>
-      </c>
-      <c r="X11" s="15" t="inlineStr">
+      <c r="W11" s="10" t="n"/>
+      <c r="X11" s="10" t="n"/>
+      <c r="Y11" s="12">
+        <f>SUM(L11:X11)</f>
+        <v/>
+      </c>
+      <c r="Z11" s="15" t="inlineStr">
         <is>
           <t>QUESTIONABLE - pending ME/DE determination (per sheet note). If reclassified Fail -&gt; D4 (suspensory ligament).</t>
         </is>
@@ -2238,11 +2292,13 @@
       <c r="T12" s="10" t="n"/>
       <c r="U12" s="10" t="n"/>
       <c r="V12" s="10" t="n"/>
-      <c r="W12" s="12">
-        <f>SUM(L12:V12)</f>
-        <v/>
-      </c>
-      <c r="X12" s="15" t="inlineStr">
+      <c r="W12" s="10" t="n"/>
+      <c r="X12" s="10" t="n"/>
+      <c r="Y12" s="12">
+        <f>SUM(L12:X12)</f>
+        <v/>
+      </c>
+      <c r="Z12" s="15" t="inlineStr">
         <is>
           <t>QUESTIONABLE - pending ME/DE determination (per sheet note). If reclassified Fail -&gt; D4 (suspensory ligament).</t>
         </is>
@@ -2299,11 +2355,13 @@
       <c r="T13" s="10" t="n"/>
       <c r="U13" s="10" t="n"/>
       <c r="V13" s="10" t="n"/>
-      <c r="W13" s="12">
-        <f>SUM(L13:V13)</f>
-        <v/>
-      </c>
-      <c r="X13" s="15" t="inlineStr">
+      <c r="W13" s="10" t="n"/>
+      <c r="X13" s="10" t="n"/>
+      <c r="Y13" s="12">
+        <f>SUM(L13:X13)</f>
+        <v/>
+      </c>
+      <c r="Z13" s="15" t="inlineStr">
         <is>
           <t>QUESTIONABLE - pending ME/DE determination (per sheet note). If reclassified Fail -&gt; D4 (suspensory ligament).</t>
         </is>
@@ -2360,11 +2418,13 @@
       <c r="T14" s="10" t="n"/>
       <c r="U14" s="10" t="n"/>
       <c r="V14" s="10" t="n"/>
-      <c r="W14" s="12">
-        <f>SUM(L14:V14)</f>
-        <v/>
-      </c>
-      <c r="X14" s="13" t="inlineStr"/>
+      <c r="W14" s="10" t="n"/>
+      <c r="X14" s="10" t="n"/>
+      <c r="Y14" s="12">
+        <f>SUM(L14:X14)</f>
+        <v/>
+      </c>
+      <c r="Z14" s="13" t="inlineStr"/>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -2417,11 +2477,13 @@
       <c r="T15" s="10" t="n"/>
       <c r="U15" s="10" t="n"/>
       <c r="V15" s="10" t="n"/>
-      <c r="W15" s="12">
-        <f>SUM(L15:V15)</f>
-        <v/>
-      </c>
-      <c r="X15" s="13" t="inlineStr"/>
+      <c r="W15" s="10" t="n"/>
+      <c r="X15" s="10" t="n"/>
+      <c r="Y15" s="12">
+        <f>SUM(L15:X15)</f>
+        <v/>
+      </c>
+      <c r="Z15" s="13" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
@@ -2476,11 +2538,13 @@
       <c r="T16" s="10" t="n"/>
       <c r="U16" s="10" t="n"/>
       <c r="V16" s="10" t="n"/>
-      <c r="W16" s="12">
-        <f>SUM(L16:V16)</f>
-        <v/>
-      </c>
-      <c r="X16" s="13" t="inlineStr"/>
+      <c r="W16" s="10" t="n"/>
+      <c r="X16" s="10" t="n"/>
+      <c r="Y16" s="12">
+        <f>SUM(L16:X16)</f>
+        <v/>
+      </c>
+      <c r="Z16" s="13" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
@@ -2535,11 +2599,13 @@
       <c r="T17" s="10" t="n"/>
       <c r="U17" s="10" t="n"/>
       <c r="V17" s="10" t="n"/>
-      <c r="W17" s="12">
-        <f>SUM(L17:V17)</f>
-        <v/>
-      </c>
-      <c r="X17" s="13" t="inlineStr"/>
+      <c r="W17" s="10" t="n"/>
+      <c r="X17" s="10" t="n"/>
+      <c r="Y17" s="12">
+        <f>SUM(L17:X17)</f>
+        <v/>
+      </c>
+      <c r="Z17" s="13" t="inlineStr"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
@@ -2594,11 +2660,13 @@
       <c r="T18" s="10" t="n"/>
       <c r="U18" s="10" t="n"/>
       <c r="V18" s="10" t="n"/>
-      <c r="W18" s="12">
-        <f>SUM(L18:V18)</f>
-        <v/>
-      </c>
-      <c r="X18" s="13" t="inlineStr"/>
+      <c r="W18" s="10" t="n"/>
+      <c r="X18" s="10" t="n"/>
+      <c r="Y18" s="12">
+        <f>SUM(L18:X18)</f>
+        <v/>
+      </c>
+      <c r="Z18" s="13" t="inlineStr"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -2653,11 +2721,13 @@
       <c r="T19" s="10" t="n"/>
       <c r="U19" s="10" t="n"/>
       <c r="V19" s="10" t="n"/>
-      <c r="W19" s="12">
-        <f>SUM(L19:V19)</f>
-        <v/>
-      </c>
-      <c r="X19" s="13" t="inlineStr"/>
+      <c r="W19" s="10" t="n"/>
+      <c r="X19" s="10" t="n"/>
+      <c r="Y19" s="12">
+        <f>SUM(L19:X19)</f>
+        <v/>
+      </c>
+      <c r="Z19" s="13" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
@@ -2712,11 +2782,13 @@
       <c r="T20" s="10" t="n"/>
       <c r="U20" s="10" t="n"/>
       <c r="V20" s="10" t="n"/>
-      <c r="W20" s="12">
-        <f>SUM(L20:V20)</f>
-        <v/>
-      </c>
-      <c r="X20" s="13" t="inlineStr"/>
+      <c r="W20" s="10" t="n"/>
+      <c r="X20" s="10" t="n"/>
+      <c r="Y20" s="12">
+        <f>SUM(L20:X20)</f>
+        <v/>
+      </c>
+      <c r="Z20" s="13" t="inlineStr"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
@@ -2771,11 +2843,13 @@
       <c r="T21" s="10" t="n"/>
       <c r="U21" s="10" t="n"/>
       <c r="V21" s="10" t="n"/>
-      <c r="W21" s="12">
-        <f>SUM(L21:V21)</f>
-        <v/>
-      </c>
-      <c r="X21" s="13" t="inlineStr"/>
+      <c r="W21" s="10" t="n"/>
+      <c r="X21" s="10" t="n"/>
+      <c r="Y21" s="12">
+        <f>SUM(L21:X21)</f>
+        <v/>
+      </c>
+      <c r="Z21" s="13" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
@@ -2830,11 +2904,13 @@
       <c r="T22" s="10" t="n"/>
       <c r="U22" s="10" t="n"/>
       <c r="V22" s="10" t="n"/>
-      <c r="W22" s="12">
-        <f>SUM(L22:V22)</f>
-        <v/>
-      </c>
-      <c r="X22" s="13" t="inlineStr"/>
+      <c r="W22" s="10" t="n"/>
+      <c r="X22" s="10" t="n"/>
+      <c r="Y22" s="12">
+        <f>SUM(L22:X22)</f>
+        <v/>
+      </c>
+      <c r="Z22" s="13" t="inlineStr"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
@@ -2889,11 +2965,13 @@
       <c r="T23" s="10" t="n"/>
       <c r="U23" s="10" t="n"/>
       <c r="V23" s="10" t="n"/>
-      <c r="W23" s="12">
-        <f>SUM(L23:V23)</f>
-        <v/>
-      </c>
-      <c r="X23" s="13" t="inlineStr"/>
+      <c r="W23" s="10" t="n"/>
+      <c r="X23" s="10" t="n"/>
+      <c r="Y23" s="12">
+        <f>SUM(L23:X23)</f>
+        <v/>
+      </c>
+      <c r="Z23" s="13" t="inlineStr"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
@@ -2948,11 +3026,13 @@
       <c r="T24" s="10" t="n"/>
       <c r="U24" s="10" t="n"/>
       <c r="V24" s="10" t="n"/>
-      <c r="W24" s="12">
-        <f>SUM(L24:V24)</f>
-        <v/>
-      </c>
-      <c r="X24" s="13" t="inlineStr"/>
+      <c r="W24" s="10" t="n"/>
+      <c r="X24" s="10" t="n"/>
+      <c r="Y24" s="12">
+        <f>SUM(L24:X24)</f>
+        <v/>
+      </c>
+      <c r="Z24" s="13" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
@@ -3007,11 +3087,13 @@
       <c r="T25" s="10" t="n"/>
       <c r="U25" s="10" t="n"/>
       <c r="V25" s="10" t="n"/>
-      <c r="W25" s="12">
-        <f>SUM(L25:V25)</f>
-        <v/>
-      </c>
-      <c r="X25" s="13" t="inlineStr"/>
+      <c r="W25" s="10" t="n"/>
+      <c r="X25" s="10" t="n"/>
+      <c r="Y25" s="12">
+        <f>SUM(L25:X25)</f>
+        <v/>
+      </c>
+      <c r="Z25" s="13" t="inlineStr"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
@@ -3066,11 +3148,13 @@
       <c r="T26" s="10" t="n"/>
       <c r="U26" s="10" t="n"/>
       <c r="V26" s="10" t="n"/>
-      <c r="W26" s="12">
-        <f>SUM(L26:V26)</f>
-        <v/>
-      </c>
-      <c r="X26" s="13" t="inlineStr"/>
+      <c r="W26" s="10" t="n"/>
+      <c r="X26" s="10" t="n"/>
+      <c r="Y26" s="12">
+        <f>SUM(L26:X26)</f>
+        <v/>
+      </c>
+      <c r="Z26" s="13" t="inlineStr"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
@@ -3125,11 +3209,13 @@
       <c r="T27" s="10" t="n"/>
       <c r="U27" s="10" t="n"/>
       <c r="V27" s="10" t="n"/>
-      <c r="W27" s="12">
-        <f>SUM(L27:V27)</f>
-        <v/>
-      </c>
-      <c r="X27" s="13" t="inlineStr"/>
+      <c r="W27" s="10" t="n"/>
+      <c r="X27" s="10" t="n"/>
+      <c r="Y27" s="12">
+        <f>SUM(L27:X27)</f>
+        <v/>
+      </c>
+      <c r="Z27" s="13" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
@@ -3184,11 +3270,13 @@
       <c r="T28" s="10" t="n"/>
       <c r="U28" s="10" t="n"/>
       <c r="V28" s="10" t="n"/>
-      <c r="W28" s="12">
-        <f>SUM(L28:V28)</f>
-        <v/>
-      </c>
-      <c r="X28" s="13" t="inlineStr"/>
+      <c r="W28" s="10" t="n"/>
+      <c r="X28" s="10" t="n"/>
+      <c r="Y28" s="12">
+        <f>SUM(L28:X28)</f>
+        <v/>
+      </c>
+      <c r="Z28" s="13" t="inlineStr"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
@@ -3243,11 +3331,13 @@
       <c r="T29" s="10" t="n"/>
       <c r="U29" s="10" t="n"/>
       <c r="V29" s="10" t="n"/>
-      <c r="W29" s="12">
-        <f>SUM(L29:V29)</f>
-        <v/>
-      </c>
-      <c r="X29" s="13" t="inlineStr"/>
+      <c r="W29" s="10" t="n"/>
+      <c r="X29" s="10" t="n"/>
+      <c r="Y29" s="12">
+        <f>SUM(L29:X29)</f>
+        <v/>
+      </c>
+      <c r="Z29" s="13" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
@@ -3302,11 +3392,13 @@
       <c r="T30" s="10" t="n"/>
       <c r="U30" s="10" t="n"/>
       <c r="V30" s="10" t="n"/>
-      <c r="W30" s="12">
-        <f>SUM(L30:V30)</f>
-        <v/>
-      </c>
-      <c r="X30" s="13" t="inlineStr"/>
+      <c r="W30" s="10" t="n"/>
+      <c r="X30" s="10" t="n"/>
+      <c r="Y30" s="12">
+        <f>SUM(L30:X30)</f>
+        <v/>
+      </c>
+      <c r="Z30" s="13" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
@@ -3361,11 +3453,13 @@
       <c r="T31" s="10" t="n"/>
       <c r="U31" s="10" t="n"/>
       <c r="V31" s="10" t="n"/>
-      <c r="W31" s="12">
-        <f>SUM(L31:V31)</f>
-        <v/>
-      </c>
-      <c r="X31" s="13" t="inlineStr"/>
+      <c r="W31" s="10" t="n"/>
+      <c r="X31" s="10" t="n"/>
+      <c r="Y31" s="12">
+        <f>SUM(L31:X31)</f>
+        <v/>
+      </c>
+      <c r="Z31" s="13" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
@@ -3420,11 +3514,13 @@
       <c r="T32" s="10" t="n"/>
       <c r="U32" s="10" t="n"/>
       <c r="V32" s="10" t="n"/>
-      <c r="W32" s="12">
-        <f>SUM(L32:V32)</f>
-        <v/>
-      </c>
-      <c r="X32" s="13" t="inlineStr"/>
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="10" t="n"/>
+      <c r="Y32" s="12">
+        <f>SUM(L32:X32)</f>
+        <v/>
+      </c>
+      <c r="Z32" s="13" t="inlineStr"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
@@ -3479,11 +3575,13 @@
       <c r="T33" s="10" t="n"/>
       <c r="U33" s="10" t="n"/>
       <c r="V33" s="10" t="n"/>
-      <c r="W33" s="12">
-        <f>SUM(L33:V33)</f>
-        <v/>
-      </c>
-      <c r="X33" s="13" t="inlineStr"/>
+      <c r="W33" s="10" t="n"/>
+      <c r="X33" s="10" t="n"/>
+      <c r="Y33" s="12">
+        <f>SUM(L33:X33)</f>
+        <v/>
+      </c>
+      <c r="Z33" s="13" t="inlineStr"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
@@ -3540,11 +3638,13 @@
       <c r="T34" s="10" t="n"/>
       <c r="U34" s="10" t="n"/>
       <c r="V34" s="10" t="n"/>
-      <c r="W34" s="12">
-        <f>SUM(L34:V34)</f>
-        <v/>
-      </c>
-      <c r="X34" s="13" t="inlineStr"/>
+      <c r="W34" s="10" t="n"/>
+      <c r="X34" s="10" t="n"/>
+      <c r="Y34" s="12">
+        <f>SUM(L34:X34)</f>
+        <v/>
+      </c>
+      <c r="Z34" s="13" t="inlineStr"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
@@ -3597,11 +3697,13 @@
       <c r="T35" s="10" t="n"/>
       <c r="U35" s="10" t="n"/>
       <c r="V35" s="10" t="n"/>
-      <c r="W35" s="12">
-        <f>SUM(L35:V35)</f>
-        <v/>
-      </c>
-      <c r="X35" s="15" t="inlineStr">
+      <c r="W35" s="10" t="n"/>
+      <c r="X35" s="10" t="n"/>
+      <c r="Y35" s="12">
+        <f>SUM(L35:X35)</f>
+        <v/>
+      </c>
+      <c r="Z35" s="15" t="inlineStr">
         <is>
           <t>Colon hole small enough to pass template.</t>
         </is>
@@ -3672,11 +3774,13 @@
         <v>1</v>
       </c>
       <c r="V36" s="10" t="n"/>
-      <c r="W36" s="12">
-        <f>SUM(L36:V36)</f>
-        <v/>
-      </c>
-      <c r="X36" s="13" t="inlineStr"/>
+      <c r="W36" s="10" t="n"/>
+      <c r="X36" s="10" t="n"/>
+      <c r="Y36" s="12">
+        <f>SUM(L36:X36)</f>
+        <v/>
+      </c>
+      <c r="Z36" s="13" t="inlineStr"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
@@ -3741,11 +3845,13 @@
       <c r="T37" s="10" t="n"/>
       <c r="U37" s="10" t="n"/>
       <c r="V37" s="10" t="n"/>
-      <c r="W37" s="12">
-        <f>SUM(L37:V37)</f>
-        <v/>
-      </c>
-      <c r="X37" s="13" t="inlineStr"/>
+      <c r="W37" s="10" t="n"/>
+      <c r="X37" s="10" t="n"/>
+      <c r="Y37" s="12">
+        <f>SUM(L37:X37)</f>
+        <v/>
+      </c>
+      <c r="Z37" s="13" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
@@ -3808,11 +3914,13 @@
       <c r="T38" s="10" t="n"/>
       <c r="U38" s="10" t="n"/>
       <c r="V38" s="10" t="n"/>
-      <c r="W38" s="12">
-        <f>SUM(L38:V38)</f>
-        <v/>
-      </c>
-      <c r="X38" s="13" t="inlineStr"/>
+      <c r="W38" s="10" t="n"/>
+      <c r="X38" s="10" t="n"/>
+      <c r="Y38" s="12">
+        <f>SUM(L38:X38)</f>
+        <v/>
+      </c>
+      <c r="Z38" s="13" t="inlineStr"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
@@ -3875,11 +3983,13 @@
       <c r="T39" s="10" t="n"/>
       <c r="U39" s="10" t="n"/>
       <c r="V39" s="10" t="n"/>
-      <c r="W39" s="12">
-        <f>SUM(L39:V39)</f>
-        <v/>
-      </c>
-      <c r="X39" s="13" t="inlineStr"/>
+      <c r="W39" s="10" t="n"/>
+      <c r="X39" s="10" t="n"/>
+      <c r="Y39" s="12">
+        <f>SUM(L39:X39)</f>
+        <v/>
+      </c>
+      <c r="Z39" s="13" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
@@ -3944,11 +4054,13 @@
       <c r="T40" s="10" t="n"/>
       <c r="U40" s="10" t="n"/>
       <c r="V40" s="10" t="n"/>
-      <c r="W40" s="12">
-        <f>SUM(L40:V40)</f>
-        <v/>
-      </c>
-      <c r="X40" s="13" t="inlineStr"/>
+      <c r="W40" s="10" t="n"/>
+      <c r="X40" s="10" t="n"/>
+      <c r="Y40" s="12">
+        <f>SUM(L40:X40)</f>
+        <v/>
+      </c>
+      <c r="Z40" s="13" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
@@ -4015,11 +4127,13 @@
       <c r="T41" s="10" t="n"/>
       <c r="U41" s="10" t="n"/>
       <c r="V41" s="10" t="n"/>
-      <c r="W41" s="12">
-        <f>SUM(L41:V41)</f>
-        <v/>
-      </c>
-      <c r="X41" s="13" t="inlineStr"/>
+      <c r="W41" s="10" t="n"/>
+      <c r="X41" s="10" t="n"/>
+      <c r="Y41" s="12">
+        <f>SUM(L41:X41)</f>
+        <v/>
+      </c>
+      <c r="Z41" s="13" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
@@ -4088,11 +4202,13 @@
       <c r="T42" s="10" t="n"/>
       <c r="U42" s="10" t="n"/>
       <c r="V42" s="10" t="n"/>
-      <c r="W42" s="12">
-        <f>SUM(L42:V42)</f>
-        <v/>
-      </c>
-      <c r="X42" s="13" t="inlineStr"/>
+      <c r="W42" s="10" t="n"/>
+      <c r="X42" s="10" t="n"/>
+      <c r="Y42" s="12">
+        <f>SUM(L42:X42)</f>
+        <v/>
+      </c>
+      <c r="Z42" s="13" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
@@ -4161,11 +4277,13 @@
       <c r="T43" s="10" t="n"/>
       <c r="U43" s="10" t="n"/>
       <c r="V43" s="10" t="n"/>
-      <c r="W43" s="12">
-        <f>SUM(L43:V43)</f>
-        <v/>
-      </c>
-      <c r="X43" s="13" t="inlineStr"/>
+      <c r="W43" s="10" t="n"/>
+      <c r="X43" s="10" t="n"/>
+      <c r="Y43" s="12">
+        <f>SUM(L43:X43)</f>
+        <v/>
+      </c>
+      <c r="Z43" s="13" t="inlineStr"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
@@ -4230,11 +4348,13 @@
       <c r="T44" s="10" t="n"/>
       <c r="U44" s="10" t="n"/>
       <c r="V44" s="10" t="n"/>
-      <c r="W44" s="12">
-        <f>SUM(L44:V44)</f>
-        <v/>
-      </c>
-      <c r="X44" s="13" t="inlineStr"/>
+      <c r="W44" s="10" t="n"/>
+      <c r="X44" s="10" t="n"/>
+      <c r="Y44" s="12">
+        <f>SUM(L44:X44)</f>
+        <v/>
+      </c>
+      <c r="Z44" s="13" t="inlineStr"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
@@ -4303,11 +4423,13 @@
       <c r="T45" s="10" t="n"/>
       <c r="U45" s="10" t="n"/>
       <c r="V45" s="10" t="n"/>
-      <c r="W45" s="12">
-        <f>SUM(L45:V45)</f>
-        <v/>
-      </c>
-      <c r="X45" s="13" t="inlineStr"/>
+      <c r="W45" s="10" t="n"/>
+      <c r="X45" s="10" t="n"/>
+      <c r="Y45" s="12">
+        <f>SUM(L45:X45)</f>
+        <v/>
+      </c>
+      <c r="Z45" s="13" t="inlineStr"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
@@ -4370,11 +4492,13 @@
       <c r="T46" s="10" t="n"/>
       <c r="U46" s="10" t="n"/>
       <c r="V46" s="10" t="n"/>
-      <c r="W46" s="12">
-        <f>SUM(L46:V46)</f>
-        <v/>
-      </c>
-      <c r="X46" s="13" t="inlineStr"/>
+      <c r="W46" s="10" t="n"/>
+      <c r="X46" s="10" t="n"/>
+      <c r="Y46" s="12">
+        <f>SUM(L46:X46)</f>
+        <v/>
+      </c>
+      <c r="Z46" s="13" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
@@ -4441,11 +4565,13 @@
       <c r="T47" s="10" t="n"/>
       <c r="U47" s="10" t="n"/>
       <c r="V47" s="10" t="n"/>
-      <c r="W47" s="12">
-        <f>SUM(L47:V47)</f>
-        <v/>
-      </c>
-      <c r="X47" s="13" t="inlineStr"/>
+      <c r="W47" s="10" t="n"/>
+      <c r="X47" s="10" t="n"/>
+      <c r="Y47" s="12">
+        <f>SUM(L47:X47)</f>
+        <v/>
+      </c>
+      <c r="Z47" s="13" t="inlineStr"/>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
@@ -4512,11 +4638,13 @@
       <c r="T48" s="10" t="n"/>
       <c r="U48" s="10" t="n"/>
       <c r="V48" s="10" t="n"/>
-      <c r="W48" s="12">
-        <f>SUM(L48:V48)</f>
-        <v/>
-      </c>
-      <c r="X48" s="13" t="inlineStr"/>
+      <c r="W48" s="10" t="n"/>
+      <c r="X48" s="10" t="n"/>
+      <c r="Y48" s="12">
+        <f>SUM(L48:X48)</f>
+        <v/>
+      </c>
+      <c r="Z48" s="13" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
@@ -4581,11 +4709,13 @@
       </c>
       <c r="U49" s="10" t="n"/>
       <c r="V49" s="10" t="n"/>
-      <c r="W49" s="12">
-        <f>SUM(L49:V49)</f>
-        <v/>
-      </c>
-      <c r="X49" s="13" t="inlineStr"/>
+      <c r="W49" s="10" t="n"/>
+      <c r="X49" s="10" t="n"/>
+      <c r="Y49" s="12">
+        <f>SUM(L49:X49)</f>
+        <v/>
+      </c>
+      <c r="Z49" s="13" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
@@ -4650,11 +4780,13 @@
       <c r="T50" s="10" t="n"/>
       <c r="U50" s="10" t="n"/>
       <c r="V50" s="10" t="n"/>
-      <c r="W50" s="12">
-        <f>SUM(L50:V50)</f>
-        <v/>
-      </c>
-      <c r="X50" s="13" t="inlineStr"/>
+      <c r="W50" s="10" t="n"/>
+      <c r="X50" s="10" t="n"/>
+      <c r="Y50" s="12">
+        <f>SUM(L50:X50)</f>
+        <v/>
+      </c>
+      <c r="Z50" s="13" t="inlineStr"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
@@ -4719,11 +4851,13 @@
       <c r="T51" s="10" t="n"/>
       <c r="U51" s="10" t="n"/>
       <c r="V51" s="10" t="n"/>
-      <c r="W51" s="12">
-        <f>SUM(L51:V51)</f>
-        <v/>
-      </c>
-      <c r="X51" s="13" t="inlineStr"/>
+      <c r="W51" s="10" t="n"/>
+      <c r="X51" s="10" t="n"/>
+      <c r="Y51" s="12">
+        <f>SUM(L51:X51)</f>
+        <v/>
+      </c>
+      <c r="Z51" s="13" t="inlineStr"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
@@ -4788,11 +4922,13 @@
       <c r="T52" s="10" t="n"/>
       <c r="U52" s="10" t="n"/>
       <c r="V52" s="10" t="n"/>
-      <c r="W52" s="12">
-        <f>SUM(L52:V52)</f>
-        <v/>
-      </c>
-      <c r="X52" s="13" t="inlineStr"/>
+      <c r="W52" s="10" t="n"/>
+      <c r="X52" s="10" t="n"/>
+      <c r="Y52" s="12">
+        <f>SUM(L52:X52)</f>
+        <v/>
+      </c>
+      <c r="Z52" s="13" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
@@ -4859,11 +4995,13 @@
       <c r="T53" s="10" t="n"/>
       <c r="U53" s="10" t="n"/>
       <c r="V53" s="10" t="n"/>
-      <c r="W53" s="12">
-        <f>SUM(L53:V53)</f>
-        <v/>
-      </c>
-      <c r="X53" s="13" t="inlineStr"/>
+      <c r="W53" s="10" t="n"/>
+      <c r="X53" s="10" t="n"/>
+      <c r="Y53" s="12">
+        <f>SUM(L53:X53)</f>
+        <v/>
+      </c>
+      <c r="Z53" s="13" t="inlineStr"/>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
@@ -4928,11 +5066,13 @@
       <c r="T54" s="10" t="n"/>
       <c r="U54" s="10" t="n"/>
       <c r="V54" s="10" t="n"/>
-      <c r="W54" s="12">
-        <f>SUM(L54:V54)</f>
-        <v/>
-      </c>
-      <c r="X54" s="13" t="inlineStr"/>
+      <c r="W54" s="10" t="n"/>
+      <c r="X54" s="10" t="n"/>
+      <c r="Y54" s="12">
+        <f>SUM(L54:X54)</f>
+        <v/>
+      </c>
+      <c r="Z54" s="13" t="inlineStr"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
@@ -4995,11 +5135,13 @@
       <c r="T55" s="10" t="n"/>
       <c r="U55" s="10" t="n"/>
       <c r="V55" s="10" t="n"/>
-      <c r="W55" s="12">
-        <f>SUM(L55:V55)</f>
-        <v/>
-      </c>
-      <c r="X55" s="13" t="inlineStr"/>
+      <c r="W55" s="10" t="n"/>
+      <c r="X55" s="10" t="n"/>
+      <c r="Y55" s="12">
+        <f>SUM(L55:X55)</f>
+        <v/>
+      </c>
+      <c r="Z55" s="13" t="inlineStr"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
@@ -5064,11 +5206,13 @@
       <c r="T56" s="10" t="n"/>
       <c r="U56" s="10" t="n"/>
       <c r="V56" s="10" t="n"/>
-      <c r="W56" s="12">
-        <f>SUM(L56:V56)</f>
-        <v/>
-      </c>
-      <c r="X56" s="13" t="inlineStr"/>
+      <c r="W56" s="10" t="n"/>
+      <c r="X56" s="10" t="n"/>
+      <c r="Y56" s="12">
+        <f>SUM(L56:X56)</f>
+        <v/>
+      </c>
+      <c r="Z56" s="13" t="inlineStr"/>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
@@ -5131,11 +5275,13 @@
       <c r="T57" s="10" t="n"/>
       <c r="U57" s="10" t="n"/>
       <c r="V57" s="10" t="n"/>
-      <c r="W57" s="12">
-        <f>SUM(L57:V57)</f>
-        <v/>
-      </c>
-      <c r="X57" s="13" t="inlineStr"/>
+      <c r="W57" s="10" t="n"/>
+      <c r="X57" s="10" t="n"/>
+      <c r="Y57" s="12">
+        <f>SUM(L57:X57)</f>
+        <v/>
+      </c>
+      <c r="Z57" s="13" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
@@ -5198,11 +5344,13 @@
       <c r="T58" s="10" t="n"/>
       <c r="U58" s="10" t="n"/>
       <c r="V58" s="10" t="n"/>
-      <c r="W58" s="12">
-        <f>SUM(L58:V58)</f>
-        <v/>
-      </c>
-      <c r="X58" s="13" t="inlineStr"/>
+      <c r="W58" s="10" t="n"/>
+      <c r="X58" s="10" t="n"/>
+      <c r="Y58" s="12">
+        <f>SUM(L58:X58)</f>
+        <v/>
+      </c>
+      <c r="Z58" s="13" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
@@ -5265,11 +5413,13 @@
       <c r="T59" s="10" t="n"/>
       <c r="U59" s="10" t="n"/>
       <c r="V59" s="10" t="n"/>
-      <c r="W59" s="12">
-        <f>SUM(L59:V59)</f>
-        <v/>
-      </c>
-      <c r="X59" s="13" t="inlineStr"/>
+      <c r="W59" s="10" t="n"/>
+      <c r="X59" s="10" t="n"/>
+      <c r="Y59" s="12">
+        <f>SUM(L59:X59)</f>
+        <v/>
+      </c>
+      <c r="Z59" s="13" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
@@ -5332,11 +5482,13 @@
       <c r="T60" s="10" t="n"/>
       <c r="U60" s="10" t="n"/>
       <c r="V60" s="10" t="n"/>
-      <c r="W60" s="12">
-        <f>SUM(L60:V60)</f>
-        <v/>
-      </c>
-      <c r="X60" s="13" t="inlineStr"/>
+      <c r="W60" s="10" t="n"/>
+      <c r="X60" s="10" t="n"/>
+      <c r="Y60" s="12">
+        <f>SUM(L60:X60)</f>
+        <v/>
+      </c>
+      <c r="Z60" s="13" t="inlineStr"/>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
@@ -5393,22 +5545,2930 @@
       <c r="T61" s="10" t="n"/>
       <c r="U61" s="10" t="n"/>
       <c r="V61" s="10" t="n"/>
-      <c r="W61" s="12">
-        <f>SUM(L61:V61)</f>
-        <v/>
-      </c>
-      <c r="X61" s="13" t="inlineStr"/>
+      <c r="W61" s="10" t="n"/>
+      <c r="X61" s="10" t="n"/>
+      <c r="Y61" s="12">
+        <f>SUM(L61:X61)</f>
+        <v/>
+      </c>
+      <c r="Z61" s="13" t="inlineStr"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>B058</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr"/>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr"/>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J62" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K62" s="9" t="inlineStr">
+        <is>
+          <t>large hole in bladder</t>
+        </is>
+      </c>
+      <c r="L62" s="10" t="n"/>
+      <c r="M62" s="10" t="n"/>
+      <c r="N62" s="10" t="n"/>
+      <c r="O62" s="10" t="n"/>
+      <c r="P62" s="10" t="n"/>
+      <c r="Q62" s="10" t="n"/>
+      <c r="R62" s="10" t="n"/>
+      <c r="S62" s="10" t="n"/>
+      <c r="T62" s="10" t="n"/>
+      <c r="U62" s="10" t="n"/>
+      <c r="V62" s="10" t="n"/>
+      <c r="W62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X62" s="10" t="n"/>
+      <c r="Y62" s="12">
+        <f>SUM(L62:X62)</f>
+        <v/>
+      </c>
+      <c r="Z62" s="13" t="inlineStr"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>B059</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr"/>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J63" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>large hole in bladder</t>
+        </is>
+      </c>
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="10" t="n"/>
+      <c r="Q63" s="10" t="n"/>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="10" t="n"/>
+      <c r="T63" s="10" t="n"/>
+      <c r="U63" s="10" t="n"/>
+      <c r="V63" s="10" t="n"/>
+      <c r="W63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X63" s="10" t="n"/>
+      <c r="Y63" s="12">
+        <f>SUM(L63:X63)</f>
+        <v/>
+      </c>
+      <c r="Z63" s="13" t="inlineStr"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>B060</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr"/>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J64" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K64" s="9" t="inlineStr">
+        <is>
+          <t>Ureter lac</t>
+        </is>
+      </c>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" s="10" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="10" t="n"/>
+      <c r="Q64" s="10" t="n"/>
+      <c r="R64" s="10" t="n"/>
+      <c r="S64" s="10" t="n"/>
+      <c r="T64" s="10" t="n"/>
+      <c r="U64" s="10" t="n"/>
+      <c r="V64" s="10" t="n"/>
+      <c r="W64" s="10" t="n"/>
+      <c r="X64" s="10" t="n"/>
+      <c r="Y64" s="12">
+        <f>SUM(L64:X64)</f>
+        <v/>
+      </c>
+      <c r="Z64" s="13" t="inlineStr"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>B061</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr"/>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr"/>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>Ureter lac</t>
+        </is>
+      </c>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="10" t="n"/>
+      <c r="Q65" s="10" t="n"/>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
+      <c r="T65" s="10" t="n"/>
+      <c r="U65" s="10" t="n"/>
+      <c r="V65" s="10" t="n"/>
+      <c r="W65" s="10" t="n"/>
+      <c r="X65" s="10" t="n"/>
+      <c r="Y65" s="12">
+        <f>SUM(L65:X65)</f>
+        <v/>
+      </c>
+      <c r="Z65" s="13" t="inlineStr"/>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>B062</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr"/>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr"/>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J66" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K66" s="9" t="inlineStr">
+        <is>
+          <t>no damage found</t>
+        </is>
+      </c>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="10" t="n"/>
+      <c r="Q66" s="10" t="n"/>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
+      <c r="U66" s="10" t="n"/>
+      <c r="V66" s="10" t="n"/>
+      <c r="W66" s="10" t="n"/>
+      <c r="X66" s="10" t="n"/>
+      <c r="Y66" s="12">
+        <f>SUM(L66:X66)</f>
+        <v/>
+      </c>
+      <c r="Z66" s="13" t="inlineStr"/>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>B063</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr"/>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr"/>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J67" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K67" s="9" t="inlineStr">
+        <is>
+          <t>ureter not imbedded</t>
+        </is>
+      </c>
+      <c r="L67" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n"/>
+      <c r="O67" s="10" t="n"/>
+      <c r="P67" s="10" t="n"/>
+      <c r="Q67" s="10" t="n"/>
+      <c r="R67" s="10" t="n"/>
+      <c r="S67" s="10" t="n"/>
+      <c r="T67" s="10" t="n"/>
+      <c r="U67" s="10" t="n"/>
+      <c r="V67" s="10" t="n"/>
+      <c r="W67" s="10" t="n"/>
+      <c r="X67" s="10" t="n"/>
+      <c r="Y67" s="12">
+        <f>SUM(L67:X67)</f>
+        <v/>
+      </c>
+      <c r="Z67" s="13" t="inlineStr"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>B064</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr"/>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr"/>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J68" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>ureter not imbedded</t>
+        </is>
+      </c>
+      <c r="L68" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M68" s="10" t="n"/>
+      <c r="N68" s="10" t="n"/>
+      <c r="O68" s="10" t="n"/>
+      <c r="P68" s="10" t="n"/>
+      <c r="Q68" s="10" t="n"/>
+      <c r="R68" s="10" t="n"/>
+      <c r="S68" s="10" t="n"/>
+      <c r="T68" s="10" t="n"/>
+      <c r="U68" s="10" t="n"/>
+      <c r="V68" s="10" t="n"/>
+      <c r="W68" s="10" t="n"/>
+      <c r="X68" s="10" t="n"/>
+      <c r="Y68" s="12">
+        <f>SUM(L68:X68)</f>
+        <v/>
+      </c>
+      <c r="Z68" s="13" t="inlineStr"/>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>B065</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr"/>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr"/>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J69" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr">
+        <is>
+          <t>ureter not imbedded</t>
+        </is>
+      </c>
+      <c r="L69" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="10" t="n"/>
+      <c r="Q69" s="10" t="n"/>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="10" t="n"/>
+      <c r="U69" s="10" t="n"/>
+      <c r="V69" s="10" t="n"/>
+      <c r="W69" s="10" t="n"/>
+      <c r="X69" s="10" t="n"/>
+      <c r="Y69" s="12">
+        <f>SUM(L69:X69)</f>
+        <v/>
+      </c>
+      <c r="Z69" s="13" t="inlineStr"/>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>B066</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr"/>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr"/>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J70" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K70" s="9" t="inlineStr">
+        <is>
+          <t>ureter not imbedded</t>
+        </is>
+      </c>
+      <c r="L70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="10" t="n"/>
+      <c r="Q70" s="10" t="n"/>
+      <c r="R70" s="10" t="n"/>
+      <c r="S70" s="10" t="n"/>
+      <c r="T70" s="10" t="n"/>
+      <c r="U70" s="10" t="n"/>
+      <c r="V70" s="10" t="n"/>
+      <c r="W70" s="10" t="n"/>
+      <c r="X70" s="10" t="n"/>
+      <c r="Y70" s="12">
+        <f>SUM(L70:X70)</f>
+        <v/>
+      </c>
+      <c r="Z70" s="13" t="inlineStr"/>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>B067</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr"/>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr"/>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J71" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
+          <t>ureter not imbedded</t>
+        </is>
+      </c>
+      <c r="L71" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" s="10" t="n"/>
+      <c r="N71" s="10" t="n"/>
+      <c r="O71" s="10" t="n"/>
+      <c r="P71" s="10" t="n"/>
+      <c r="Q71" s="10" t="n"/>
+      <c r="R71" s="10" t="n"/>
+      <c r="S71" s="10" t="n"/>
+      <c r="T71" s="10" t="n"/>
+      <c r="U71" s="10" t="n"/>
+      <c r="V71" s="10" t="n"/>
+      <c r="W71" s="10" t="n"/>
+      <c r="X71" s="10" t="n"/>
+      <c r="Y71" s="12">
+        <f>SUM(L71:X71)</f>
+        <v/>
+      </c>
+      <c r="Z71" s="13" t="inlineStr"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>B068</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr"/>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr"/>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J72" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K72" s="9" t="inlineStr">
+        <is>
+          <t>ureter not imbedded</t>
+        </is>
+      </c>
+      <c r="L72" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="10" t="n"/>
+      <c r="Q72" s="10" t="n"/>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="10" t="n"/>
+      <c r="U72" s="10" t="n"/>
+      <c r="V72" s="10" t="n"/>
+      <c r="W72" s="10" t="n"/>
+      <c r="X72" s="10" t="n"/>
+      <c r="Y72" s="12">
+        <f>SUM(L72:X72)</f>
+        <v/>
+      </c>
+      <c r="Z72" s="13" t="inlineStr"/>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>B069</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr"/>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr"/>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J73" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K73" s="9" t="inlineStr">
+        <is>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
+      <c r="L73" s="10" t="n"/>
+      <c r="M73" s="10" t="n"/>
+      <c r="N73" s="10" t="n"/>
+      <c r="O73" s="10" t="n"/>
+      <c r="P73" s="10" t="n"/>
+      <c r="Q73" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R73" s="10" t="n"/>
+      <c r="S73" s="10" t="n"/>
+      <c r="T73" s="10" t="n"/>
+      <c r="U73" s="10" t="n"/>
+      <c r="V73" s="10" t="n"/>
+      <c r="W73" s="10" t="n"/>
+      <c r="X73" s="10" t="n"/>
+      <c r="Y73" s="12">
+        <f>SUM(L73:X73)</f>
+        <v/>
+      </c>
+      <c r="Z73" s="13" t="inlineStr"/>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>B070</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr"/>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr"/>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J74" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K74" s="9" t="inlineStr">
+        <is>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
+      <c r="L74" s="10" t="n"/>
+      <c r="M74" s="10" t="n"/>
+      <c r="N74" s="10" t="n"/>
+      <c r="O74" s="10" t="n"/>
+      <c r="P74" s="10" t="n"/>
+      <c r="Q74" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R74" s="10" t="n"/>
+      <c r="S74" s="10" t="n"/>
+      <c r="T74" s="10" t="n"/>
+      <c r="U74" s="10" t="n"/>
+      <c r="V74" s="10" t="n"/>
+      <c r="W74" s="10" t="n"/>
+      <c r="X74" s="10" t="n"/>
+      <c r="Y74" s="12">
+        <f>SUM(L74:X74)</f>
+        <v/>
+      </c>
+      <c r="Z74" s="13" t="inlineStr"/>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>B071</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr"/>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr"/>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J75" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K75" s="9" t="inlineStr">
+        <is>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
+      <c r="L75" s="10" t="n"/>
+      <c r="M75" s="10" t="n"/>
+      <c r="N75" s="10" t="n"/>
+      <c r="O75" s="10" t="n"/>
+      <c r="P75" s="10" t="n"/>
+      <c r="Q75" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" s="10" t="n"/>
+      <c r="S75" s="10" t="n"/>
+      <c r="T75" s="10" t="n"/>
+      <c r="U75" s="10" t="n"/>
+      <c r="V75" s="10" t="n"/>
+      <c r="W75" s="10" t="n"/>
+      <c r="X75" s="10" t="n"/>
+      <c r="Y75" s="12">
+        <f>SUM(L75:X75)</f>
+        <v/>
+      </c>
+      <c r="Z75" s="13" t="inlineStr"/>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>B072</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr"/>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr"/>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J76" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K76" s="9" t="inlineStr">
+        <is>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
+      <c r="L76" s="10" t="n"/>
+      <c r="M76" s="10" t="n"/>
+      <c r="N76" s="10" t="n"/>
+      <c r="O76" s="10" t="n"/>
+      <c r="P76" s="10" t="n"/>
+      <c r="Q76" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R76" s="10" t="n"/>
+      <c r="S76" s="10" t="n"/>
+      <c r="T76" s="10" t="n"/>
+      <c r="U76" s="10" t="n"/>
+      <c r="V76" s="10" t="n"/>
+      <c r="W76" s="10" t="n"/>
+      <c r="X76" s="10" t="n"/>
+      <c r="Y76" s="12">
+        <f>SUM(L76:X76)</f>
+        <v/>
+      </c>
+      <c r="Z76" s="13" t="inlineStr"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>B073</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr"/>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J77" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K77" s="9" t="inlineStr">
+        <is>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
+      <c r="L77" s="10" t="n"/>
+      <c r="M77" s="10" t="n"/>
+      <c r="N77" s="10" t="n"/>
+      <c r="O77" s="10" t="n"/>
+      <c r="P77" s="10" t="n"/>
+      <c r="Q77" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R77" s="10" t="n"/>
+      <c r="S77" s="10" t="n"/>
+      <c r="T77" s="10" t="n"/>
+      <c r="U77" s="10" t="n"/>
+      <c r="V77" s="10" t="n"/>
+      <c r="W77" s="10" t="n"/>
+      <c r="X77" s="10" t="n"/>
+      <c r="Y77" s="12">
+        <f>SUM(L77:X77)</f>
+        <v/>
+      </c>
+      <c r="Z77" s="13" t="inlineStr"/>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>B074</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr"/>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H78" s="7" t="inlineStr"/>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J78" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K78" s="9" t="inlineStr">
+        <is>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
+      <c r="L78" s="10" t="n"/>
+      <c r="M78" s="10" t="n"/>
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="10" t="n"/>
+      <c r="Q78" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R78" s="10" t="n"/>
+      <c r="S78" s="10" t="n"/>
+      <c r="T78" s="10" t="n"/>
+      <c r="U78" s="10" t="n"/>
+      <c r="V78" s="10" t="n"/>
+      <c r="W78" s="10" t="n"/>
+      <c r="X78" s="10" t="n"/>
+      <c r="Y78" s="12">
+        <f>SUM(L78:X78)</f>
+        <v/>
+      </c>
+      <c r="Z78" s="13" t="inlineStr"/>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>B075</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr"/>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr"/>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J79" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K79" s="9" t="inlineStr">
+        <is>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
+      <c r="L79" s="10" t="n"/>
+      <c r="M79" s="10" t="n"/>
+      <c r="N79" s="10" t="n"/>
+      <c r="O79" s="10" t="n"/>
+      <c r="P79" s="10" t="n"/>
+      <c r="Q79" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R79" s="10" t="n"/>
+      <c r="S79" s="10" t="n"/>
+      <c r="T79" s="10" t="n"/>
+      <c r="U79" s="10" t="n"/>
+      <c r="V79" s="10" t="n"/>
+      <c r="W79" s="10" t="n"/>
+      <c r="X79" s="10" t="n"/>
+      <c r="Y79" s="12">
+        <f>SUM(L79:X79)</f>
+        <v/>
+      </c>
+      <c r="Z79" s="13" t="inlineStr"/>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>B076</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr"/>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H80" s="7" t="inlineStr"/>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J80" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K80" s="9" t="inlineStr">
+        <is>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
+      <c r="L80" s="10" t="n"/>
+      <c r="M80" s="10" t="n"/>
+      <c r="N80" s="10" t="n"/>
+      <c r="O80" s="10" t="n"/>
+      <c r="P80" s="10" t="n"/>
+      <c r="Q80" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R80" s="10" t="n"/>
+      <c r="S80" s="10" t="n"/>
+      <c r="T80" s="10" t="n"/>
+      <c r="U80" s="10" t="n"/>
+      <c r="V80" s="10" t="n"/>
+      <c r="W80" s="10" t="n"/>
+      <c r="X80" s="10" t="n"/>
+      <c r="Y80" s="12">
+        <f>SUM(L80:X80)</f>
+        <v/>
+      </c>
+      <c r="Z80" s="13" t="inlineStr"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>B077</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr"/>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr"/>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J81" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K81" s="9" t="inlineStr">
+        <is>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
+      <c r="L81" s="10" t="n"/>
+      <c r="M81" s="10" t="n"/>
+      <c r="N81" s="10" t="n"/>
+      <c r="O81" s="10" t="n"/>
+      <c r="P81" s="10" t="n"/>
+      <c r="Q81" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R81" s="10" t="n"/>
+      <c r="S81" s="10" t="n"/>
+      <c r="T81" s="10" t="n"/>
+      <c r="U81" s="10" t="n"/>
+      <c r="V81" s="10" t="n"/>
+      <c r="W81" s="10" t="n"/>
+      <c r="X81" s="10" t="n"/>
+      <c r="Y81" s="12">
+        <f>SUM(L81:X81)</f>
+        <v/>
+      </c>
+      <c r="Z81" s="13" t="inlineStr"/>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>B078</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr"/>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr"/>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J82" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K82" s="9" t="inlineStr">
+        <is>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
+      <c r="L82" s="10" t="n"/>
+      <c r="M82" s="10" t="n"/>
+      <c r="N82" s="10" t="n"/>
+      <c r="O82" s="10" t="n"/>
+      <c r="P82" s="10" t="n"/>
+      <c r="Q82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R82" s="10" t="n"/>
+      <c r="S82" s="10" t="n"/>
+      <c r="T82" s="10" t="n"/>
+      <c r="U82" s="10" t="n"/>
+      <c r="V82" s="10" t="n"/>
+      <c r="W82" s="10" t="n"/>
+      <c r="X82" s="10" t="n"/>
+      <c r="Y82" s="12">
+        <f>SUM(L82:X82)</f>
+        <v/>
+      </c>
+      <c r="Z82" s="13" t="inlineStr"/>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>B079</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr"/>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J83" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K83" s="9" t="inlineStr">
+        <is>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
+      <c r="L83" s="10" t="n"/>
+      <c r="M83" s="10" t="n"/>
+      <c r="N83" s="10" t="n"/>
+      <c r="O83" s="10" t="n"/>
+      <c r="P83" s="10" t="n"/>
+      <c r="Q83" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R83" s="10" t="n"/>
+      <c r="S83" s="10" t="n"/>
+      <c r="T83" s="10" t="n"/>
+      <c r="U83" s="10" t="n"/>
+      <c r="V83" s="10" t="n"/>
+      <c r="W83" s="10" t="n"/>
+      <c r="X83" s="10" t="n"/>
+      <c r="Y83" s="12">
+        <f>SUM(L83:X83)</f>
+        <v/>
+      </c>
+      <c r="Z83" s="13" t="inlineStr"/>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>B080</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr"/>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr"/>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J84" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K84" s="9" t="inlineStr">
+        <is>
+          <t>hole in mesentary membrane in critical area greater than 1.5"</t>
+        </is>
+      </c>
+      <c r="L84" s="10" t="n"/>
+      <c r="M84" s="10" t="n"/>
+      <c r="N84" s="10" t="n"/>
+      <c r="O84" s="10" t="n"/>
+      <c r="P84" s="10" t="n"/>
+      <c r="Q84" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R84" s="10" t="n"/>
+      <c r="S84" s="10" t="n"/>
+      <c r="T84" s="10" t="n"/>
+      <c r="U84" s="10" t="n"/>
+      <c r="V84" s="10" t="n"/>
+      <c r="W84" s="10" t="n"/>
+      <c r="X84" s="10" t="n"/>
+      <c r="Y84" s="12">
+        <f>SUM(L84:X84)</f>
+        <v/>
+      </c>
+      <c r="Z84" s="13" t="inlineStr"/>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>B081</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr"/>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr"/>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J85" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K85" s="9" t="inlineStr">
+        <is>
+          <t>Block too short</t>
+        </is>
+      </c>
+      <c r="L85" s="10" t="n"/>
+      <c r="M85" s="10" t="n"/>
+      <c r="N85" s="10" t="n"/>
+      <c r="O85" s="10" t="n"/>
+      <c r="P85" s="10" t="n"/>
+      <c r="Q85" s="10" t="n"/>
+      <c r="R85" s="10" t="n"/>
+      <c r="S85" s="10" t="n"/>
+      <c r="T85" s="10" t="n"/>
+      <c r="U85" s="10" t="n"/>
+      <c r="V85" s="10" t="n"/>
+      <c r="W85" s="10" t="n"/>
+      <c r="X85" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y85" s="12">
+        <f>SUM(L85:X85)</f>
+        <v/>
+      </c>
+      <c r="Z85" s="13" t="inlineStr"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>B082</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr"/>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr"/>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J86" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K86" s="9" t="inlineStr">
+        <is>
+          <t>Block too short</t>
+        </is>
+      </c>
+      <c r="L86" s="10" t="n"/>
+      <c r="M86" s="10" t="n"/>
+      <c r="N86" s="10" t="n"/>
+      <c r="O86" s="10" t="n"/>
+      <c r="P86" s="10" t="n"/>
+      <c r="Q86" s="10" t="n"/>
+      <c r="R86" s="10" t="n"/>
+      <c r="S86" s="10" t="n"/>
+      <c r="T86" s="10" t="n"/>
+      <c r="U86" s="10" t="n"/>
+      <c r="V86" s="10" t="n"/>
+      <c r="W86" s="10" t="n"/>
+      <c r="X86" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y86" s="12">
+        <f>SUM(L86:X86)</f>
+        <v/>
+      </c>
+      <c r="Z86" s="13" t="inlineStr"/>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>B083</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr"/>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J87" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K87" s="9" t="inlineStr">
+        <is>
+          <t>Block too short</t>
+        </is>
+      </c>
+      <c r="L87" s="10" t="n"/>
+      <c r="M87" s="10" t="n"/>
+      <c r="N87" s="10" t="n"/>
+      <c r="O87" s="10" t="n"/>
+      <c r="P87" s="10" t="n"/>
+      <c r="Q87" s="10" t="n"/>
+      <c r="R87" s="10" t="n"/>
+      <c r="S87" s="10" t="n"/>
+      <c r="T87" s="10" t="n"/>
+      <c r="U87" s="10" t="n"/>
+      <c r="V87" s="10" t="n"/>
+      <c r="W87" s="10" t="n"/>
+      <c r="X87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y87" s="12">
+        <f>SUM(L87:X87)</f>
+        <v/>
+      </c>
+      <c r="Z87" s="13" t="inlineStr"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>B084</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr"/>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J88" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K88" s="9" t="inlineStr">
+        <is>
+          <t>Block too short</t>
+        </is>
+      </c>
+      <c r="L88" s="10" t="n"/>
+      <c r="M88" s="10" t="n"/>
+      <c r="N88" s="10" t="n"/>
+      <c r="O88" s="10" t="n"/>
+      <c r="P88" s="10" t="n"/>
+      <c r="Q88" s="10" t="n"/>
+      <c r="R88" s="10" t="n"/>
+      <c r="S88" s="10" t="n"/>
+      <c r="T88" s="10" t="n"/>
+      <c r="U88" s="10" t="n"/>
+      <c r="V88" s="10" t="n"/>
+      <c r="W88" s="10" t="n"/>
+      <c r="X88" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y88" s="12">
+        <f>SUM(L88:X88)</f>
+        <v/>
+      </c>
+      <c r="Z88" s="13" t="inlineStr"/>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>B085</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr"/>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr"/>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J89" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K89" s="9" t="inlineStr">
+        <is>
+          <t>Block too short</t>
+        </is>
+      </c>
+      <c r="L89" s="10" t="n"/>
+      <c r="M89" s="10" t="n"/>
+      <c r="N89" s="10" t="n"/>
+      <c r="O89" s="10" t="n"/>
+      <c r="P89" s="10" t="n"/>
+      <c r="Q89" s="10" t="n"/>
+      <c r="R89" s="10" t="n"/>
+      <c r="S89" s="10" t="n"/>
+      <c r="T89" s="10" t="n"/>
+      <c r="U89" s="10" t="n"/>
+      <c r="V89" s="10" t="n"/>
+      <c r="W89" s="10" t="n"/>
+      <c r="X89" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y89" s="12">
+        <f>SUM(L89:X89)</f>
+        <v/>
+      </c>
+      <c r="Z89" s="13" t="inlineStr"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>B086</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr"/>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="inlineStr"/>
+      <c r="I90" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J90" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K90" s="9" t="inlineStr">
+        <is>
+          <t>Block too short</t>
+        </is>
+      </c>
+      <c r="L90" s="10" t="n"/>
+      <c r="M90" s="10" t="n"/>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="10" t="n"/>
+      <c r="R90" s="10" t="n"/>
+      <c r="S90" s="10" t="n"/>
+      <c r="T90" s="10" t="n"/>
+      <c r="U90" s="10" t="n"/>
+      <c r="V90" s="10" t="n"/>
+      <c r="W90" s="10" t="n"/>
+      <c r="X90" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y90" s="12">
+        <f>SUM(L90:X90)</f>
+        <v/>
+      </c>
+      <c r="Z90" s="13" t="inlineStr"/>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>B087</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr"/>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr"/>
+      <c r="I91" s="7" t="inlineStr">
+        <is>
+          <t>Pelvic block</t>
+        </is>
+      </c>
+      <c r="J91" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K91" s="9" t="inlineStr">
+        <is>
+          <t>laceration in urethra</t>
+        </is>
+      </c>
+      <c r="L91" s="10" t="n"/>
+      <c r="M91" s="10" t="n"/>
+      <c r="N91" s="10" t="n"/>
+      <c r="O91" s="10" t="n"/>
+      <c r="P91" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q91" s="10" t="n"/>
+      <c r="R91" s="10" t="n"/>
+      <c r="S91" s="10" t="n"/>
+      <c r="T91" s="10" t="n"/>
+      <c r="U91" s="10" t="n"/>
+      <c r="V91" s="10" t="n"/>
+      <c r="W91" s="10" t="n"/>
+      <c r="X91" s="10" t="n"/>
+      <c r="Y91" s="12">
+        <f>SUM(L91:X91)</f>
+        <v/>
+      </c>
+      <c r="Z91" s="15" t="inlineStr">
+        <is>
+          <t>Sheet's handwritten total read '1 Pass / 22 failures'; per-row entries sum to 29 fails (used here).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>B088</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr"/>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>Toni</t>
+        </is>
+      </c>
+      <c r="H92" s="7" t="inlineStr"/>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J92" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K92" s="9" t="inlineStr">
+        <is>
+          <t>bowel is cut open</t>
+        </is>
+      </c>
+      <c r="L92" s="10" t="n"/>
+      <c r="M92" s="10" t="n"/>
+      <c r="N92" s="10" t="n"/>
+      <c r="O92" s="10" t="n"/>
+      <c r="P92" s="10" t="n"/>
+      <c r="Q92" s="10" t="n"/>
+      <c r="R92" s="10" t="n"/>
+      <c r="S92" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T92" s="10" t="n"/>
+      <c r="U92" s="10" t="n"/>
+      <c r="V92" s="10" t="n"/>
+      <c r="W92" s="10" t="n"/>
+      <c r="X92" s="10" t="n"/>
+      <c r="Y92" s="12">
+        <f>SUM(L92:X92)</f>
+        <v/>
+      </c>
+      <c r="Z92" s="13" t="inlineStr"/>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>B089</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr"/>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>Toni</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr"/>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J93" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K93" s="9" t="inlineStr">
+        <is>
+          <t>membrane damage greater than .5" in critical area</t>
+        </is>
+      </c>
+      <c r="L93" s="10" t="n"/>
+      <c r="M93" s="10" t="n"/>
+      <c r="N93" s="10" t="n"/>
+      <c r="O93" s="10" t="n"/>
+      <c r="P93" s="10" t="n"/>
+      <c r="Q93" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R93" s="10" t="n"/>
+      <c r="S93" s="10" t="n"/>
+      <c r="T93" s="10" t="n"/>
+      <c r="U93" s="10" t="n"/>
+      <c r="V93" s="10" t="n"/>
+      <c r="W93" s="10" t="n"/>
+      <c r="X93" s="10" t="n"/>
+      <c r="Y93" s="12">
+        <f>SUM(L93:X93)</f>
+        <v/>
+      </c>
+      <c r="Z93" s="13" t="inlineStr"/>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>B090</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr"/>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>Toni</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr"/>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J94" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K94" s="9" t="inlineStr">
+        <is>
+          <t>membrane damage greater than .5" in critical area</t>
+        </is>
+      </c>
+      <c r="L94" s="10" t="n"/>
+      <c r="M94" s="10" t="n"/>
+      <c r="N94" s="10" t="n"/>
+      <c r="O94" s="10" t="n"/>
+      <c r="P94" s="10" t="n"/>
+      <c r="Q94" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R94" s="10" t="n"/>
+      <c r="S94" s="10" t="n"/>
+      <c r="T94" s="10" t="n"/>
+      <c r="U94" s="10" t="n"/>
+      <c r="V94" s="10" t="n"/>
+      <c r="W94" s="10" t="n"/>
+      <c r="X94" s="10" t="n"/>
+      <c r="Y94" s="12">
+        <f>SUM(L94:X94)</f>
+        <v/>
+      </c>
+      <c r="Z94" s="13" t="inlineStr"/>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>B091</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr"/>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>Toni</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J95" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K95" s="9" t="inlineStr">
+        <is>
+          <t>membrane damage greater than .5" in critical area</t>
+        </is>
+      </c>
+      <c r="L95" s="10" t="n"/>
+      <c r="M95" s="10" t="n"/>
+      <c r="N95" s="10" t="n"/>
+      <c r="O95" s="10" t="n"/>
+      <c r="P95" s="10" t="n"/>
+      <c r="Q95" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R95" s="10" t="n"/>
+      <c r="S95" s="10" t="n"/>
+      <c r="T95" s="10" t="n"/>
+      <c r="U95" s="10" t="n"/>
+      <c r="V95" s="10" t="n"/>
+      <c r="W95" s="10" t="n"/>
+      <c r="X95" s="10" t="n"/>
+      <c r="Y95" s="12">
+        <f>SUM(L95:X95)</f>
+        <v/>
+      </c>
+      <c r="Z95" s="13" t="inlineStr"/>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>B092</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr"/>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>Toni</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="inlineStr"/>
+      <c r="I96" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J96" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K96" s="9" t="inlineStr">
+        <is>
+          <t>membrane damage greater than .5" in critical area</t>
+        </is>
+      </c>
+      <c r="L96" s="10" t="n"/>
+      <c r="M96" s="10" t="n"/>
+      <c r="N96" s="10" t="n"/>
+      <c r="O96" s="10" t="n"/>
+      <c r="P96" s="10" t="n"/>
+      <c r="Q96" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R96" s="10" t="n"/>
+      <c r="S96" s="10" t="n"/>
+      <c r="T96" s="10" t="n"/>
+      <c r="U96" s="10" t="n"/>
+      <c r="V96" s="10" t="n"/>
+      <c r="W96" s="10" t="n"/>
+      <c r="X96" s="10" t="n"/>
+      <c r="Y96" s="12">
+        <f>SUM(L96:X96)</f>
+        <v/>
+      </c>
+      <c r="Z96" s="13" t="inlineStr"/>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>B093</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr"/>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>Toni</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J97" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K97" s="9" t="inlineStr">
+        <is>
+          <t>membrane damage greater than .5" in critical area</t>
+        </is>
+      </c>
+      <c r="L97" s="10" t="n"/>
+      <c r="M97" s="10" t="n"/>
+      <c r="N97" s="10" t="n"/>
+      <c r="O97" s="10" t="n"/>
+      <c r="P97" s="10" t="n"/>
+      <c r="Q97" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R97" s="10" t="n"/>
+      <c r="S97" s="10" t="n"/>
+      <c r="T97" s="10" t="n"/>
+      <c r="U97" s="10" t="n"/>
+      <c r="V97" s="10" t="n"/>
+      <c r="W97" s="10" t="n"/>
+      <c r="X97" s="10" t="n"/>
+      <c r="Y97" s="12">
+        <f>SUM(L97:X97)</f>
+        <v/>
+      </c>
+      <c r="Z97" s="13" t="inlineStr"/>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>B094</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr"/>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>Toni</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="inlineStr"/>
+      <c r="I98" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J98" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K98" s="9" t="inlineStr">
+        <is>
+          <t>urethra cut, bowel damaged</t>
+        </is>
+      </c>
+      <c r="L98" s="10" t="n"/>
+      <c r="M98" s="10" t="n"/>
+      <c r="N98" s="10" t="n"/>
+      <c r="O98" s="10" t="n"/>
+      <c r="P98" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q98" s="10" t="n"/>
+      <c r="R98" s="10" t="n"/>
+      <c r="S98" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T98" s="10" t="n"/>
+      <c r="U98" s="10" t="n"/>
+      <c r="V98" s="10" t="n"/>
+      <c r="W98" s="10" t="n"/>
+      <c r="X98" s="10" t="n"/>
+      <c r="Y98" s="12">
+        <f>SUM(L98:X98)</f>
+        <v/>
+      </c>
+      <c r="Z98" s="13" t="inlineStr"/>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>B095</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr"/>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>Toni</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr"/>
+      <c r="I99" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J99" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K99" s="9" t="inlineStr">
+        <is>
+          <t>ureter is damaged and cut off</t>
+        </is>
+      </c>
+      <c r="L99" s="10" t="n"/>
+      <c r="M99" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N99" s="10" t="n"/>
+      <c r="O99" s="10" t="n"/>
+      <c r="P99" s="10" t="n"/>
+      <c r="Q99" s="10" t="n"/>
+      <c r="R99" s="10" t="n"/>
+      <c r="S99" s="10" t="n"/>
+      <c r="T99" s="10" t="n"/>
+      <c r="U99" s="10" t="n"/>
+      <c r="V99" s="10" t="n"/>
+      <c r="W99" s="10" t="n"/>
+      <c r="X99" s="10" t="n"/>
+      <c r="Y99" s="12">
+        <f>SUM(L99:X99)</f>
+        <v/>
+      </c>
+      <c r="Z99" s="13" t="inlineStr"/>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>B096</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr"/>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>Toni</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="inlineStr"/>
+      <c r="I100" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J100" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K100" s="9" t="inlineStr">
+        <is>
+          <t>ureter is damaged and cut off</t>
+        </is>
+      </c>
+      <c r="L100" s="10" t="n"/>
+      <c r="M100" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N100" s="10" t="n"/>
+      <c r="O100" s="10" t="n"/>
+      <c r="P100" s="10" t="n"/>
+      <c r="Q100" s="10" t="n"/>
+      <c r="R100" s="10" t="n"/>
+      <c r="S100" s="10" t="n"/>
+      <c r="T100" s="10" t="n"/>
+      <c r="U100" s="10" t="n"/>
+      <c r="V100" s="10" t="n"/>
+      <c r="W100" s="10" t="n"/>
+      <c r="X100" s="10" t="n"/>
+      <c r="Y100" s="12">
+        <f>SUM(L100:X100)</f>
+        <v/>
+      </c>
+      <c r="Z100" s="13" t="inlineStr"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>B097</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr"/>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>Toni</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr"/>
+      <c r="I101" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J101" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K101" s="9" t="inlineStr">
+        <is>
+          <t>bladder is cut open</t>
+        </is>
+      </c>
+      <c r="L101" s="10" t="n"/>
+      <c r="M101" s="10" t="n"/>
+      <c r="N101" s="10" t="n"/>
+      <c r="O101" s="10" t="n"/>
+      <c r="P101" s="10" t="n"/>
+      <c r="Q101" s="10" t="n"/>
+      <c r="R101" s="10" t="n"/>
+      <c r="S101" s="10" t="n"/>
+      <c r="T101" s="10" t="n"/>
+      <c r="U101" s="10" t="n"/>
+      <c r="V101" s="10" t="n"/>
+      <c r="W101" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X101" s="10" t="n"/>
+      <c r="Y101" s="12">
+        <f>SUM(L101:X101)</f>
+        <v/>
+      </c>
+      <c r="Z101" s="13" t="inlineStr"/>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>B098</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr"/>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>Toni</t>
+        </is>
+      </c>
+      <c r="H102" s="7" t="inlineStr"/>
+      <c r="I102" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J102" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K102" s="9" t="inlineStr">
+        <is>
+          <t>bladder is cut open, urethra seperated, membrane damage greater than .5"</t>
+        </is>
+      </c>
+      <c r="L102" s="10" t="n"/>
+      <c r="M102" s="10" t="n"/>
+      <c r="N102" s="10" t="n"/>
+      <c r="O102" s="10" t="n"/>
+      <c r="P102" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q102" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R102" s="10" t="n"/>
+      <c r="S102" s="10" t="n"/>
+      <c r="T102" s="10" t="n"/>
+      <c r="U102" s="10" t="n"/>
+      <c r="V102" s="10" t="n"/>
+      <c r="W102" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X102" s="10" t="n"/>
+      <c r="Y102" s="12">
+        <f>SUM(L102:X102)</f>
+        <v/>
+      </c>
+      <c r="Z102" s="13" t="inlineStr"/>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>B099</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr"/>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>Toni</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr"/>
+      <c r="I103" s="7" t="inlineStr">
+        <is>
+          <t>Tiss, porcine, fem, Pelvic block</t>
+        </is>
+      </c>
+      <c r="J103" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="K103" s="9" t="inlineStr">
+        <is>
+          <t>short block</t>
+        </is>
+      </c>
+      <c r="L103" s="10" t="n"/>
+      <c r="M103" s="10" t="n"/>
+      <c r="N103" s="10" t="n"/>
+      <c r="O103" s="10" t="n"/>
+      <c r="P103" s="10" t="n"/>
+      <c r="Q103" s="10" t="n"/>
+      <c r="R103" s="10" t="n"/>
+      <c r="S103" s="10" t="n"/>
+      <c r="T103" s="10" t="n"/>
+      <c r="U103" s="10" t="n"/>
+      <c r="V103" s="10" t="n"/>
+      <c r="W103" s="10" t="n"/>
+      <c r="X103" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y103" s="12">
+        <f>SUM(L103:X103)</f>
+        <v/>
+      </c>
+      <c r="Z103" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:X2"/>
-    <mergeCell ref="A1:X1"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A2:Z2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="J5:J405" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail"</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:V405" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:X405" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5422,7 +8482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5703,12 +8763,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Urethra breach (cut / laceration / hole)</t>
+          <t>Urethra breach (cut / laceration / hole / separation)</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Urethra transected, lacerated or perforated (incl. hole in distal urethra).</t>
+          <t>Urethra transected, lacerated, perforated or separated (incl. hole in distal urethra).</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
@@ -6030,6 +9090,102 @@
         </is>
       </c>
       <c r="J15" s="18" t="inlineStr"/>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Bladder cut / hole (breach)</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Bladder wall cut open or holed. Urine-contamination risk. Distinct from D7 (deformed) &amp; D11 (neck separation).</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Evisceration knife / splitting saw</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>S3 Evisceration</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Machine / Method</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Knife nick or saw path opens the bladder; or over-distended bladder ruptures under handling.</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Protect bladder during gut removal; verify saw path; manage bladder fill (lairage/water timing).</t>
+        </is>
+      </c>
+      <c r="J16" s="18" t="inlineStr"/>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Block too short / undersized</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Harvested pelvic block dimensionally too short / fails the length template (insufficient tissue retained).</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Pelvic-block separation cut (cut-boundary placement)</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>S3 Evisceration</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>Method / Man</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Separation cut placed too close; insufficient block length retained vs template/spec.</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Define &amp; train pelvic-block cut boundaries / minimum length; cut to template; provide a length gauge.</t>
+        </is>
+      </c>
+      <c r="J17" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6046,7 +9202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6131,11 +9287,11 @@
         </is>
       </c>
       <c r="D6" s="12">
-        <f>SUM('Inspection Log'!Q5:Q461)</f>
+        <f>SUM('Inspection Log'!Q5:Q503)</f>
         <v/>
       </c>
       <c r="E6" s="25">
-        <f>D6/SUM('Inspection Log'!L5:V461)</f>
+        <f>D6/SUM('Inspection Log'!L5:X503)</f>
         <v/>
       </c>
       <c r="F6" s="25">
@@ -6166,11 +9322,11 @@
         </is>
       </c>
       <c r="D7" s="12">
-        <f>SUM('Inspection Log'!L5:L461)</f>
+        <f>SUM('Inspection Log'!L5:L503)</f>
         <v/>
       </c>
       <c r="E7" s="25">
-        <f>D7/SUM('Inspection Log'!L5:V461)</f>
+        <f>D7/SUM('Inspection Log'!L5:X503)</f>
         <v/>
       </c>
       <c r="F7" s="25">
@@ -6197,15 +9353,15 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>Urethra breach (cut / laceration / hole)</t>
+          <t>Urethra breach (cut / laceration / hole / separation)</t>
         </is>
       </c>
       <c r="D8" s="12">
-        <f>SUM('Inspection Log'!P5:P461)</f>
+        <f>SUM('Inspection Log'!P5:P503)</f>
         <v/>
       </c>
       <c r="E8" s="25">
-        <f>D8/SUM('Inspection Log'!L5:V461)</f>
+        <f>D8/SUM('Inspection Log'!L5:X503)</f>
         <v/>
       </c>
       <c r="F8" s="25">
@@ -6227,20 +9383,20 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>Suspensory ligaments damaged</t>
+          <t>Bowel / colon / rectum breach</t>
         </is>
       </c>
       <c r="D9" s="12">
-        <f>SUM('Inspection Log'!O5:O461)</f>
+        <f>SUM('Inspection Log'!S5:S503)</f>
         <v/>
       </c>
       <c r="E9" s="25">
-        <f>D9/SUM('Inspection Log'!L5:V461)</f>
+        <f>D9/SUM('Inspection Log'!L5:X503)</f>
         <v/>
       </c>
       <c r="F9" s="25">
@@ -6249,7 +9405,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>D4 · Susp. ligament</t>
+          <t>D8 · Bowel/colon</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -6262,20 +9418,20 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>D8</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>Bowel / colon / rectum breach</t>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>Suspensory ligaments damaged</t>
         </is>
       </c>
       <c r="D10" s="12">
-        <f>SUM('Inspection Log'!S5:S461)</f>
+        <f>SUM('Inspection Log'!O5:O503)</f>
         <v/>
       </c>
       <c r="E10" s="25">
-        <f>D10/SUM('Inspection Log'!L5:V461)</f>
+        <f>D10/SUM('Inspection Log'!L5:X503)</f>
         <v/>
       </c>
       <c r="F10" s="25">
@@ -6284,7 +9440,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>D8 · Bowel/colon</t>
+          <t>D4 · Susp. ligament</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -6306,11 +9462,11 @@
         </is>
       </c>
       <c r="D11" s="12">
-        <f>SUM('Inspection Log'!M5:M461)</f>
+        <f>SUM('Inspection Log'!M5:M503)</f>
         <v/>
       </c>
       <c r="E11" s="25">
-        <f>D11/SUM('Inspection Log'!L5:V461)</f>
+        <f>D11/SUM('Inspection Log'!L5:X503)</f>
         <v/>
       </c>
       <c r="F11" s="25">
@@ -6332,20 +9488,20 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
-          <t>Ureter missing</t>
+          <t>Block too short / undersized</t>
         </is>
       </c>
       <c r="D12" s="12">
-        <f>SUM('Inspection Log'!N5:N461)</f>
+        <f>SUM('Inspection Log'!X5:X503)</f>
         <v/>
       </c>
       <c r="E12" s="25">
-        <f>D12/SUM('Inspection Log'!L5:V461)</f>
+        <f>D12/SUM('Inspection Log'!L5:X503)</f>
         <v/>
       </c>
       <c r="F12" s="25">
@@ -6354,7 +9510,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>D3 · Ureter missing</t>
+          <t>D13 · Block too short</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -6367,20 +9523,20 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>Bladder deformed / deformed attachment</t>
+          <t>Bladder cut / hole (breach)</t>
         </is>
       </c>
       <c r="D13" s="12">
-        <f>SUM('Inspection Log'!R5:R461)</f>
+        <f>SUM('Inspection Log'!W5:W503)</f>
         <v/>
       </c>
       <c r="E13" s="25">
-        <f>D13/SUM('Inspection Log'!L5:V461)</f>
+        <f>D13/SUM('Inspection Log'!L5:X503)</f>
         <v/>
       </c>
       <c r="F13" s="25">
@@ -6389,7 +9545,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>D7 · Bladder def.</t>
+          <t>D12 · Bladder breach</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -6402,20 +9558,20 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>Blood clots</t>
+          <t>Ureter missing</t>
         </is>
       </c>
       <c r="D14" s="12">
-        <f>SUM('Inspection Log'!T5:T461)</f>
+        <f>SUM('Inspection Log'!N5:N503)</f>
         <v/>
       </c>
       <c r="E14" s="25">
-        <f>D14/SUM('Inspection Log'!L5:V461)</f>
+        <f>D14/SUM('Inspection Log'!L5:X503)</f>
         <v/>
       </c>
       <c r="F14" s="25">
@@ -6424,7 +9580,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>D9 · Blood clots</t>
+          <t>D3 · Ureter missing</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -6437,20 +9593,20 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
-          <t>Broad ligament hole / tear</t>
+          <t>Bladder deformed / deformed attachment</t>
         </is>
       </c>
       <c r="D15" s="12">
-        <f>SUM('Inspection Log'!U5:U461)</f>
+        <f>SUM('Inspection Log'!R5:R503)</f>
         <v/>
       </c>
       <c r="E15" s="25">
-        <f>D15/SUM('Inspection Log'!L5:V461)</f>
+        <f>D15/SUM('Inspection Log'!L5:X503)</f>
         <v/>
       </c>
       <c r="F15" s="25">
@@ -6459,7 +9615,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>D10 · Broad ligament</t>
+          <t>D7 · Bladder def.</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -6472,20 +9628,20 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="C16" s="26" t="inlineStr">
         <is>
-          <t>Bladder neck separation</t>
+          <t>Blood clots</t>
         </is>
       </c>
       <c r="D16" s="12">
-        <f>SUM('Inspection Log'!V5:V461)</f>
+        <f>SUM('Inspection Log'!T5:T503)</f>
         <v/>
       </c>
       <c r="E16" s="25">
-        <f>D16/SUM('Inspection Log'!L5:V461)</f>
+        <f>D16/SUM('Inspection Log'!L5:X503)</f>
         <v/>
       </c>
       <c r="F16" s="25">
@@ -6494,7 +9650,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>D11 · Bladder neck sep.</t>
+          <t>D9 · Blood clots</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -6502,177 +9658,247 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="n"/>
-      <c r="B17" s="27" t="n"/>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="A17" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>Broad ligament hole / tear</t>
+        </is>
+      </c>
+      <c r="D17" s="12">
+        <f>SUM('Inspection Log'!U5:U503)</f>
+        <v/>
+      </c>
+      <c r="E17" s="25">
+        <f>D17/SUM('Inspection Log'!L5:X503)</f>
+        <v/>
+      </c>
+      <c r="F17" s="25">
+        <f>F16+E17</f>
+        <v/>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>D10 · Broad ligament</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>D11</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Bladder neck separation</t>
+        </is>
+      </c>
+      <c r="D18" s="12">
+        <f>SUM('Inspection Log'!V5:V503)</f>
+        <v/>
+      </c>
+      <c r="E18" s="25">
+        <f>D18/SUM('Inspection Log'!L5:X503)</f>
+        <v/>
+      </c>
+      <c r="F18" s="25">
+        <f>F17+E18</f>
+        <v/>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>D11 · Bladder neck sep.</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="n"/>
+      <c r="B19" s="27" t="n"/>
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D17" s="29">
-        <f>SUM(D6:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" s="30">
-        <f>D17/SUM('Inspection Log'!L5:V461)</f>
-        <v/>
-      </c>
-      <c r="F17" s="27" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="D19" s="29">
+        <f>SUM(D6:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="30">
+        <f>D19/SUM('Inspection Log'!L5:X503)</f>
+        <v/>
+      </c>
+      <c r="F19" s="27" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>B.  ROLLUP BY SUPPLIER STATION  (which station to fix first)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Station</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Station Name</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Defect Count</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>% of Total</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Defect Codes</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="B22" s="32" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>Evisceration</t>
         </is>
       </c>
-      <c r="C22" s="33">
-        <f>SUM('Inspection Log'!L5:L461)+SUM('Inspection Log'!M5:M461)+SUM('Inspection Log'!O5:O461)+SUM('Inspection Log'!Q5:Q461)+SUM('Inspection Log'!S5:S461)+SUM('Inspection Log'!U5:U461)</f>
-        <v/>
-      </c>
-      <c r="D22" s="34">
-        <f>C22/SUM('Inspection Log'!L5:V461)</f>
-        <v/>
-      </c>
-      <c r="E22" s="32" t="inlineStr">
-        <is>
-          <t>D1, D2, D4, D6, D8, D10</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="23" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="B23" s="26" t="inlineStr">
-        <is>
-          <t>Carcass splitting</t>
-        </is>
-      </c>
-      <c r="C23" s="12">
-        <f>SUM('Inspection Log'!P5:P461)+SUM('Inspection Log'!V5:V461)</f>
-        <v/>
-      </c>
-      <c r="D23" s="25">
-        <f>C23/SUM('Inspection Log'!L5:V461)</f>
-        <v/>
-      </c>
-      <c r="E23" s="26" t="inlineStr">
-        <is>
-          <t>D5, D11</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="23" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="B24" s="26" t="inlineStr">
-        <is>
-          <t>Bung dropping</t>
-        </is>
-      </c>
-      <c r="C24" s="12">
-        <f>SUM('Inspection Log'!N5:N461)</f>
-        <v/>
-      </c>
-      <c r="D24" s="25">
-        <f>C24/SUM('Inspection Log'!L5:V461)</f>
-        <v/>
-      </c>
-      <c r="E24" s="26" t="inlineStr">
-        <is>
-          <t>D3</t>
+      <c r="C24" s="33">
+        <f>SUM('Inspection Log'!L5:L503)+SUM('Inspection Log'!M5:M503)+SUM('Inspection Log'!O5:O503)+SUM('Inspection Log'!Q5:Q503)+SUM('Inspection Log'!S5:S503)+SUM('Inspection Log'!U5:U503)+SUM('Inspection Log'!W5:W503)+SUM('Inspection Log'!X5:X503)</f>
+        <v/>
+      </c>
+      <c r="D24" s="34">
+        <f>C24/SUM('Inspection Log'!L5:X503)</f>
+        <v/>
+      </c>
+      <c r="E24" s="32" t="inlineStr">
+        <is>
+          <t>D1, D2, D4, D6, D8, D10, D12, D13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>Live / physiology</t>
+          <t>Carcass splitting</t>
         </is>
       </c>
       <c r="C25" s="12">
-        <f>SUM('Inspection Log'!R5:R461)</f>
+        <f>SUM('Inspection Log'!P5:P503)+SUM('Inspection Log'!V5:V503)</f>
         <v/>
       </c>
       <c r="D25" s="25">
-        <f>C25/SUM('Inspection Log'!L5:V461)</f>
+        <f>C25/SUM('Inspection Log'!L5:X503)</f>
         <v/>
       </c>
       <c r="E25" s="26" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D5, D11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="23" t="inlineStr">
         <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>Bung dropping</t>
+        </is>
+      </c>
+      <c r="C26" s="12">
+        <f>SUM('Inspection Log'!N5:N503)</f>
+        <v/>
+      </c>
+      <c r="D26" s="25">
+        <f>C26/SUM('Inspection Log'!L5:X503)</f>
+        <v/>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>Live / physiology</t>
+        </is>
+      </c>
+      <c r="C27" s="12">
+        <f>SUM('Inspection Log'!R5:R503)</f>
+        <v/>
+      </c>
+      <c r="D27" s="25">
+        <f>C27/SUM('Inspection Log'!L5:X503)</f>
+        <v/>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>Sticking / Bleeding</t>
         </is>
       </c>
-      <c r="C26" s="12">
-        <f>SUM('Inspection Log'!T5:T461)</f>
-        <v/>
-      </c>
-      <c r="D26" s="25">
-        <f>C26/SUM('Inspection Log'!L5:V461)</f>
-        <v/>
-      </c>
-      <c r="E26" s="26" t="inlineStr">
+      <c r="C28" s="12">
+        <f>SUM('Inspection Log'!T5:T503)</f>
+        <v/>
+      </c>
+      <c r="D28" s="25">
+        <f>C28/SUM('Inspection Log'!L5:X503)</f>
+        <v/>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>D9</t>
         </is>
@@ -6680,8 +9906,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
   </mergeCells>
@@ -6905,7 +10131,7 @@
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Urethra breach (cut / laceration / hole)</t>
+          <t>Urethra breach (cut / laceration / hole / separation)</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
@@ -7121,7 +10347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7143,7 +10369,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SH: Martins  |  2 batches ingested (kills 2026-05-27 &amp; 2026-07-08)</t>
+          <t>SH: Martins  |  4 inspection sheets across 3 kill dates (2026-05-27, 2026-07-08, 2026-07-28)</t>
         </is>
       </c>
     </row>
@@ -7161,7 +10387,7 @@
         </is>
       </c>
       <c r="B5" s="47">
-        <f>COUNTIF('Inspection Log'!J5:J461,"Pass")+COUNTIF('Inspection Log'!J5:J461,"Fail")</f>
+        <f>COUNTIF('Inspection Log'!J5:J503,"Pass")+COUNTIF('Inspection Log'!J5:J503,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -7172,7 +10398,7 @@
         </is>
       </c>
       <c r="B6" s="47">
-        <f>COUNTIF('Inspection Log'!J5:J461,"Pass")</f>
+        <f>COUNTIF('Inspection Log'!J5:J503,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -7183,7 +10409,7 @@
         </is>
       </c>
       <c r="B7" s="47">
-        <f>COUNTIF('Inspection Log'!J5:J461,"Fail")</f>
+        <f>COUNTIF('Inspection Log'!J5:J503,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -7194,7 +10420,7 @@
         </is>
       </c>
       <c r="B8" s="48">
-        <f>IFERROR(COUNTIF('Inspection Log'!J5:J461,"Pass")/(COUNTIF('Inspection Log'!J5:J461,"Pass")+COUNTIF('Inspection Log'!J5:J461,"Fail")),0)</f>
+        <f>IFERROR(COUNTIF('Inspection Log'!J5:J503,"Pass")/(COUNTIF('Inspection Log'!J5:J503,"Pass")+COUNTIF('Inspection Log'!J5:J503,"Fail")),0)</f>
         <v/>
       </c>
     </row>
@@ -7205,7 +10431,7 @@
         </is>
       </c>
       <c r="B9" s="47">
-        <f>SUM('Inspection Log'!L5:V461)</f>
+        <f>SUM('Inspection Log'!L5:X503)</f>
         <v/>
       </c>
     </row>
@@ -7216,7 +10442,7 @@
         </is>
       </c>
       <c r="B10" s="49">
-        <f>IFERROR(SUM('Inspection Log'!L5:V461)/COUNTIF('Inspection Log'!J5:J461,"Fail"),0)</f>
+        <f>IFERROR(SUM('Inspection Log'!L5:X503)/COUNTIF('Inspection Log'!J5:J503,"Fail"),0)</f>
         <v/>
       </c>
     </row>
@@ -7266,15 +10492,15 @@
         </is>
       </c>
       <c r="B14" s="22">
-        <f>COUNTIF('Inspection Log'!C5:C461,"2026-05-27")</f>
+        <f>COUNTIF('Inspection Log'!C5:C503,"2026-05-27")</f>
         <v/>
       </c>
       <c r="C14" s="22">
-        <f>COUNTIFS('Inspection Log'!C5:C461,"2026-05-27",'Inspection Log'!J5:J461,"Pass")</f>
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-05-27",'Inspection Log'!J5:J503,"Pass")</f>
         <v/>
       </c>
       <c r="D14" s="22">
-        <f>COUNTIFS('Inspection Log'!C5:C461,"2026-05-27",'Inspection Log'!J5:J461,"Fail")</f>
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-05-27",'Inspection Log'!J5:J503,"Fail")</f>
         <v/>
       </c>
       <c r="E14" s="25">
@@ -7294,15 +10520,15 @@
         </is>
       </c>
       <c r="B15" s="22">
-        <f>COUNTIF('Inspection Log'!C5:C461,"2026-07-08")</f>
+        <f>COUNTIF('Inspection Log'!C5:C503,"2026-07-08")</f>
         <v/>
       </c>
       <c r="C15" s="22">
-        <f>COUNTIFS('Inspection Log'!C5:C461,"2026-07-08",'Inspection Log'!J5:J461,"Pass")</f>
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-07-08",'Inspection Log'!J5:J503,"Pass")</f>
         <v/>
       </c>
       <c r="D15" s="22">
-        <f>COUNTIFS('Inspection Log'!C5:C461,"2026-07-08",'Inspection Log'!J5:J461,"Fail")</f>
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-07-08",'Inspection Log'!J5:J503,"Fail")</f>
         <v/>
       </c>
       <c r="E15" s="34">
@@ -7315,73 +10541,109 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="45" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B16" s="22">
+        <f>COUNTIF('Inspection Log'!C5:C503,"2026-07-28")</f>
+        <v/>
+      </c>
+      <c r="C16" s="22">
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-07-28",'Inspection Log'!J5:J503,"Pass")</f>
+        <v/>
+      </c>
+      <c r="D16" s="22">
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-07-28",'Inspection Log'!J5:J503,"Fail")</f>
+        <v/>
+      </c>
+      <c r="E16" s="34">
+        <f>IFERROR(C16/B16,0)</f>
+        <v/>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>D6 Membrane damage in critical area (18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="inlineStr">
         <is>
           <t>Top defect (all batches)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="50" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="50" t="inlineStr">
         <is>
           <t>D6 Membrane damage in critical area</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="51" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Dominant supplier station</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="52" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>S3 Evisceration  -&gt;  primary target for corrective action</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="53" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="53" t="inlineStr">
         <is>
           <t>Critical / food-safety defect occurrences</t>
         </is>
       </c>
-      <c r="B22" s="54">
-        <f>SUM('Inspection Log'!Q5:Q461)+SUM('Inspection Log'!S5:S461)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="55" t="inlineStr">
+      <c r="B23" s="54">
+        <f>SUM('Inspection Log'!Q5:Q503)+SUM('Inspection Log'!S5:S503)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  (Critical codes: D6, D8 — membrane damage &amp; bowel/colon/rectum breach)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="56" t="inlineStr">
-        <is>
-          <t>OPEN ITEM</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" s="57" t="inlineStr">
-        <is>
-          <t>5 blocks (kill 2026-05-27), 8" hole in bladder suspensory ligament, recorded as PASS pending ME/DE determination. If confirmed Fail -&gt; tag D4.</t>
+      <c r="A26" s="56" t="inlineStr">
+        <is>
+          <t>OPEN ITEMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="57" t="inlineStr">
+        <is>
+          <t>1)  5 blocks (kill 2026-05-27), 8" hole in bladder suspensory ligament, recorded as PASS pending ME/DE determination. If confirmed Fail -&gt; tag D4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="57" t="inlineStr">
+        <is>
+          <t>2)  Rasmin 07-28 sheet: handwritten total read '1 Pass / 22 failures', but the per-row entries sum to 29 fails — the granular rows were used. Confirm with inspector.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A18:D18"/>
+  <mergeCells count="6">
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pelvic-block-iqc-pareto/Pelvic_Block_IQC_Pareto_RootCause.xlsx
+++ b/pelvic-block-iqc-pareto/Pelvic_Block_IQC_Pareto_RootCause.xlsx
@@ -723,7 +723,7 @@
               <a:bodyPr/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="950" b="1">
+                  <a:defRPr sz="1000" b="1">
                     <a:solidFill>
                       <a:srgbClr val="404040"/>
                     </a:solidFill>
@@ -733,7 +733,7 @@
                 <a:r>
                   <a:t/>
                 </a:r>
-                <a:endParaRPr sz="950" b="1">
+                <a:endParaRPr sz="1000" b="1">
                   <a:solidFill>
                     <a:srgbClr val="404040"/>
                   </a:solidFill>
@@ -742,7 +742,12 @@
               </a:p>
             </txPr>
             <dLblPos val="outEnd"/>
+            <showLegendKey val="0"/>
             <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
           </dLbls>
           <cat>
             <numRef>
@@ -770,7 +775,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575">
+            <a:ln w="19050">
               <a:solidFill>
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
@@ -779,7 +784,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="C0504D"/>
@@ -793,31 +798,12 @@
             </spPr>
           </marker>
           <dLbls>
-            <numFmt formatCode="0%"/>
-            <txPr>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="850" b="1">
-                    <a:solidFill>
-                      <a:srgbClr val="C0504D"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-                <a:endParaRPr sz="850" b="1">
-                  <a:solidFill>
-                    <a:srgbClr val="C0504D"/>
-                  </a:solidFill>
-                  <a:latin typeface="Calibri"/>
-                </a:endParaRPr>
-              </a:p>
-            </txPr>
-            <dLblPos val="t"/>
-            <showVal val="1"/>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
           </dLbls>
           <val>
             <numRef>
@@ -850,6 +836,14 @@
               </a:ln>
             </spPr>
           </marker>
+          <dLbls>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
           <val>
             <numRef>
               <f>'Pareto'!$N$6:$N$18</f>

--- a/pelvic-block-iqc-pareto/Pelvic_Block_IQC_Pareto_RootCause.xlsx
+++ b/pelvic-block-iqc-pareto/Pelvic_Block_IQC_Pareto_RootCause.xlsx
@@ -11,8 +11,9 @@
     <sheet name="Inspection Log" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Defect Taxonomy" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Pareto" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Root Cause 5-Why" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Dashboard" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Root-Cause Deep-Dive" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Root Cause 5-Why" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Dashboard" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -118,6 +119,17 @@
       <i val="1"/>
       <color rgb="00808080"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -234,7 +246,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -256,11 +268,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -358,10 +414,30 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -370,45 +446,42 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="22" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="22" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="20" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="22" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1361,7 +1434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1449,136 +1522,143 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. Inspection Log   Master data — ONE ROW PER BLOCK. Each free-text scrap reason is normalized into 1/0 flags against the defect taxonomy. Append future batches here.</t>
+          <t xml:space="preserve">  1. Inspection Log      Master data — ONE ROW PER BLOCK. Each free-text scrap reason is normalized into 1/0 flags against the defect taxonomy. Append future batches here.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Defect Taxonomy  Controlled vocabulary (D1–D11) + root-cause map: each defect -&gt; process step, supplier station, 6M cause, mechanism, corrective action.</t>
+          <t xml:space="preserve">  2. Defect Taxonomy     Controlled vocabulary (D1–D13) + root-cause map: each defect -&gt; process step, supplier station, 6M cause, mechanism, corrective action.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Pareto           Auto-calculating defect Pareto (bar + cumulative line) and a rollup by SUPPLIER STATION — the key view for the supplier conversation.</t>
+          <t xml:space="preserve">  3. Pareto              Auto-calculating defect Pareto (bar + cumulative line) and a rollup by SUPPLIER STATION — the key view for the supplier conversation.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Root Cause 5-Why  Structured RCA template, seeded for the vital-few defects, with a Lessons-Learned column to fill in over time.</t>
+          <t xml:space="preserve">  4. Root-Cause Deep-Dive  The pork evisceration process studied: where each defect is BORN, a damage-signature diagnostic, contributing factors, supplier questions, glossary.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. Dashboard        Combined KPIs + a per-batch breakdown so you can watch the trend batch over batch.</t>
+          <t xml:space="preserve">  5. Root Cause 5-Why     Structured RCA template, seeded for the vital-few + new defects, with a Lessons-Learned column to fill in over time.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Dashboard           Combined KPIs + a per-batch breakdown so you can watch the trend batch over batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>HOW TO ADD THE NEXT INSPECTION</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  a. In 'Inspection Log', add one row per inspected block (metadata + Result = Pass/Fail + verbatim reason).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  b. Put a 1 in each defect column (D1–D11) that applies. Use the dropdown. If a NEW defect type appears, add it to 'Defect Taxonomy' first, then add its column.</t>
+          <t xml:space="preserve">  a. In 'Inspection Log', add one row per inspected block (metadata + Result = Pass/Fail + verbatim reason).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  b. Put a 1 in each defect column (D1–D11) that applies. Use the dropdown. If a NEW defect type appears, add it to 'Defect Taxonomy' first, then add its column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  c. Pareto + Dashboard recalc automatically. Re-sort the Pareto table high-&gt;low if the ranking changes (counts are live; row order is not).</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>WHAT THE DATA SAYS SO FAR  (4 inspection sheets across 3 kill dates: 2026-05-27, 2026-07-08, 2026-07-28 — SH: Martins)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  99 blocks inspected · 10 pass · 89 fail · combined First Pass Yield 10.1% · 122 defect occurrences</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Vital few (~80%): membrane damage (critical area), ureters not embedded, urethra breach, bowel/colon/rectum breach, suspensory-ligament damage.  ~84% of ALL defects originate at ONE station: Evisceration.</t>
+          <t xml:space="preserve">  99 blocks inspected · 10 pass · 89 fail · combined First Pass Yield 10.1% · 122 defect occurrences</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Vital few (~80%): membrane damage (critical area), ureters not embedded, urethra breach, bowel/colon/rectum breach, suspensory-ligament damage.  ~84% of ALL defects originate at ONE station: Evisceration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  OPEN ITEMS: (1) 5 blocks (kill 2026-05-27), 8" hole in bladder suspensory ligament — recorded PASS pending ME/DE (flip to Fail + tag D4 if confirmed).  (2) Rasmin 07-28 sheet handwritten total said '22 fails' but per-row entries sum to 29 (used).</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>SEVERITY KEY</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  Critical = function-destroying or food-safety (e.g. bowel/colon/rectum breach = contamination).   Major = block rejected.   Minor = cosmetic / recoverable.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>SOURCE</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  IQC Tally Sheets — SH: Martins. Originals kept as source_*.xlsx in this folder.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="34">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A15:H15"/>
@@ -1605,6 +1685,7 @@
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A28:H28"/>
@@ -8580,7 +8661,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Gut/pluck removal (traction) + pit handling</t>
+          <t>Evisceration traction (gut-set withdrawal)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -8595,12 +8676,12 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>Tensile traction: block pulled/stripped so fascia separates from ureter; over-trim.</t>
+          <t>The ureter runs retroperitoneally in sublumbar fat (ventral to psoas, through the lateral bladder ligaments); caudo-ventral pull on the gut set peels it out of that fat bed intact-but-loose.</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>Standardize gut-pull technique &amp; pull-force; reduce stripping of perirenal fat; gentler drop to pit.</t>
+          <t>Cut the ureters &amp; sublumbar attachments BEFORE withdrawing the gut set (per hand-slaughter standard); slower, controlled set removal; gentler pit drop.</t>
         </is>
       </c>
       <c r="J5" s="18" t="inlineStr"/>
@@ -8628,7 +8709,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Evisceration knife / splitting saw</t>
+          <t>Bung/aitch coring, split saw, or traction avulsion</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -8643,12 +8724,12 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Sharp laceration by evisceration knife or off-line pelvic saw path.</t>
+          <t>Coring knife/aitch blade cuts the pelvic ureter (step 8); split saw shears it if off-center (11); over-pull avulses it at the narrow external-iliac crossing (10).</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>Retrain knife path around pelvic organs; verify saw alignment through symphysis.</t>
+          <t>Coring depth/axis control; verify aitch-blade &amp; split-saw alignment; cut-don't-over-pull the gut set.</t>
         </is>
       </c>
       <c r="J6" s="18" t="inlineStr"/>
@@ -8676,12 +8757,12 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Bung dropping / splitting (over-cut) or lost in handling</t>
+          <t>Bung/aitch over-cut or lost in the dropped set</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>S2 Bung dropping</t>
+          <t>S2 Bung + aitch bone</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -8691,12 +8772,12 @@
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>Over-aggressive bung/pelvic cut removes ureter, or ureter lost during drop/collection.</t>
+          <t>Aitch/bung over-cut removes the distal ureter, or it avulses at the iliac crossing and is lost in the dropped gut set / pit.</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>Tighten bung-dropping cut boundary; audit pit collection for detached tissue.</t>
+          <t>Tighten bung/aitch cut boundary &amp; coring axis; audit pit collection for detached tissue.</t>
         </is>
       </c>
       <c r="J7" s="18" t="inlineStr"/>
@@ -8724,7 +8805,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Gut pull (traction) + handling</t>
+          <t>Evisceration traction (gut-set withdrawal)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -8739,12 +8820,12 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>Excessive pull force / rough handling tears ligament attachments.</t>
+          <t>The bladder is slung by a median ligament (ventral) &amp; paired lateral ligaments (dorsolateral, carrying the ureters); traction on the gut set tears these off the bladder/body wall; the midline knife/saw severs the median ligament.</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>Control pull-force &amp; angle on gut set removal; handle block by support surface, not by ligaments.</t>
+          <t>Handle the block by a support surface, not by the ligaments; control pull-force &amp; angle; cut attachments first.</t>
         </is>
       </c>
       <c r="J8" s="18" t="inlineStr"/>
@@ -8772,7 +8853,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Carcass splitting saw / bung dropping</t>
+          <t>Aitch-bone cut &amp; carcass split saw (midline)</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -8787,12 +8868,12 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>Splitting saw off-center through pelvis, or bung-drop cut catches/perforates urethra.</t>
+          <t>The urethra sits on the midline directly under the pubic symphysis — in the path of BOTH the aitch-bone cut (step 8) and the split saw (step 11); a midline pizzle cut severs the penile urethra in barrows.</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>Center pelvic split on symphysis; calibrate/align splitting saw; slow through pelvic zone.</t>
+          <t>Center the pelvic split on the symphysis; calibrate/align split saw &amp; guide; verify aitch-blade alignment; size-class sorting; keep the pizzle cut off-center.</t>
         </is>
       </c>
       <c r="J9" s="18" t="inlineStr"/>
@@ -8820,7 +8901,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Evisceration knife technique / bung dropping</t>
+          <t>Evisceration traction (gut-set withdrawal)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -8835,12 +8916,12 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>Knife nick or tensile tear of membrane during gut removal / bung loosening.</t>
+          <t>The thin, fenestrated mesentery/broad-ligament membrane is the weakest element under traction and tears/holes first — especially where fingers/hook engage it to pull, or where the knife releases the set.</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>Retrain evisceration knife depth &amp; path; slow line in pelvic zone; blunt-dissect where possible.</t>
+          <t>Cut membrane attachments before pulling; blunt-dissect; slow the line through the pelvic zone; ergonomic relief so operators aren't yanking to keep pace.</t>
         </is>
       </c>
       <c r="J10" s="18" t="inlineStr"/>
@@ -8883,12 +8964,12 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>Distended (full) bladder at slaughter, or compression during handling.</t>
+          <t>Distended (full) bladder at slaughter, or compression/traction on the attachment during handling.</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>Manage lairage/feed-water timing to reduce bladder fill; avoid compressing block.</t>
+          <t>Manage lairage feed/water withdrawal (fasting) to empty the bladder; avoid compressing the block.</t>
         </is>
       </c>
       <c r="J11" s="18" t="inlineStr"/>
@@ -8916,7 +8997,7 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Evisceration / bung dropping</t>
+          <t>Bung margin / belly-opening knife / traction</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -8931,12 +9012,12 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>Knife slip or aggressive bung separation opens/severs colon or rectum.</t>
+          <t>A &lt;1/2" circumanal margin nicks the rectum (step 8); the knife perforates the colon at belly opening (step 9); pull separates colon from rectum (step 10). Bung not sealed before withdrawal.</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>Reinforce bung-bagging/tie-off; retrain knife path; treat as contamination CCP at supplier.</t>
+          <t>Hold a &gt;=1/2" circumanal margin; seal/bag the bung BEFORE pulling; retrain knife path; treat as a contamination CCP.</t>
         </is>
       </c>
       <c r="J12" s="18" t="inlineStr"/>
@@ -8954,7 +9035,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Retained blood clots in the tissue block.</t>
+          <t>Retained blood clots / blood-splash speckle in the tissue block.</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -8964,7 +9045,7 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Sticking / bleeding efficiency</t>
+          <t>Stunning + sticking (stun-to-stick interval)</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -8979,12 +9060,12 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>Incomplete exsanguination (stick placement / stun-to-stick interval / bleed time).</t>
+          <t>Electrical-stun blood-pressure spike + a long/variable stun-to-stick interval ruptures capillaries (splash/speckle) and leaves vessels filled; incomplete bleed-out.</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>Verify stick placement &amp; bleed-out time; check stun-to-stick interval.</t>
+          <t>Shorten &amp; stabilize the stun-to-stick interval; verify stick placement &amp; bleed-out time; consider CO2 stun (fewer hemorrhages).</t>
         </is>
       </c>
       <c r="J13" s="18" t="inlineStr"/>
@@ -9002,7 +9083,7 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Large hole/tear in the broad ligament.</t>
+          <t>Large hole/tear in the broad ligament (mesometrium in gilts).</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
@@ -9012,7 +9093,7 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Evisceration / bung dropping</t>
+          <t>Evisceration traction (gut-set withdrawal)</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -9027,12 +9108,12 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>Traction tear or knife nick near broad ligament during gut removal.</t>
+          <t>The broad ligament suspending the uterus/ovary is torn by the same caudo-ventral pull on the gut set; the ovarian suspensory ligament is a common tear point.</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>Control pull-force; retrain knife path near broad ligament.</t>
+          <t>Control pull-force; cut attachments before pulling; retrain knife path near the broad ligament.</t>
         </is>
       </c>
       <c r="J14" s="18" t="inlineStr"/>
@@ -9060,7 +9141,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Carcass splitting saw / pelvic outlet cut</t>
+          <t>Aitch-bone cut &amp; split saw (symphysis plane)</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -9075,12 +9156,12 @@
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>Saw path or traction at the pelvic floor separates the bladder neck from the urethra.</t>
+          <t>The neck is sheared at the pubic-symphysis plane by the aitch cut / split saw, or avulsed by traction on the urethra/ligaments.</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>Center pelvic split; protect bladder neck at the pelvic outlet; control traction.</t>
+          <t>Center the pelvic split; protect the bladder neck at the pelvic outlet; verify aitch-blade alignment; control traction.</t>
         </is>
       </c>
       <c r="J15" s="18" t="inlineStr"/>
@@ -9108,7 +9189,7 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Evisceration knife / splitting saw</t>
+          <t>Belly opening (knife) - full-bladder risk</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -9123,12 +9204,12 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>Knife nick or saw path opens the bladder; or over-distended bladder ruptures under handling.</t>
+          <t>The knife tip enters the cavity and punctures a distended, thin-walled bladder (a full bladder sits abdominally, in the knife's path) instead of riding along the body wall.</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>Protect bladder during gut removal; verify saw path; manage bladder fill (lairage/water timing).</t>
+          <t>'Unzip' belly cut (handle inside, blade riding outward); sharper knives; fasting/feed-water withdrawal to empty the bladder before slaughter.</t>
         </is>
       </c>
       <c r="J16" s="18" t="inlineStr"/>
@@ -9156,7 +9237,7 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Pelvic-block separation cut (cut-boundary placement)</t>
+          <t>Aitch/split cut height + harvester recovery boundary</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -9171,12 +9252,12 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>Separation cut placed too close; insufficient block length retained vs template/spec.</t>
+          <t>The distal urethra/bladder-neck was already transected high at the aitch-bone cut or split (steps 8/11), leaving insufficient distal length; or the harvester sets the cranial boundary too tight to the bladder.</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>Define &amp; train pelvic-block cut boundaries / minimum length; cut to template; provide a length gauge.</t>
+          <t>Define minimum block length &amp; cut boundaries vs a template/gauge; align aitch/split to preserve distal urethra length; train the recovery boundary cut.</t>
         </is>
       </c>
       <c r="J17" s="18" t="inlineStr"/>
@@ -9831,7 +9912,7 @@
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>Bung dropping</t>
+          <t>Bung + aitch bone</t>
         </is>
       </c>
       <c r="C26" s="12">
@@ -9916,7 +9997,1052 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ROOT-CAUSE DEEP-DIVE — THE PORK EVISCERATION PROCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Where each defect is BORN, before the block reaches the harvest tech. Read the damage 'signature' (Section D) to name the station.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>A.  WHERE YOUR PELVIC BLOCK COMES FROM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Your pelvic block is NOT harvested as a designed unit. It is the caudal (tail) end of the 'gut set' (green offal) — the abdominal-pelvic digestive tract plus the urogenital organs (bladder, ureters, urethra, bladder neck, ligaments, membranes, adjacent colon/rectum) — that is dropped out of the carcass during EVISCERATION onto the viscera table ('the pit'). The supplier's harvester then recovers the pelvic portion from that dropped set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>So almost every defect is inflicted during one of FOUR caudal kill-floor substeps — (1) bung + aitch-bone cut, (2) belly opening, (3) evisceration traction, (4) the split saw — or during the harvester's own boundary cut. The damage SIGNATURE (Section D) tells you which one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>B.  THE PROCESS (stunning -&gt; chilling) — steps 8-11 are the ones that touch the pelvic block</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B9" s="38" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="C9" s="39" t="n"/>
+      <c r="D9" s="38" t="inlineStr">
+        <is>
+          <t>Touches the pelvic block?</t>
+        </is>
+      </c>
+      <c r="E9" s="39" t="n"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Stunning</t>
+        </is>
+      </c>
+      <c r="C10" s="39" t="n"/>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Indirect — drives blood splash / clot retention</t>
+        </is>
+      </c>
+      <c r="E10" s="39" t="n"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Sticking / bleeding (exsanguination)</t>
+        </is>
+      </c>
+      <c r="C11" s="39" t="n"/>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Indirect — stun-to-stick interval -&gt; retained clots</t>
+        </is>
+      </c>
+      <c r="E11" s="39" t="n"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>3-6</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Scald -&gt; dehair -&gt; singe -&gt; polish/wash</t>
+        </is>
+      </c>
+      <c r="C12" s="39" t="n"/>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E12" s="39" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Head dropping</t>
+        </is>
+      </c>
+      <c r="C13" s="39" t="n"/>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E13" s="39" t="n"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>Bung dropping + AITCH-BONE opening</t>
+        </is>
+      </c>
+      <c r="C14" s="39" t="n"/>
+      <c r="D14" s="40" t="inlineStr">
+        <is>
+          <t>YES - PRIMARY: rectum, bladder neck, urethra, distal ureters</t>
+        </is>
+      </c>
+      <c r="E14" s="39" t="n"/>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B15" s="40" t="inlineStr">
+        <is>
+          <t>Belly + brisket opening</t>
+        </is>
+      </c>
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="40" t="inlineStr">
+        <is>
+          <t>YES - HIGH: bladder puncture; sets the plane the gut set is pulled through</t>
+        </is>
+      </c>
+      <c r="E15" s="39" t="n"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B16" s="40" t="inlineStr">
+        <is>
+          <t>EVISCERATION (gut-set / green-offal withdrawal)</t>
+        </is>
+      </c>
+      <c r="C16" s="39" t="n"/>
+      <c r="D16" s="40" t="inlineStr">
+        <is>
+          <t>YES - PRIMARY: strips ureters, tears membranes &amp; ligaments</t>
+        </is>
+      </c>
+      <c r="E16" s="39" t="n"/>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="40" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t>Carcass SPLITTING (saw through spine + pelvis)</t>
+        </is>
+      </c>
+      <c r="C17" s="39" t="n"/>
+      <c r="D17" s="40" t="inlineStr">
+        <is>
+          <t>YES - HIGH: off-center split shears urethra / bladder neck / ureter</t>
+        </is>
+      </c>
+      <c r="E17" s="39" t="n"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Final-rail trim &amp; inspection</t>
+        </is>
+      </c>
+      <c r="C18" s="39" t="n"/>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Trimming can shorten attached urogenital tissue</t>
+        </is>
+      </c>
+      <c r="E18" s="39" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Chilling</t>
+        </is>
+      </c>
+      <c r="C19" s="39" t="n"/>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E19" s="39" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>C.  THE FOUR CAUDAL SUBSTEPS  —  what each one creates, and how</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="38" t="inlineStr">
+        <is>
+          <t>Substep (station)</t>
+        </is>
+      </c>
+      <c r="B22" s="38" t="inlineStr">
+        <is>
+          <t>Defects it creates</t>
+        </is>
+      </c>
+      <c r="C22" s="38" t="inlineStr">
+        <is>
+          <t>Mechanism</t>
+        </is>
+      </c>
+      <c r="D22" s="38" t="inlineStr">
+        <is>
+          <t>Damage signature</t>
+        </is>
+      </c>
+      <c r="E22" s="38" t="inlineStr">
+        <is>
+          <t>Primary fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="74" customHeight="1">
+      <c r="A23" s="41" t="inlineStr">
+        <is>
+          <t>Bung dropping + aitch-bone (S2, step 8)</t>
+        </is>
+      </c>
+      <c r="B23" s="41" t="inlineStr">
+        <is>
+          <t>Rectum nick (D8); distal ureter cut/missing (D2/D3); urethra &amp; bladder-neck cut (D5/D11)</t>
+        </is>
+      </c>
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t>Coring knife too deep / off-axis; the aitch blade crosses the midline urethra &amp; bladder neck</t>
+        </is>
+      </c>
+      <c r="D23" s="41" t="inlineStr">
+        <is>
+          <t>Clean knife slit; fecal spill if rectum</t>
+        </is>
+      </c>
+      <c r="E23" s="41" t="inlineStr">
+        <is>
+          <t>Coring depth/axis control; &gt;=1/2" circumanal margin; aitch-blade alignment; size-adaptive settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="74" customHeight="1">
+      <c r="A24" s="41" t="inlineStr">
+        <is>
+          <t>Belly + brisket opening (S3, step 9)</t>
+        </is>
+      </c>
+      <c r="B24" s="41" t="inlineStr">
+        <is>
+          <t>Bladder hole (D12); median-ligament cut (D4)</t>
+        </is>
+      </c>
+      <c r="C24" s="41" t="inlineStr">
+        <is>
+          <t>Knife tip stabs the distended bladder instead of riding the body wall</t>
+        </is>
+      </c>
+      <c r="D24" s="41" t="inlineStr">
+        <is>
+          <t>Single clean slit; URINE spill</t>
+        </is>
+      </c>
+      <c r="E24" s="41" t="inlineStr">
+        <is>
+          <t>'Unzip' handle-in belly cut; sharper knives; FAST the hogs to empty the bladder</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="74" customHeight="1">
+      <c r="A25" s="41" t="inlineStr">
+        <is>
+          <t>Evisceration traction (S3, step 10)</t>
+        </is>
+      </c>
+      <c r="B25" s="41" t="inlineStr">
+        <is>
+          <t>Ureters not embedded (D1); mesentery / broad / suspensory tears (D6/D10/D4); avulsed ureter (D2)</t>
+        </is>
+      </c>
+      <c r="C25" s="41" t="inlineStr">
+        <is>
+          <t>Caudo-ventral PULL peels the ureter out of its sublumbar fat bed; the thin membranes tear first</t>
+        </is>
+      </c>
+      <c r="D25" s="41" t="inlineStr">
+        <is>
+          <t>Irregular, stretched, FRAYED tear; NO bone dust</t>
+        </is>
+      </c>
+      <c r="E25" s="41" t="inlineStr">
+        <is>
+          <t>Cut ureters &amp; attachments BEFORE pulling; slower set removal; ergonomic relief</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="74" customHeight="1">
+      <c r="A26" s="41" t="inlineStr">
+        <is>
+          <t>Carcass split saw (S4, step 11)</t>
+        </is>
+      </c>
+      <c r="B26" s="41" t="inlineStr">
+        <is>
+          <t>Urethra / bladder-neck / ureter transection (D5/D11/D2)</t>
+        </is>
+      </c>
+      <c r="C26" s="41" t="inlineStr">
+        <is>
+          <t>Saw through the pubic symphysis bisects the midline urogenital tissue; off-center shears one side</t>
+        </is>
+      </c>
+      <c r="D26" s="41" t="inlineStr">
+        <is>
+          <t>Straight parallel KERF + bone dust; matching cut on the mirror side</t>
+        </is>
+      </c>
+      <c r="E26" s="41" t="inlineStr">
+        <is>
+          <t>Saw/guide calibration; blade condition; size-class sorting</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="35" t="inlineStr">
+        <is>
+          <t>D.  DAMAGE-SIGNATURE DIAGNOSTIC  —  read the defect, name the station  (the most useful tool here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="38" t="inlineStr">
+        <is>
+          <t>What you see on the block</t>
+        </is>
+      </c>
+      <c r="B29" s="39" t="n"/>
+      <c r="C29" s="38" t="inlineStr">
+        <is>
+          <t>What it means</t>
+        </is>
+      </c>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="38" t="inlineStr">
+        <is>
+          <t>Look at this station</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="41" t="inlineStr">
+        <is>
+          <t>Straight, parallel-sided cut + bone dust/marrow; matching cut on the mirror side</t>
+        </is>
+      </c>
+      <c r="B30" s="39" t="n"/>
+      <c r="C30" s="41" t="inlineStr">
+        <is>
+          <t>SAW cut</t>
+        </is>
+      </c>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="41" t="inlineStr">
+        <is>
+          <t>S4 Carcass splitting</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="41" t="inlineStr">
+        <is>
+          <t>Single clean slit, no bone dust</t>
+        </is>
+      </c>
+      <c r="B31" s="39" t="n"/>
+      <c r="C31" s="41" t="inlineStr">
+        <is>
+          <t>KNIFE cut</t>
+        </is>
+      </c>
+      <c r="D31" s="39" t="n"/>
+      <c r="E31" s="41" t="inlineStr">
+        <is>
+          <t>S2 Bung/aitch  or  S3 belly opening</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="41" t="inlineStr">
+        <is>
+          <t>Irregular, stretched, FRAYED tear; no bone dust</t>
+        </is>
+      </c>
+      <c r="B32" s="39" t="n"/>
+      <c r="C32" s="41" t="inlineStr">
+        <is>
+          <t>TRACTION tear</t>
+        </is>
+      </c>
+      <c r="D32" s="39" t="n"/>
+      <c r="E32" s="41" t="inlineStr">
+        <is>
+          <t>S3 Evisceration (the pull)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="41" t="inlineStr">
+        <is>
+          <t>Petechiae / speckle in fat &amp; connective tissue</t>
+        </is>
+      </c>
+      <c r="B33" s="39" t="n"/>
+      <c r="C33" s="41" t="inlineStr">
+        <is>
+          <t>Blood splash</t>
+        </is>
+      </c>
+      <c r="D33" s="39" t="n"/>
+      <c r="E33" s="41" t="inlineStr">
+        <is>
+          <t>S1 Stunning / sticking</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="41" t="inlineStr">
+        <is>
+          <t>Fecal spill at the cut</t>
+        </is>
+      </c>
+      <c r="B34" s="39" t="n"/>
+      <c r="C34" s="41" t="inlineStr">
+        <is>
+          <t>Rectum / colon breach</t>
+        </is>
+      </c>
+      <c r="D34" s="39" t="n"/>
+      <c r="E34" s="41" t="inlineStr">
+        <is>
+          <t>S2 bung margin  /  S3 belly knife</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>Urine spill at the cut</t>
+        </is>
+      </c>
+      <c r="B35" s="39" t="n"/>
+      <c r="C35" s="41" t="inlineStr">
+        <is>
+          <t>Bladder breach</t>
+        </is>
+      </c>
+      <c r="D35" s="39" t="n"/>
+      <c r="E35" s="41" t="inlineStr">
+        <is>
+          <t>S3 belly opening (full bladder)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="41" t="inlineStr">
+        <is>
+          <t>Missing distal urethra / short block</t>
+        </is>
+      </c>
+      <c r="B36" s="39" t="n"/>
+      <c r="C36" s="41" t="inlineStr">
+        <is>
+          <t>Cut too high upstream</t>
+        </is>
+      </c>
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="41" t="inlineStr">
+        <is>
+          <t>S2 aitch / S4 split, then harvest boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>E.  CONTRIBUTING FACTORS  —  track these as covariates (by shift, station, hog weight class)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="38" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="B39" s="38" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="C39" s="39" t="n"/>
+      <c r="D39" s="38" t="inlineStr">
+        <is>
+          <t>What to do / track</t>
+        </is>
+      </c>
+      <c r="E39" s="39" t="n"/>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="41" t="inlineStr">
+        <is>
+          <t>Line speed</t>
+        </is>
+      </c>
+      <c r="B40" s="41" t="inlineStr">
+        <is>
+          <t>NSIS removed the federal max line-speed cap; a faster line = rushed coring margins, off-center saw, more yanking</t>
+        </is>
+      </c>
+      <c r="C40" s="39" t="n"/>
+      <c r="D40" s="41" t="inlineStr">
+        <is>
+          <t>Correlate defect rate with line speed / shift; ergonomic relief</t>
+        </is>
+      </c>
+      <c r="E40" s="39" t="n"/>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="41" t="inlineStr">
+        <is>
+          <t>Hog size variability</t>
+        </is>
+      </c>
+      <c r="B41" s="41" t="inlineStr">
+        <is>
+          <t>Bung / aitch / saw are set for an 'average' pelvis and mis-locate on off-size hogs</t>
+        </is>
+      </c>
+      <c r="C41" s="39" t="n"/>
+      <c r="D41" s="41" t="inlineStr">
+        <is>
+          <t>Size-class sorting; size-adaptive tool settings; track defects by weight class</t>
+        </is>
+      </c>
+      <c r="E41" s="39" t="n"/>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="41" t="inlineStr">
+        <is>
+          <t>Bladder fill (fasting)</t>
+        </is>
+      </c>
+      <c r="B42" s="41" t="inlineStr">
+        <is>
+          <t>A full bladder is abdominal &amp; thin-walled, in the knife's path; fasting empties it (~70% of contamination variance)</t>
+        </is>
+      </c>
+      <c r="C42" s="39" t="n"/>
+      <c r="D42" s="41" t="inlineStr">
+        <is>
+          <t>Enforce feed/water withdrawal; verify lairage time; track by fasting time</t>
+        </is>
+      </c>
+      <c r="E42" s="39" t="n"/>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="41" t="inlineStr">
+        <is>
+          <t>Stun-to-stick interval</t>
+        </is>
+      </c>
+      <c r="B43" s="41" t="inlineStr">
+        <is>
+          <t>Long / variable interval -&gt; blood splash &amp; retained clots (D9)</t>
+        </is>
+      </c>
+      <c r="C43" s="39" t="n"/>
+      <c r="D43" s="41" t="inlineStr">
+        <is>
+          <t>Shorten &amp; stabilize the interval; consider CO2 stun</t>
+        </is>
+      </c>
+      <c r="E43" s="39" t="n"/>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="41" t="inlineStr">
+        <is>
+          <t>Knife sharpness</t>
+        </is>
+      </c>
+      <c r="B44" s="41" t="inlineStr">
+        <is>
+          <t>A dull knife needs more force -&gt; over-travel into bladder / urethra / ureter</t>
+        </is>
+      </c>
+      <c r="C44" s="39" t="n"/>
+      <c r="D44" s="41" t="inlineStr">
+        <is>
+          <t>Steel/replace on schedule; sharpness checks</t>
+        </is>
+      </c>
+      <c r="E44" s="39" t="n"/>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="41" t="inlineStr">
+        <is>
+          <t>Saw alignment / calibration</t>
+        </is>
+      </c>
+      <c r="B45" s="41" t="inlineStr">
+        <is>
+          <t>Off-center / worn saw shears the midline urogenital tissue</t>
+        </is>
+      </c>
+      <c r="C45" s="39" t="n"/>
+      <c r="D45" s="41" t="inlineStr">
+        <is>
+          <t>Calibrate guide &amp; blade; preventive-maintenance schedule</t>
+        </is>
+      </c>
+      <c r="E45" s="39" t="n"/>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="41" t="inlineStr">
+        <is>
+          <t>Operator training / fatigue</t>
+        </is>
+      </c>
+      <c r="B46" s="41" t="inlineStr">
+        <is>
+          <t>Margin-setting, the 'unzip' cut, and the cut-vs-yank decision are all skill &amp; attention dependent</t>
+        </is>
+      </c>
+      <c r="C46" s="39" t="n"/>
+      <c r="D46" s="41" t="inlineStr">
+        <is>
+          <t>Train the four substeps; rotate to manage fatigue; track by station/shift</t>
+        </is>
+      </c>
+      <c r="E46" s="39" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="35" t="inlineStr">
+        <is>
+          <t>F.  TAKE TO THE SUPPLIER  —  walk the line and ask / observe</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="41" t="inlineStr">
+        <is>
+          <t>Bung / aitch (S2):</t>
+        </is>
+      </c>
+      <c r="B49" s="41" t="inlineStr">
+        <is>
+          <t>What coring tool &amp; margin? Is the bung sealed/bagged BEFORE withdrawal? Is aitch-blade alignment checked per hog? Size-adaptive?</t>
+        </is>
+      </c>
+      <c r="C49" s="42" t="n"/>
+      <c r="D49" s="42" t="n"/>
+      <c r="E49" s="39" t="n"/>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="41" t="inlineStr">
+        <is>
+          <t>Belly opening (S3):</t>
+        </is>
+      </c>
+      <c r="B50" s="41" t="inlineStr">
+        <is>
+          <t>Is the 'unzip' (handle-in) technique used? Knife-sharpening schedule? What is the fasting / feed-water-withdrawal time before slaughter?</t>
+        </is>
+      </c>
+      <c r="C50" s="42" t="n"/>
+      <c r="D50" s="42" t="n"/>
+      <c r="E50" s="39" t="n"/>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="41" t="inlineStr">
+        <is>
+          <t>Traction (S3):</t>
+        </is>
+      </c>
+      <c r="B51" s="41" t="inlineStr">
+        <is>
+          <t>Are the ureters &amp; sublumbar attachments CUT before the gut set is pulled, or yanked? Line speed at evisceration? Operator ergonomics?</t>
+        </is>
+      </c>
+      <c r="C51" s="42" t="n"/>
+      <c r="D51" s="42" t="n"/>
+      <c r="E51" s="39" t="n"/>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="41" t="inlineStr">
+        <is>
+          <t>Split saw (S4):</t>
+        </is>
+      </c>
+      <c r="B52" s="41" t="inlineStr">
+        <is>
+          <t>How is the split centered? Guide/blade calibration &amp; PM frequency? Are hogs sorted by size class?</t>
+        </is>
+      </c>
+      <c r="C52" s="42" t="n"/>
+      <c r="D52" s="42" t="n"/>
+      <c r="E52" s="39" t="n"/>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="41" t="inlineStr">
+        <is>
+          <t>Cross-cut:</t>
+        </is>
+      </c>
+      <c r="B53" s="41" t="inlineStr">
+        <is>
+          <t>Can they share defect data by shift, station, and hog weight class so we can correlate?</t>
+        </is>
+      </c>
+      <c r="C53" s="42" t="n"/>
+      <c r="D53" s="42" t="n"/>
+      <c r="E53" s="39" t="n"/>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="35" t="inlineStr">
+        <is>
+          <t>G.  GLOSSARY  (use the right terms with the supplier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="41" t="inlineStr">
+        <is>
+          <t>Aitch bone</t>
+        </is>
+      </c>
+      <c r="B56" s="41" t="inlineStr">
+        <is>
+          <t>The pelvic bone / pubic symphysis. 'Opening the aitch' = splitting the symphysis on the midline to open the pelvic canal.</t>
+        </is>
+      </c>
+      <c r="C56" s="42" t="n"/>
+      <c r="D56" s="42" t="n"/>
+      <c r="E56" s="39" t="n"/>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="41" t="inlineStr">
+        <is>
+          <t>Bung</t>
+        </is>
+      </c>
+      <c r="B57" s="41" t="inlineStr">
+        <is>
+          <t>The terminal rectum / anus. 'Bunging' / 'bung dropping' = coring it free of the pelvic wall and sealing it (tie / clip / bag).</t>
+        </is>
+      </c>
+      <c r="C57" s="42" t="n"/>
+      <c r="D57" s="42" t="n"/>
+      <c r="E57" s="39" t="n"/>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="41" t="inlineStr">
+        <is>
+          <t>Rodding</t>
+        </is>
+      </c>
+      <c r="B58" s="41" t="inlineStr">
+        <is>
+          <t>Inserting a rod to free &amp; seal a tube — classically the weasand (esophagus) — before the pull. A 'rodding gun' does the coring/sealing.</t>
+        </is>
+      </c>
+      <c r="C58" s="42" t="n"/>
+      <c r="D58" s="42" t="n"/>
+      <c r="E58" s="39" t="n"/>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="41" t="inlineStr">
+        <is>
+          <t>Weasand</t>
+        </is>
+      </c>
+      <c r="B59" s="41" t="inlineStr">
+        <is>
+          <t>The esophagus (industry term).</t>
+        </is>
+      </c>
+      <c r="C59" s="42" t="n"/>
+      <c r="D59" s="42" t="n"/>
+      <c r="E59" s="39" t="n"/>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="41" t="inlineStr">
+        <is>
+          <t>Pluck</t>
+        </is>
+      </c>
+      <c r="B60" s="41" t="inlineStr">
+        <is>
+          <t>The thoracic organ set removed together — heart, lungs, liver, trachea ('red offal').</t>
+        </is>
+      </c>
+      <c r="C60" s="42" t="n"/>
+      <c r="D60" s="42" t="n"/>
+      <c r="E60" s="39" t="n"/>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="41" t="inlineStr">
+        <is>
+          <t>Gut set / green offal</t>
+        </is>
+      </c>
+      <c r="B61" s="41" t="inlineStr">
+        <is>
+          <t>The abdominal-pelvic digestive tract removed as a unit (stomach, intestines, rectum), carrying the bladder/urogenital organs. Your block is its caudal end.</t>
+        </is>
+      </c>
+      <c r="C61" s="42" t="n"/>
+      <c r="D61" s="42" t="n"/>
+      <c r="E61" s="39" t="n"/>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="41" t="inlineStr">
+        <is>
+          <t>Brisket cut</t>
+        </is>
+      </c>
+      <c r="B62" s="41" t="inlineStr">
+        <is>
+          <t>The cut that opens the sternum / chest to access the pluck.</t>
+        </is>
+      </c>
+      <c r="C62" s="42" t="n"/>
+      <c r="D62" s="42" t="n"/>
+      <c r="E62" s="39" t="n"/>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="41" t="inlineStr">
+        <is>
+          <t>Pizzle</t>
+        </is>
+      </c>
+      <c r="B63" s="41" t="inlineStr">
+        <is>
+          <t>The penis (barrows); in the pig it is the extrapelvic continuation of the urethra, so a mishandled pizzle cut is a urethra defect.</t>
+        </is>
+      </c>
+      <c r="C63" s="42" t="n"/>
+      <c r="D63" s="42" t="n"/>
+      <c r="E63" s="39" t="n"/>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="41" t="inlineStr">
+        <is>
+          <t>Split / sides</t>
+        </is>
+      </c>
+      <c r="B64" s="41" t="inlineStr">
+        <is>
+          <t>Sawing the carcass into two 'sides' down the spine and through the pelvis.</t>
+        </is>
+      </c>
+      <c r="C64" s="42" t="n"/>
+      <c r="D64" s="42" t="n"/>
+      <c r="E64" s="39" t="n"/>
+    </row>
+    <row r="66" ht="56" customHeight="1">
+      <c r="A66" s="43" t="inlineStr">
+        <is>
+          <t>Process grounded in the USDA-FSIS swine HACCP model, Purdue Extension AS-671-W hand-slaughter guide, the FAO slaughter manual, Frontmatec/DMRI/Marel equipment references, and porcine pelvic anatomy (ureter retroperitoneal course; bladder median/lateral ligaments; midline urethra under the pubic symphysis). Defect-&gt;substep attributions are engineering inferences — validate them against your incoming-defect photos and a walk of the supplier's evisceration &amp; splitting stations.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="80">
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="D44:E44"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10015,53 +11141,53 @@
           <t>D6</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>Membrane damage in critical area</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Membrane torn/holed in critical area (&gt;1.5")</t>
+          <t>Hole/tear in mesentery membrane, critical zone (&gt;1.5")</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Knife path too deep / tensile tear during gut pull</t>
+          <t>The thin fenestrated membrane is the weakest element under traction — it tears first</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Evisceration technique not standardized for pelvic zone</t>
+          <t>Gut set pulled caudo-ventrally; fingers/hook engage the membrane to pull</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>No defined knife depth/path SOP + line-speed pressure</t>
-        </is>
-      </c>
-      <c r="G5" s="36" t="inlineStr">
-        <is>
-          <t>(confirm w/ supplier) training + line-speed control gap</t>
-        </is>
-      </c>
-      <c r="H5" s="37" t="inlineStr">
-        <is>
-          <t>Retrain knife depth &amp; path in pelvic zone; blunt-dissect; slow line through pelvic cut</t>
-        </is>
-      </c>
-      <c r="I5" s="38" t="inlineStr">
+          <t>'Pull-don't-cut' evisceration; attachments not released first; line-speed pressure</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>(confirm) no cut-first SOP for pelvic attachments + speed/ergonomic load on eviscerator</t>
+        </is>
+      </c>
+      <c r="H5" s="45" t="inlineStr">
+        <is>
+          <t>Cut membrane attachments BEFORE pulling; blunt-dissect; slow line through pelvic zone; ergonomic relief</t>
+        </is>
+      </c>
+      <c r="I5" s="46" t="inlineStr">
         <is>
           <t>SH Martins - Evisceration lead</t>
         </is>
       </c>
-      <c r="J5" s="38" t="inlineStr"/>
-      <c r="K5" s="39" t="inlineStr">
+      <c r="J5" s="46" t="inlineStr"/>
+      <c r="K5" s="47" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L5" s="40" t="inlineStr"/>
+      <c r="L5" s="41" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
@@ -10069,53 +11195,53 @@
           <t>D1</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>Ureters not embedded</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Ureters not embedded in tissue</t>
+          <t>Ureter lying free, its fat bed empty (not embedded)</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Fascia/perirenal fat stripped away from ureter</t>
+          <t>Retroperitoneal ureter (in sublumbar fat) peeled out of its bed during the pull</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Excessive pull force / over-trim during gut set removal</t>
+          <t>Gut set withdrawn WITHOUT first releasing ureter / sublumbar attachments</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Pull technique &amp; trim spec not controlled</t>
-        </is>
-      </c>
-      <c r="G6" s="36" t="inlineStr">
-        <is>
-          <t>(confirm) handling standard missing</t>
-        </is>
-      </c>
-      <c r="H6" s="37" t="inlineStr">
-        <is>
-          <t>Standardize pull-force &amp; angle; limit fat stripping; gentler pit drop</t>
-        </is>
-      </c>
-      <c r="I6" s="38" t="inlineStr">
+          <t>Hand-slaughter standard ('cut the ureters, don't yank') not applied on the line</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>(confirm) cut-first standard missing; speed rewards pulling over cutting</t>
+        </is>
+      </c>
+      <c r="H6" s="45" t="inlineStr">
+        <is>
+          <t>Cut ureters &amp; sublumbar attachments before withdrawing the set; controlled removal; gentler pit drop</t>
+        </is>
+      </c>
+      <c r="I6" s="46" t="inlineStr">
         <is>
           <t>SH Martins - Evisceration lead</t>
         </is>
       </c>
-      <c r="J6" s="38" t="inlineStr"/>
-      <c r="K6" s="39" t="inlineStr">
+      <c r="J6" s="46" t="inlineStr"/>
+      <c r="K6" s="47" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L6" s="40" t="inlineStr"/>
+      <c r="L6" s="41" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
@@ -10123,203 +11249,297 @@
           <t>D5</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>Urethra breach (cut / laceration / hole / separation)</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Urethra cut / laceration / hole</t>
+          <t>Urethra cut / laceration / hole / separation</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Sharp transection or perforation through pelvic zone</t>
+          <t>The urethra sits on the midline directly under the pubic symphysis</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Splitting saw off-center / bung-drop cut catches urethra</t>
+          <t>In the plane of BOTH the aitch-bone cut and the split saw; off-axis / over-deep cut hits it</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Saw alignment &amp; pelvic-split centering not verified</t>
-        </is>
-      </c>
-      <c r="G7" s="36" t="inlineStr">
-        <is>
-          <t>(confirm) saw calibration + technique gap</t>
-        </is>
-      </c>
-      <c r="H7" s="37" t="inlineStr">
-        <is>
-          <t>Center split on symphysis; calibrate/align saw; slow through pelvic zone</t>
-        </is>
-      </c>
-      <c r="I7" s="38" t="inlineStr">
-        <is>
-          <t>SH Martins - Splitting lead</t>
-        </is>
-      </c>
-      <c r="J7" s="38" t="inlineStr"/>
-      <c r="K7" s="39" t="inlineStr">
+          <t>Saw/guide &amp; aitch-blade alignment not verified per hog size; size variability</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>(confirm) size-adaptive settings + saw calibration gap</t>
+        </is>
+      </c>
+      <c r="H7" s="45" t="inlineStr">
+        <is>
+          <t>Center split on symphysis; calibrate saw/guide; verify aitch-blade; size-class sorting</t>
+        </is>
+      </c>
+      <c r="I7" s="46" t="inlineStr">
+        <is>
+          <t>SH Martins - Splitting / Bung lead</t>
+        </is>
+      </c>
+      <c r="J7" s="46" t="inlineStr"/>
+      <c r="K7" s="47" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L7" s="40" t="inlineStr"/>
+      <c r="L7" s="41" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>D4</t>
-        </is>
-      </c>
-      <c r="B8" s="35" t="inlineStr">
-        <is>
-          <t>Suspensory ligaments damaged</t>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="B8" s="44" t="inlineStr">
+        <is>
+          <t>Bowel / colon / rectum breach</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>Suspensory ligaments torn/frayed/holed</t>
+          <t>Rectum / colon breached (FOOD SAFETY)</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Block pulled/handled by the ligaments</t>
+          <t>&lt;1/2" circumanal margin nicks rectum; knife perforates colon; pull separates colon</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>Rough handling + high traction on removal</t>
+          <t>Coring margin too tight at speed; bung not sealed before the pull</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>No 'support-surface' handling rule</t>
-        </is>
-      </c>
-      <c r="G8" s="36" t="inlineStr">
-        <is>
-          <t>(confirm) handling standard missing</t>
-        </is>
-      </c>
-      <c r="H8" s="37" t="inlineStr">
-        <is>
-          <t>Handle block by support surface, not ligaments; control pull force</t>
-        </is>
-      </c>
-      <c r="I8" s="38" t="inlineStr">
-        <is>
-          <t>SH Martins - Evisceration lead</t>
-        </is>
-      </c>
-      <c r="J8" s="38" t="inlineStr"/>
-      <c r="K8" s="39" t="inlineStr">
+          <t>Margin/seal SOP not enforced; bung-dropping CCP not robust</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>(confirm) contamination-control gap at the bung/aitch station + speed</t>
+        </is>
+      </c>
+      <c r="H8" s="45" t="inlineStr">
+        <is>
+          <t>Hold &gt;=1/2" margin; seal/bag bung BEFORE pulling; retrain knife path; contamination CCP</t>
+        </is>
+      </c>
+      <c r="I8" s="46" t="inlineStr">
+        <is>
+          <t>SH Martins - Bung/Evisc. lead</t>
+        </is>
+      </c>
+      <c r="J8" s="46" t="inlineStr"/>
+      <c r="K8" s="47" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L8" s="40" t="inlineStr"/>
+      <c r="L8" s="41" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>D8</t>
-        </is>
-      </c>
-      <c r="B9" s="35" t="inlineStr">
-        <is>
-          <t>Bowel / colon / rectum breach</t>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B9" s="44" t="inlineStr">
+        <is>
+          <t>Suspensory ligaments damaged</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Bowel/colon/rectum breached (FOOD SAFETY)</t>
+          <t>Median/lateral bladder &amp; suspensory ligaments torn</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Knife slip or aggressive bung separation opens colon/rectum</t>
+          <t>Traction on the gut set/bladder tears the ligaments off the bladder/body wall</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Bung not adequately bagged/tied before cut</t>
+          <t>Block pulled/handled BY the ligaments; median ligament severed by midline knife/saw</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>Bung-dropping CCP not robust</t>
-        </is>
-      </c>
-      <c r="G9" s="36" t="inlineStr">
-        <is>
-          <t>(confirm) contamination-control gap at bung station</t>
-        </is>
-      </c>
-      <c r="H9" s="37" t="inlineStr">
-        <is>
-          <t>Reinforce bung bag/tie-off; retrain knife path; treat as contamination CCP</t>
-        </is>
-      </c>
-      <c r="I9" s="38" t="inlineStr">
-        <is>
-          <t>SH Martins - Bung/Evisc. lead</t>
-        </is>
-      </c>
-      <c r="J9" s="38" t="inlineStr"/>
-      <c r="K9" s="39" t="inlineStr">
+          <t>No 'handle-by-support-surface' rule; pull-force &amp; angle uncontrolled</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>(confirm) handling standard missing + speed</t>
+        </is>
+      </c>
+      <c r="H9" s="45" t="inlineStr">
+        <is>
+          <t>Handle by a support surface, not the ligaments; control pull-force; cut attachments first</t>
+        </is>
+      </c>
+      <c r="I9" s="46" t="inlineStr">
+        <is>
+          <t>SH Martins - Evisceration lead</t>
+        </is>
+      </c>
+      <c r="J9" s="46" t="inlineStr"/>
+      <c r="K9" s="47" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L9" s="40" t="inlineStr"/>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="41" t="n"/>
-      <c r="B10" s="41" t="n"/>
-      <c r="C10" s="41" t="n"/>
-      <c r="D10" s="41" t="n"/>
-      <c r="E10" s="41" t="n"/>
-      <c r="F10" s="41" t="n"/>
-      <c r="G10" s="42" t="n"/>
-      <c r="H10" s="43" t="n"/>
-      <c r="I10" s="41" t="n"/>
-      <c r="J10" s="41" t="n"/>
-      <c r="K10" s="41" t="n"/>
-      <c r="L10" s="44" t="n"/>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="41" t="n"/>
-      <c r="B11" s="41" t="n"/>
-      <c r="C11" s="41" t="n"/>
-      <c r="D11" s="41" t="n"/>
-      <c r="E11" s="41" t="n"/>
-      <c r="F11" s="41" t="n"/>
-      <c r="G11" s="42" t="n"/>
-      <c r="H11" s="43" t="n"/>
-      <c r="I11" s="41" t="n"/>
-      <c r="J11" s="41" t="n"/>
-      <c r="K11" s="41" t="n"/>
-      <c r="L11" s="44" t="n"/>
+      <c r="L9" s="41" t="inlineStr"/>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+      <c r="B10" s="44" t="inlineStr">
+        <is>
+          <t>Bladder cut / hole (breach)</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Bladder cut open / large hole (urine spill)</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Knife tip punctures a distended, thin-walled bladder during belly opening</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Bladder full &amp; sitting abdominally (in the knife's path); stab entry, not an 'unzip'</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Fasting (feed/water withdrawal) not enforced; belly-cut technique not standardized</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>(confirm) lairage feed-water timing + belly-opening technique gap</t>
+        </is>
+      </c>
+      <c r="H10" s="45" t="inlineStr">
+        <is>
+          <t>Fasting to empty the bladder; 'unzip' handle-in belly cut; sharper knives</t>
+        </is>
+      </c>
+      <c r="I10" s="46" t="inlineStr">
+        <is>
+          <t>SH Martins - Evisc./Lairage lead</t>
+        </is>
+      </c>
+      <c r="J10" s="46" t="inlineStr"/>
+      <c r="K10" s="47" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L10" s="41" t="inlineStr"/>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="B11" s="44" t="inlineStr">
+        <is>
+          <t>Block too short / undersized</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Block too short / fails the length template</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Distal urethra/bladder-neck already transected high at the aitch-bone cut or split</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Aitch/split cut takes too much distal length, OR harvester boundary set too tight to bladder</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>No cut-height / minimum-length spec vs a template at aitch/split + recovery</t>
+        </is>
+      </c>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>(confirm) length spec/gauge missing across aitch, split, and recovery cut</t>
+        </is>
+      </c>
+      <c r="H11" s="45" t="inlineStr">
+        <is>
+          <t>Define min block length &amp; boundaries vs template/gauge; align aitch/split to preserve distal urethra</t>
+        </is>
+      </c>
+      <c r="I11" s="46" t="inlineStr">
+        <is>
+          <t>SH Martins - Splitting + Harvest lead</t>
+        </is>
+      </c>
+      <c r="J11" s="46" t="inlineStr"/>
+      <c r="K11" s="47" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L11" s="41" t="inlineStr"/>
     </row>
     <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="41" t="n"/>
-      <c r="B12" s="41" t="n"/>
-      <c r="C12" s="41" t="n"/>
-      <c r="D12" s="41" t="n"/>
-      <c r="E12" s="41" t="n"/>
-      <c r="F12" s="41" t="n"/>
-      <c r="G12" s="42" t="n"/>
-      <c r="H12" s="43" t="n"/>
-      <c r="I12" s="41" t="n"/>
-      <c r="J12" s="41" t="n"/>
-      <c r="K12" s="41" t="n"/>
-      <c r="L12" s="44" t="n"/>
+      <c r="A12" s="48" t="n"/>
+      <c r="B12" s="48" t="n"/>
+      <c r="C12" s="48" t="n"/>
+      <c r="D12" s="48" t="n"/>
+      <c r="E12" s="48" t="n"/>
+      <c r="F12" s="48" t="n"/>
+      <c r="G12" s="49" t="n"/>
+      <c r="H12" s="50" t="n"/>
+      <c r="I12" s="48" t="n"/>
+      <c r="J12" s="48" t="n"/>
+      <c r="K12" s="48" t="n"/>
+      <c r="L12" s="51" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="48" t="n"/>
+      <c r="B13" s="48" t="n"/>
+      <c r="C13" s="48" t="n"/>
+      <c r="D13" s="48" t="n"/>
+      <c r="E13" s="48" t="n"/>
+      <c r="F13" s="48" t="n"/>
+      <c r="G13" s="49" t="n"/>
+      <c r="H13" s="50" t="n"/>
+      <c r="I13" s="48" t="n"/>
+      <c r="J13" s="48" t="n"/>
+      <c r="K13" s="48" t="n"/>
+      <c r="L13" s="51" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10335,7 +11555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10368,80 +11588,80 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="52" t="inlineStr">
         <is>
           <t>KEY METRICS (all batches)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="46" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>Blocks Inspected</t>
         </is>
       </c>
-      <c r="B5" s="47">
+      <c r="B5" s="54">
         <f>COUNTIF('Inspection Log'!J5:J503,"Pass")+COUNTIF('Inspection Log'!J5:J503,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="46" t="inlineStr">
+      <c r="A6" s="53" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="54">
         <f>COUNTIF('Inspection Log'!J5:J503,"Pass")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="46" t="inlineStr">
+      <c r="A7" s="53" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="B7" s="47">
+      <c r="B7" s="54">
         <f>COUNTIF('Inspection Log'!J5:J503,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="46" t="inlineStr">
+      <c r="A8" s="53" t="inlineStr">
         <is>
           <t>First Pass Yield</t>
         </is>
       </c>
-      <c r="B8" s="48">
+      <c r="B8" s="55">
         <f>IFERROR(COUNTIF('Inspection Log'!J5:J503,"Pass")/(COUNTIF('Inspection Log'!J5:J503,"Pass")+COUNTIF('Inspection Log'!J5:J503,"Fail")),0)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="46" t="inlineStr">
+      <c r="A9" s="53" t="inlineStr">
         <is>
           <t>Total Defect Occurrences</t>
         </is>
       </c>
-      <c r="B9" s="47">
+      <c r="B9" s="54">
         <f>SUM('Inspection Log'!L5:X503)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="46" t="inlineStr">
+      <c r="A10" s="53" t="inlineStr">
         <is>
           <t>Defects per Failed Block</t>
         </is>
       </c>
-      <c r="B10" s="49">
+      <c r="B10" s="56">
         <f>IFERROR(SUM('Inspection Log'!L5:X503)/COUNTIF('Inspection Log'!J5:J503,"Fail"),0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="A12" s="52" t="inlineStr">
         <is>
           <t>PER-BATCH BREAKDOWN (watch the trend)</t>
         </is>
@@ -10564,67 +11784,67 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="45" t="inlineStr">
+      <c r="A18" s="52" t="inlineStr">
         <is>
           <t>Top defect (all batches)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="50" t="inlineStr">
+      <c r="A19" s="57" t="inlineStr">
         <is>
           <t>D6 Membrane damage in critical area</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="51" t="inlineStr">
+      <c r="A20" s="58" t="inlineStr">
         <is>
           <t>Dominant supplier station</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="52" t="inlineStr">
+      <c r="A21" s="59" t="inlineStr">
         <is>
           <t>S3 Evisceration  -&gt;  primary target for corrective action</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="53" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>Critical / food-safety defect occurrences</t>
         </is>
       </c>
-      <c r="B23" s="54">
+      <c r="B23" s="61">
         <f>SUM('Inspection Log'!Q5:Q503)+SUM('Inspection Log'!S5:S503)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="55" t="inlineStr">
+      <c r="A24" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  (Critical codes: D6, D8 — membrane damage &amp; bowel/colon/rectum breach)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="56" t="inlineStr">
+      <c r="A26" s="63" t="inlineStr">
         <is>
           <t>OPEN ITEMS</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="57" t="inlineStr">
+      <c r="A27" s="64" t="inlineStr">
         <is>
           <t>1)  5 blocks (kill 2026-05-27), 8" hole in bladder suspensory ligament, recorded as PASS pending ME/DE determination. If confirmed Fail -&gt; tag D4.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="57" t="inlineStr">
+      <c r="A28" s="64" t="inlineStr">
         <is>
           <t>2)  Rasmin 07-28 sheet: handwritten total read '1 Pass / 22 failures', but the per-row entries sum to 29 fails — the granular rows were used. Confirm with inspector.</t>
         </is>

--- a/pelvic-block-iqc-pareto/Pelvic_Block_IQC_Pareto_RootCause.xlsx
+++ b/pelvic-block-iqc-pareto/Pelvic_Block_IQC_Pareto_RootCause.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Root-Cause Deep-Dive" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Root Cause 5-Why" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Dashboard" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Yield &amp; Alignment" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -197,6 +198,23 @@
       <color rgb="00833C00"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="40"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00444444"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -316,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -482,6 +500,36 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="29" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1434,7 +1482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1562,107 +1610,115 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Yield &amp; Alignment   Good-pelvic % across the board; what it may mean for harvest-tech training; and tech&lt;-&gt;inspector alignment (with input cells).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>HOW TO ADD THE NEXT INSPECTION</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  a. In 'Inspection Log', add one row per inspected block (metadata + Result = Pass/Fail + verbatim reason).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  b. Put a 1 in each defect column (D1–D11) that applies. Use the dropdown. If a NEW defect type appears, add it to 'Defect Taxonomy' first, then add its column.</t>
+          <t xml:space="preserve">  a. In 'Inspection Log', add one row per inspected block (metadata + Result = Pass/Fail + verbatim reason).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  b. Put a 1 in each defect column (D1–D11) that applies. Use the dropdown. If a NEW defect type appears, add it to 'Defect Taxonomy' first, then add its column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  c. Pareto + Dashboard recalc automatically. Re-sort the Pareto table high-&gt;low if the ranking changes (counts are live; row order is not).</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>WHAT THE DATA SAYS SO FAR  (4 inspection sheets across 3 kill dates: 2026-05-27, 2026-07-08, 2026-07-28 — SH: Martins)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  99 blocks inspected · 10 pass · 89 fail · combined First Pass Yield 10.1% · 122 defect occurrences</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Vital few (~80%): membrane damage (critical area), ureters not embedded, urethra breach, bowel/colon/rectum breach, suspensory-ligament damage.  ~84% of ALL defects originate at ONE station: Evisceration.</t>
+          <t xml:space="preserve">  99 blocks inspected · 10 pass · 89 fail · combined First Pass Yield 10.1% · 122 defect occurrences</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Vital few (~80%): membrane damage (critical area), ureters not embedded, urethra breach, bowel/colon/rectum breach, suspensory-ligament damage.  ~84% of ALL defects originate at ONE station: Evisceration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  OPEN ITEMS: (1) 5 blocks (kill 2026-05-27), 8" hole in bladder suspensory ligament — recorded PASS pending ME/DE (flip to Fail + tag D4 if confirmed).  (2) Rasmin 07-28 sheet handwritten total said '22 fails' but per-row entries sum to 29 (used).</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>SEVERITY KEY</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  Critical = function-destroying or food-safety (e.g. bowel/colon/rectum breach = contamination).   Major = block rejected.   Minor = cosmetic / recoverable.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>SOURCE</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  IQC Tally Sheets — SH: Martins. Originals kept as source_*.xlsx in this folder.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="35">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A6:H6"/>
@@ -11861,4 +11917,429 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>YIELD &amp; INSPECTOR–TECH ALIGNMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>How many pelvics are good across the board — and what it may say about harvest-tech training and tech&lt;-&gt;inspector alignment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>GOOD PELVICS — ACROSS THE BOARD  (First Pass Yield = good / inspected)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="65">
+        <f>IFERROR(COUNTIFS('Inspection Log'!J5:J503,"Pass")/(COUNTIFS('Inspection Log'!J5:J503,"Pass")+COUNTIFS('Inspection Log'!J5:J503,"Fail")),0)</f>
+        <v/>
+      </c>
+      <c r="B5" s="51" t="n"/>
+      <c r="C5" s="66" t="inlineStr">
+        <is>
+          <t>of pelvic blocks that reach inspection pass IQC on the first look.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="51" t="n"/>
+      <c r="B6" s="51" t="n"/>
+      <c r="C6" s="67">
+        <f>"= "&amp;COUNTIFS('Inspection Log'!J5:J503,"Pass")&amp;" good  /  "&amp;(COUNTIFS('Inspection Log'!J5:J503,"Pass")+COUNTIFS('Inspection Log'!J5:J503,"Fail"))&amp;" inspected  -&gt;  ~9 of every 10 blocks are rejected"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="51" t="n"/>
+      <c r="B7" s="51" t="n"/>
+      <c r="C7" s="68" t="inlineStr">
+        <is>
+          <t>A yield this low is first a SUPPLIER signal (84% of defects are evisceration-origin) — but it also frames the tech/inspector questions below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="69" t="inlineStr">
+        <is>
+          <t>Caveat: the 8 passes on 2026-05-27 include 5 blocks recorded Pass pending ME/DE. If those are confirmed failures, the across-the-board good rate falls to ~5% (5/99).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>GOOD RATE BY INSPECTION SHEET  (kill date x inspector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Kill Date</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Inspector</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Inspected</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Good (pass)</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Good %</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>(unnamed)</t>
+        </is>
+      </c>
+      <c r="C12" s="7">
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-05-27",'Inspection Log'!J5:J503,"Pass")+COUNTIFS('Inspection Log'!C5:C503,"2026-05-27",'Inspection Log'!J5:J503,"Fail")</f>
+        <v/>
+      </c>
+      <c r="D12" s="7">
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-05-27",'Inspection Log'!J5:J503,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E12" s="70">
+        <f>IFERROR(D12/C12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>(unnamed)</t>
+        </is>
+      </c>
+      <c r="C13" s="7">
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-07-08",'Inspection Log'!J5:J503,"Pass")+COUNTIFS('Inspection Log'!C5:C503,"2026-07-08",'Inspection Log'!J5:J503,"Fail")</f>
+        <v/>
+      </c>
+      <c r="D13" s="7">
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-07-08",'Inspection Log'!J5:J503,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E13" s="70">
+        <f>IFERROR(D13/C13,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Rasmin</t>
+        </is>
+      </c>
+      <c r="C14" s="7">
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-07-28",'Inspection Log'!G5:G503,"Rasmin",'Inspection Log'!J5:J503,"Pass")+COUNTIFS('Inspection Log'!C5:C503,"2026-07-28",'Inspection Log'!G5:G503,"Rasmin",'Inspection Log'!J5:J503,"Fail")</f>
+        <v/>
+      </c>
+      <c r="D14" s="7">
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-07-28",'Inspection Log'!G5:G503,"Rasmin",'Inspection Log'!J5:J503,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E14" s="70">
+        <f>IFERROR(D14/C14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Toni</t>
+        </is>
+      </c>
+      <c r="C15" s="7">
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-07-28",'Inspection Log'!G5:G503,"Toni",'Inspection Log'!J5:J503,"Pass")+COUNTIFS('Inspection Log'!C5:C503,"2026-07-28",'Inspection Log'!G5:G503,"Toni",'Inspection Log'!J5:J503,"Fail")</f>
+        <v/>
+      </c>
+      <c r="D15" s="7">
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-07-28",'Inspection Log'!G5:G503,"Toni",'Inspection Log'!J5:J503,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E15" s="70">
+        <f>IFERROR(D15/C15,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B16" s="29" t="inlineStr"/>
+      <c r="C16" s="29">
+        <f>COUNTIFS('Inspection Log'!J5:J503,"Pass")+COUNTIFS('Inspection Log'!J5:J503,"Fail")</f>
+        <v/>
+      </c>
+      <c r="D16" s="29">
+        <f>COUNTIFS('Inspection Log'!J5:J503,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E16" s="71">
+        <f>IFERROR(D16/C16,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>WHAT THIS COULD MEAN ABOUT HARVEST-TECH TRAINING</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t>The harvest techs are the first-pass filter: they recover blocks from the pit and keep (spec-out) or discard each one. A ~10% good rate can mean two very different things, and the current data cannot fully separate them:</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="72" t="inlineStr">
+        <is>
+          <t>1)  MATERIAL (most likely).  The incoming tissue is overwhelmingly defective — 84% of defects are evisceration-origin — so even a perfectly-trained tech would keep mostly-bad blocks because there is little good material to choose from. Here the low yield is a SUPPLIER signal, not a tech signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="72" t="inlineStr">
+        <is>
+          <t>2)  CALIBRATION GAP.  If the techs are keeping blocks that inspectors then reject, their internal 'good/bad' threshold is looser than the inspection spec — a training / standardization gap. The tell for this is a high tech KEEP rate paired with a low IQC pass rate (see alignment below).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="73" t="inlineStr">
+        <is>
+          <t>Reading them together: because the defects are dominated by real, supplier-side damage, (1) is the stronger explanation today — but (2) cannot be ruled out until we log the techs' keep/discard decisions. A quick check: have a lead re-grade a sample of kept AND discarded blocks against the written spec and compare to both the tech and the inspector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="35" t="inlineStr">
+        <is>
+          <t>INSPECTOR &lt;-&gt; HARVEST-TECH ALIGNMENT  (agreement on the good/bad call)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="64" customHeight="1">
+      <c r="A25" s="36" t="inlineStr">
+        <is>
+          <t>Alignment = do the harvest tech (keep/discard) and the inspector (pass/fail) make the SAME good/bad call on the same block? What we can see now: the inspected blocks are the ones the techs KEPT, and inspectors pass only ~10% of them — so on the KEEP decision the two groups agree ~10% of the time (9 of 10 blocks a tech judged good enough to keep, the inspector rejected). That is a strong misalignment signal, but it is confounded with material quality, and we cannot yet see the techs' DISCARD calls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="73" t="inlineStr">
+        <is>
+          <t>To measure alignment properly, enter the harvest-tech first-pass numbers below (received from pit, discarded first-pass). Then the agreement metrics compute automatically. Also re-inspect a sample of discarded blocks to catch over-discarding (good blocks thrown away).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Kill Date</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Received from pit  (enter)</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Tech discarded 1st-pass  (enter)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>IQC inspected (=kept)</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>IQC good</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Tech reject %</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Good-from-pit %</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B29" s="74" t="n"/>
+      <c r="C29" s="74" t="n"/>
+      <c r="D29" s="7">
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-05-27",'Inspection Log'!J5:J503,"Pass")+COUNTIFS('Inspection Log'!C5:C503,"2026-05-27",'Inspection Log'!J5:J503,"Fail")</f>
+        <v/>
+      </c>
+      <c r="E29" s="7">
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-05-27",'Inspection Log'!J5:J503,"Pass")</f>
+        <v/>
+      </c>
+      <c r="F29" s="70">
+        <f>IF(B29="","",IFERROR(C29/B29,0))</f>
+        <v/>
+      </c>
+      <c r="G29" s="70">
+        <f>IF(B29="","",IFERROR(E29/B29,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B30" s="74" t="n"/>
+      <c r="C30" s="74" t="n"/>
+      <c r="D30" s="7">
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-07-08",'Inspection Log'!J5:J503,"Pass")+COUNTIFS('Inspection Log'!C5:C503,"2026-07-08",'Inspection Log'!J5:J503,"Fail")</f>
+        <v/>
+      </c>
+      <c r="E30" s="7">
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-07-08",'Inspection Log'!J5:J503,"Pass")</f>
+        <v/>
+      </c>
+      <c r="F30" s="70">
+        <f>IF(B30="","",IFERROR(C30/B30,0))</f>
+        <v/>
+      </c>
+      <c r="G30" s="70">
+        <f>IF(B30="","",IFERROR(E30/B30,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B31" s="74" t="n"/>
+      <c r="C31" s="74" t="n"/>
+      <c r="D31" s="7">
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-07-28",'Inspection Log'!J5:J503,"Pass")+COUNTIFS('Inspection Log'!C5:C503,"2026-07-28",'Inspection Log'!J5:J503,"Fail")</f>
+        <v/>
+      </c>
+      <c r="E31" s="7">
+        <f>COUNTIFS('Inspection Log'!C5:C503,"2026-07-28",'Inspection Log'!J5:J503,"Pass")</f>
+        <v/>
+      </c>
+      <c r="F31" s="70">
+        <f>IF(B31="","",IFERROR(C31/B31,0))</f>
+        <v/>
+      </c>
+      <c r="G31" s="70">
+        <f>IF(B31="","",IFERROR(E31/B31,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="62" t="inlineStr">
+        <is>
+          <t>Tech reject % = discarded / received.   Good-from-pit % = IQC good / received (the true end-to-end yield).   IQC good / IQC inspected = the agreement on kept blocks (headline above).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A5:B7"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A10:G10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>